--- a/literature/concept-map/concept-map.xlsx
+++ b/literature/concept-map/concept-map.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="896">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="888">
   <si>
     <t xml:space="preserve">Concept map of the note “Voting for a consensus with veto rights” (v0.1)</t>
   </si>
@@ -270,8 +270,8 @@
     <t xml:space="preserve">Brams &amp; Fishburn (1978). Approval Voting
 Balinski &amp; Laraki (2007). A Theory of Measuring, Electing, and Ranking
 Felsenthal &amp; Machover (2008). The Majority Judgement Voting Procedure: A Critical Evaluation
-Balinski &amp; Laraki (2010). Majority Judgment: Measuring, Ranking, and Electing
 Laslier &amp; Sanver (2010). Handbook on Approval Voting
+Balinski &amp; Laraki (2011). Majority Judgment: Measuring, Ranking, and Electing
 Laslier (2012). And the Loser Is… Plurality Voting</t>
   </si>
   <si>
@@ -903,7 +903,7 @@
     <t xml:space="preserve">https://doi.org/10.1073/pnas.0702634104</t>
   </si>
   <si>
-    <t xml:space="preserve">Balinski &amp; Laraki (2010). Majority Judgment: Measuring, Ranking, and Electing</t>
+    <t xml:space="preserve">Balinski &amp; Laraki (2011). Majority Judgment: Measuring, Ranking, and Electing</t>
   </si>
   <si>
     <t xml:space="preserve">Book-length theory of Majority Judgment: measuring, ranking and electing with grades.</t>
@@ -912,7 +912,10 @@
     <t xml:space="preserve">BalinskiLaraki2011</t>
   </si>
   <si>
-    <t xml:space="preserve">Balinski, M. &amp; Laraki, R. (2010). Majority Judgment: Measuring, Ranking, and Electing. MIT Press.</t>
+    <t xml:space="preserve">Balinski, M. &amp; Laraki, R. (2011). Majority Judgment: Measuring, Ranking, and Electing. MIT Press.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.7551/mitpress/9780262015134.001.0001</t>
   </si>
   <si>
     <t xml:space="preserve">Barberà &amp; Coelho (2017). Balancing the Power to Appoint Officers</t>
@@ -1014,9 +1017,6 @@
     <t xml:space="preserve">https://doi.org/10.1007/BF00303169</t>
   </si>
   <si>
-    <t xml:space="preserve">To verify: issue number</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bartholdi et al. (1989). The Computational Difficulty of Manipulating an Election</t>
   </si>
   <si>
@@ -1032,7 +1032,7 @@
     <t xml:space="preserve">Bartholdi, I. J. J., Tovey, C. A. &amp; Trick, M. A. (1989). The Computational Difficulty of Manipulating an Election. Social Choice and Welfare 6(3): 227–241.</t>
   </si>
   <si>
-    <t xml:space="preserve">To verify: DOI (probably 10.1007/BF00295861, not confirmed)</t>
+    <t xml:space="preserve">https://doi.org/10.1007/BF00295861</t>
   </si>
   <si>
     <t xml:space="preserve">Black (1948). On the Rationale of Group Decision-Making</t>
@@ -1204,7 +1204,7 @@
     <t xml:space="preserve">Brandt, F., Geist, C. &amp; Peters, D. (2017). Optimal Bounds for the No-Show Paradox via SAT Solving. Mathematical Social Sciences 90: 18–27.</t>
   </si>
   <si>
-    <t xml:space="preserve">DOI not checked (RePEc record matsoc v90 2017 p18-27)</t>
+    <t xml:space="preserve">https://doi.org/10.1016/j.mathsocsci.2016.09.003</t>
   </si>
   <si>
     <t xml:space="preserve">Breitmoser &amp; Valasek (2024). Strategic Communication in Committees with Expressive Payoffs</t>
@@ -1263,9 +1263,6 @@
     <t xml:space="preserve">https://doi.org/10.1007/s10058-022-00302-w</t>
   </si>
   <si>
-    <t xml:space="preserve">Published online May 2022; print issue 27(3), September 2023.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Caplin &amp; Nalebuff (1988). On 64%-Majority Rule</t>
   </si>
   <si>
@@ -1303,7 +1300,7 @@
     <t xml:space="preserve">Casella, A. (2005). Storable Votes. Games and Economic Behavior 51(2): 391–419.</t>
   </si>
   <si>
-    <t xml:space="preserve">DOI (probably 10.1016/j.geb.2004.09.009), from memory, not checked</t>
+    <t xml:space="preserve">https://doi.org/10.1016/j.geb.2004.09.009</t>
   </si>
   <si>
     <t xml:space="preserve">Condorcet (1785). Essai sur l'application de l'analyse à la probabilité des décisions rendues à la pluralité des voix</t>
@@ -1419,7 +1416,7 @@
     <t xml:space="preserve">Faliszewski, P. &amp; Procaccia, A. D. (2010). AI's War on Manipulation: Are We Winning?. AI Magazine 31(4): 53–64.</t>
   </si>
   <si>
-    <t xml:space="preserve">To verify: DOI (probably 10.1609/aimag.v31i4.2314, not confirmed)</t>
+    <t xml:space="preserve">https://doi.org/10.1609/aimag.v31i4.2314</t>
   </si>
   <si>
     <t xml:space="preserve">Felsenthal &amp; Machover (2008). The Majority Judgement Voting Procedure: A Critical Evaluation</t>
@@ -1480,9 +1477,6 @@
     <t xml:space="preserve">https://doi.org/10.1137/0133030</t>
   </si>
   <si>
-    <t xml:space="preserve">To verify: page range</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fishburn (1984). Probabilistic Social Choice Based on Simple Voting Comparisons</t>
   </si>
   <si>
@@ -1495,7 +1489,7 @@
     <t xml:space="preserve">Fishburn, P. C. (1984). Probabilistic Social Choice Based on Simple Voting Comparisons. Review of Economic Studies 51(4): 683–692.</t>
   </si>
   <si>
-    <t xml:space="preserve">To verify: DOI (probably 10.2307/2297786, not confirmed)</t>
+    <t xml:space="preserve">https://doi.org/10.2307/2297786</t>
   </si>
   <si>
     <t xml:space="preserve">Gehrlein &amp; Fishburn (1976). The Probability of the Paradox of Voting: A Computable Solution</t>
@@ -1514,7 +1508,7 @@
     <t xml:space="preserve">Gehrlein, W. V. &amp; Fishburn, P. C. (1976). The Probability of the Paradox of Voting: A Computable Solution. Journal of Economic Theory 13(1): 14–25.</t>
   </si>
   <si>
-    <t xml:space="preserve">To verify: DOI (probably 10.1016/0022-0531(76)90063-6, not confirmed)</t>
+    <t xml:space="preserve">https://doi.org/10.1016/0022-0531(76)90063-6</t>
   </si>
   <si>
     <t xml:space="preserve">Gehrlein (2006). Condorcet's Paradox</t>
@@ -1620,7 +1614,7 @@
     <t xml:space="preserve">GlyniaThumXefteris2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Glynia, N., Thum, M. &amp; Xefteris, D. (2026). Unanimity versus Majority: Proposing under Incomplete Information. Public Choice 208(3): 691–719.</t>
+    <t xml:space="preserve">Glynia, N., Thum, M. &amp; Xefteris, D. (2026). Unanimity versus Majority: Proposing under Incomplete Information. Public Choice 208(3–4): 691–719.</t>
   </si>
   <si>
     <t xml:space="preserve">https://doi.org/10.1007/s11127-026-01383-9</t>
@@ -1663,7 +1657,7 @@
     <t xml:space="preserve">Greenberg, J. (1979). Consistent Majority Rules over Compact Sets of Alternatives. Econometrica 47(3): 627–636.</t>
   </si>
   <si>
-    <t xml:space="preserve">To verify: DOI (probably 10.2307/1910410; JSTOR stable 1910410 confirmed)</t>
+    <t xml:space="preserve">https://doi.org/10.2307/1910410</t>
   </si>
   <si>
     <t xml:space="preserve">Guilbaud (1952). Les théories de l'intérêt général et le problème logique de l'agrégation</t>
@@ -1681,7 +1675,7 @@
     <t xml:space="preserve">Guilbaud, G.-T. (1952). Les théories de l'intérêt général et le problème logique de l'agrégation. Économie appliquée 5(4): 501–584.</t>
   </si>
   <si>
-    <t xml:space="preserve">To verify: page range (most French sources give 501–584; the English translation in JEHPS 2008 gives 501–551)</t>
+    <t xml:space="preserve">https://doi.org/10.3406/ecoap.1952.3831</t>
   </si>
   <si>
     <t xml:space="preserve">Harrington (1990). The Power of the Proposal Maker in a Model of Endogenous Agenda Formation</t>
@@ -1719,7 +1713,7 @@
     <t xml:space="preserve">§1 Introduction, §5 Aggregation, App. B Algorithms</t>
   </si>
   <si>
-    <t xml:space="preserve">Holliday, W. H. &amp; Pacuit, E. (2023). Split Cycle: A New Condorcet-Consistent Voting Method Independent of Clones and Immune to Spoilers. Public Choice 197(1): 1–62.</t>
+    <t xml:space="preserve">Holliday, W. H. &amp; Pacuit, E. (2023). Split Cycle: A New Condorcet-Consistent Voting Method Independent of Clones and Immune to Spoilers. Public Choice 197(1–2): 1–62.</t>
   </si>
   <si>
     <t xml:space="preserve">https://doi.org/10.1007/s11127-023-01042-3</t>
@@ -1756,9 +1750,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://doi.org/10.1007/978-1-349-14540-9_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Springer gives the volume subtitle as ``Economic Behaviour and Design''; original 1999 imprint Macmillan Press with the IEA. To verify: imprint wording on the title page.</t>
   </si>
   <si>
     <t xml:space="preserve">Ianovski &amp; Kondratev (2021). Computing the Proportional Veto Core</t>
@@ -1826,13 +1817,13 @@
     <t xml:space="preserve">Kemeny1959</t>
   </si>
   <si>
-    <t xml:space="preserve">Kemeny, J. G. (1959). Mathematics without Numbers. Daedalus 88(4): 577–591.</t>
+    <t xml:space="preserve">Kemeny, J. G. (1959). Mathematics without Numbers. Daedalus 88(4): 571–591.</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.jstor.org/stable/20026529</t>
   </si>
   <si>
-    <t xml:space="preserve">To verify: first page (577 in most sources; 575 and 571 also appear). No DOI found</t>
+    <t xml:space="preserve">No Crossref record. First page 571 as cited by Young and Levenglick (1978), Young (1988) and Bartholdi et al. (1989) in their Crossref reference lists; Kondratev and Nesterov (2020) give 577. JSTOR 20026529 not reachable to settle it</t>
   </si>
   <si>
     <t xml:space="preserve">Kondratev &amp; Ianovski (2024). Veto Core Consistent Preference Aggregation</t>
@@ -1851,10 +1842,7 @@
     <t xml:space="preserve">Kondratev, A. Y. &amp; Ianovski, E. (2024). Veto Core Consistent Preference Aggregation. Proceedings of the 23rd International Conference on Autonomous Agents and Multiagent Systems (AAMAS 2024): 1020–1028.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ifaamas.org/Proceedings/aamas2024/pdfs/p1020.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No registered DOI (ACM DL identifier 10.5555/3635637.3662957). No journal version found as of October 2026.</t>
+    <t xml:space="preserve">https://doi.org/10.65109/hmhq1427</t>
   </si>
   <si>
     <t xml:space="preserve">C27 Majority power versus veto power
@@ -1867,15 +1855,12 @@
     <t xml:space="preserve">KondratevNesterov2020</t>
   </si>
   <si>
-    <t xml:space="preserve">Kondratev, A. Y. &amp; Nesterov, A. S. (2020). Measuring Majority Power and Veto Power of Voting Rules. Public Choice 183: 187–210.</t>
+    <t xml:space="preserve">Kondratev, A. Y. &amp; Nesterov, A. S. (2020). Measuring Majority Power and Veto Power of Voting Rules. Public Choice 183(1–2): 187–210. Preprint arXiv:1811.06739.</t>
   </si>
   <si>
     <t xml:space="preserve">https://doi.org/10.1007/s11127-019-00697-1</t>
   </si>
   <si>
-    <t xml:space="preserve">To verify: issue number (RePEc codes it as issue 1) and the first name of the second author. Preprint: arXiv:1811.06739</t>
-  </si>
-  <si>
     <t xml:space="preserve">Krick (2017). The Myth of Effective Veto Power under the Rule of Consensus: Dynamics and Democratic Legitimacy of Collective Decision-Making by ``Tacit Consent''</t>
   </si>
   <si>
@@ -1892,9 +1877,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://doi.org/10.3917/neg.027.0109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Issue 2017/1 (no. 27).</t>
   </si>
   <si>
     <t xml:space="preserve">Laffond et al. (1993). The Bipartisan Set of a Tournament Game</t>
@@ -1913,7 +1895,7 @@
     <t xml:space="preserve">Laffond, G., Laslier, J.-F. &amp; Le Breton, M. (1993). The Bipartisan Set of a Tournament Game. Games and Economic Behavior 5(1): 182–201.</t>
   </si>
   <si>
-    <t xml:space="preserve">To verify: DOI (probably 10.1006/game.1993.1010, not confirmed)</t>
+    <t xml:space="preserve">https://doi.org/10.1006/game.1993.1010</t>
   </si>
   <si>
     <t xml:space="preserve">Laing &amp; Slotznick (1991). When Anyone Can Veto: A Laboratory Study of Committees Governed by Unanimous Rule</t>
@@ -2207,7 +2189,7 @@
     <t xml:space="preserve">Nakamura, K. (1979). The Vetoers in a Simple Game with Ordinal Preferences. International Journal of Game Theory 8(1): 55–61.</t>
   </si>
   <si>
-    <t xml:space="preserve">To verify: DOI (not found; 10.1007/BF01763051 is a candidate, not confirmed)</t>
+    <t xml:space="preserve">https://doi.org/10.1007/BF01763051</t>
   </si>
   <si>
     <t xml:space="preserve">Nunnari (2021). Dynamic Legislative Bargaining with Veto Power: Theory and Experiments</t>
@@ -2267,9 +2249,6 @@
     <t xml:space="preserve">https://www.jstor.org/stable/1815369</t>
   </si>
   <si>
-    <t xml:space="preserve">To verify: DOI (none found; JSTOR stable 1815369)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rae (1969). Decision-Rules and Individual Values in Constitutional Choice</t>
   </si>
   <si>
@@ -2286,7 +2265,7 @@
     <t xml:space="preserve">Rae, D. W. (1969). Decision-Rules and Individual Values in Constitutional Choice. American Political Science Review 63(1): 40–56.</t>
   </si>
   <si>
-    <t xml:space="preserve">To verify: DOI (probably 10.2307/1954283, not confirmed)</t>
+    <t xml:space="preserve">https://doi.org/10.2307/1954283</t>
   </si>
   <si>
     <t xml:space="preserve">Regenwetter et al. (2006). Behavioral Social Choice: Probabilistic Models, Statistical Inference, and Applications</t>
@@ -2301,7 +2280,7 @@
     <t xml:space="preserve">Regenwetter, M., Grofman, B., Marley, A. A. J. &amp; Tsetlin, I. (2006). Behavioral Social Choice: Probabilistic Models, Statistical Inference, and Applications. Cambridge University Press.</t>
   </si>
   <si>
-    <t xml:space="preserve">To verify: DOI (probably 10.1017/CBO9780511617577, not confirmed)</t>
+    <t xml:space="preserve">No DOI found in Crossref. The candidate DOI given earlier (10.1017/CBO9780511617577) belongs to another book. The book is confirmed by its reviews in Social Choice and Welfare 31(2), 2008 (doi 10.1007/s00355-008-0314-z) and Choice 44-3496, 2007</t>
   </si>
   <si>
     <t xml:space="preserve">Resnick (2014). On Consensus and Humming in the IETF</t>
@@ -2369,7 +2348,7 @@
     <t xml:space="preserve">Satterthwaite, M. A. (1975). Strategy-Proofness and Arrow's Conditions: Existence and Correspondence Theorems for Voting Procedures and Social Welfare Functions. Journal of Economic Theory 10(2): 187–217.</t>
   </si>
   <si>
-    <t xml:space="preserve">To verify: DOI (probably 10.1016/0022-0531(75)90050-2, not confirmed)</t>
+    <t xml:space="preserve">https://doi.org/10.1016/0022-0531(75)90050-2</t>
   </si>
   <si>
     <t xml:space="preserve">Schulze (2011). A New Monotonic, Clone-Independent, Reversal Symmetric, and Condorcet-Consistent Single-Winner Election Method</t>
@@ -2425,7 +2404,7 @@
     <t xml:space="preserve">Simpson, P. B. (1969). On Defining Areas of Voter Choice: Professor Tullock on Stable Voting. Quarterly Journal of Economics 83(3): 478–490.</t>
   </si>
   <si>
-    <t xml:space="preserve">To verify: DOI (probably 10.2307/1880533, not confirmed)</t>
+    <t xml:space="preserve">https://doi.org/10.2307/1880533</t>
   </si>
   <si>
     <t xml:space="preserve">Smith (1973). Aggregation of Preferences with Variable Electorate</t>
@@ -2538,7 +2517,7 @@
     <t xml:space="preserve">Tsebelis, G. (2002). Veto Players: How Political Institutions Work. Princeton University Press and Russell Sage Foundation.</t>
   </si>
   <si>
-    <t xml:space="preserve">Paperback ISBN 0-691-09989-8. The De Gruyter e-book edition has DOI 10.1515/9781400831456 (dated 2011 there).</t>
+    <t xml:space="preserve">https://doi.org/10.1515/9781400831456</t>
   </si>
   <si>
     <t xml:space="preserve">Young &amp; Levenglick (1978). A Consistent Extension of Condorcet's Election Principle</t>
@@ -2560,9 +2539,6 @@
     <t xml:space="preserve">https://doi.org/10.1137/0135023</t>
   </si>
   <si>
-    <t xml:space="preserve">To verify: issue number and page range</t>
-  </si>
-  <si>
     <t xml:space="preserve">Young (1974). An Axiomatization of Borda's Rule</t>
   </si>
   <si>
@@ -2639,7 +2615,7 @@
     <t xml:space="preserve">Balinski &amp; Laraki (2007)</t>
   </si>
   <si>
-    <t xml:space="preserve">Balinski &amp; Laraki (2010)</t>
+    <t xml:space="preserve">Balinski &amp; Laraki (2011)</t>
   </si>
   <si>
     <t xml:space="preserve">Barberà &amp; Coelho (2017)</t>
@@ -4585,7 +4561,9 @@
       <c r="F9" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="G9" s="8"/>
+      <c r="G9" s="9" t="s">
+        <v>250</v>
+      </c>
       <c r="H9" s="8"/>
       <c r="I9" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D9,Matrix!$B$3:$B$100,0),0),"x")</f>
@@ -4594,25 +4572,25 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="8" t="n">
@@ -4622,25 +4600,25 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8" t="n">
@@ -4650,25 +4628,25 @@
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8" t="n">
@@ -4678,25 +4656,25 @@
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8" t="n">
@@ -4706,29 +4684,27 @@
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="H14" s="8" t="s">
         <v>282</v>
       </c>
+      <c r="H14" s="8"/>
       <c r="I14" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D14,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>2</v>
@@ -4753,10 +4729,10 @@
       <c r="F15" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8" t="s">
+      <c r="G15" s="9" t="s">
         <v>288</v>
       </c>
+      <c r="H15" s="8"/>
       <c r="I15" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D15,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>1</v>
@@ -4944,7 +4920,7 @@
         <v>330</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>331</v>
@@ -4972,7 +4948,7 @@
         <v>336</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>337</v>
@@ -5005,10 +4981,10 @@
       <c r="F24" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8" t="s">
+      <c r="G24" s="9" t="s">
         <v>344</v>
       </c>
+      <c r="H24" s="8"/>
       <c r="I24" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D24,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>1</v>
@@ -5082,7 +5058,7 @@
         <v>360</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>361</v>
@@ -5090,9 +5066,7 @@
       <c r="G27" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="H27" s="8" t="s">
-        <v>363</v>
-      </c>
+      <c r="H27" s="8"/>
       <c r="I27" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D27,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>2</v>
@@ -5100,25 +5074,25 @@
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="C28" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="D28" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="E28" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="F28" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="G28" s="9" t="s">
         <v>369</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>370</v>
       </c>
       <c r="H28" s="8"/>
       <c r="I28" s="8" t="n">
@@ -5126,29 +5100,29 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
         <v>185</v>
       </c>
       <c r="B29" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="D29" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="E29" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="F29" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="G29" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8" t="s">
-        <v>376</v>
-      </c>
+      <c r="H29" s="8"/>
       <c r="I29" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D29,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>1</v>
@@ -5156,22 +5130,22 @@
     </row>
     <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="B30" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="C30" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="D30" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="E30" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="F30" s="8" t="s">
         <v>381</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>382</v>
       </c>
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
@@ -5182,25 +5156,25 @@
     </row>
     <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="B31" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="C31" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="D31" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="E31" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="F31" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="G31" s="9" t="s">
         <v>388</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>389</v>
       </c>
       <c r="H31" s="8"/>
       <c r="I31" s="8" t="n">
@@ -5210,25 +5184,25 @@
     </row>
     <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>222</v>
       </c>
       <c r="C32" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="D32" s="8" t="s">
         <v>391</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="E32" s="8" t="s">
         <v>392</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="F32" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="G32" s="9" t="s">
         <v>394</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>395</v>
       </c>
       <c r="H32" s="8"/>
       <c r="I32" s="8" t="n">
@@ -5238,25 +5212,25 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="B33" s="8" t="s">
         <v>396</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="C33" s="8" t="s">
         <v>397</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="D33" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="E33" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F33" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="E33" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="F33" s="8" t="s">
+      <c r="G33" s="9" t="s">
         <v>400</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>401</v>
       </c>
       <c r="H33" s="8"/>
       <c r="I33" s="8" t="n">
@@ -5266,57 +5240,57 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="B34" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="C34" s="8" t="s">
         <v>403</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="D34" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="E34" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="F34" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="G34" s="9" t="s">
         <v>407</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="H34" s="8" t="s">
         <v>408</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>409</v>
       </c>
       <c r="I34" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D34,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>284</v>
       </c>
       <c r="C35" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>411</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>412</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F35" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="G35" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8" t="s">
-        <v>414</v>
-      </c>
+      <c r="H35" s="8"/>
       <c r="I35" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D35,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>1</v>
@@ -5324,22 +5298,22 @@
     </row>
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="B36" s="8" t="s">
         <v>415</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="C36" s="8" t="s">
         <v>416</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="D36" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="E36" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F36" s="8" t="s">
         <v>418</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>419</v>
       </c>
       <c r="G36" s="8"/>
       <c r="H36" s="8"/>
@@ -5350,25 +5324,25 @@
     </row>
     <row r="37" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B37" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="C37" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="D37" s="8" t="s">
         <v>422</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="E37" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F37" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="E37" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="F37" s="8" t="s">
+      <c r="G37" s="9" t="s">
         <v>424</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>425</v>
       </c>
       <c r="H37" s="8"/>
       <c r="I37" s="8" t="n">
@@ -5378,29 +5352,27 @@
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="B38" s="8" t="s">
         <v>426</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="C38" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="D38" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="E38" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="F38" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="F38" s="8" t="s">
+      <c r="G38" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="G38" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>433</v>
-      </c>
+      <c r="H38" s="8"/>
       <c r="I38" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D38,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>2</v>
@@ -5408,27 +5380,27 @@
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>328</v>
       </c>
       <c r="C39" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F39" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="G39" s="9" t="s">
         <v>436</v>
       </c>
-      <c r="E39" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8" t="s">
-        <v>438</v>
-      </c>
+      <c r="H39" s="8"/>
       <c r="I39" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D39,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>1</v>
@@ -5436,27 +5408,27 @@
     </row>
     <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="C40" s="8" t="s">
         <v>439</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="D40" s="8" t="s">
         <v>440</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>441</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>442</v>
       </c>
       <c r="E40" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8" t="s">
-        <v>444</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="H40" s="8"/>
       <c r="I40" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D40,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>2</v>
@@ -5464,25 +5436,25 @@
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="D41" s="8" t="s">
         <v>445</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>440</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>447</v>
       </c>
       <c r="E41" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="H41" s="8"/>
       <c r="I41" s="8" t="n">
@@ -5492,25 +5464,25 @@
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>297</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E42" s="8" t="s">
         <v>348</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="H42" s="8"/>
       <c r="I42" s="8" t="n">
@@ -5520,25 +5492,25 @@
     </row>
     <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>455</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="D43" s="8" t="s">
         <v>456</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>457</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>458</v>
       </c>
       <c r="E43" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="H43" s="8"/>
       <c r="I43" s="8" t="n">
@@ -5548,25 +5520,25 @@
     </row>
     <row r="44" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C44" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="D44" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="E44" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="F44" s="8" t="s">
         <v>463</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="G44" s="9" t="s">
         <v>464</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>466</v>
       </c>
       <c r="H44" s="8"/>
       <c r="I44" s="8" t="n">
@@ -5576,25 +5548,25 @@
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="C45" s="8" t="s">
         <v>467</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="D45" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="E45" s="8" t="s">
         <v>469</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="F45" s="8" t="s">
         <v>470</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="G45" s="9" t="s">
         <v>471</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>472</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>473</v>
       </c>
       <c r="H45" s="8"/>
       <c r="I45" s="8" t="n">
@@ -5604,25 +5576,25 @@
     </row>
     <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="C46" s="8" t="s">
         <v>474</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="D46" s="8" t="s">
         <v>475</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>476</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>477</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="H46" s="8"/>
       <c r="I46" s="8" t="n">
@@ -5632,25 +5604,25 @@
     </row>
     <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="C47" s="8" t="s">
         <v>480</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="D47" s="8" t="s">
         <v>481</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="E47" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="F47" s="8" t="s">
         <v>483</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="G47" s="9" t="s">
         <v>484</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>485</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>486</v>
       </c>
       <c r="H47" s="8"/>
       <c r="I47" s="8" t="n">
@@ -5660,55 +5632,55 @@
     </row>
     <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="C48" s="8" t="s">
         <v>487</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="D48" s="8" t="s">
         <v>488</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="E48" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="F48" s="8" t="s">
         <v>489</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="G48" s="9" t="s">
         <v>490</v>
       </c>
-      <c r="E48" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>491</v>
-      </c>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8" t="s">
-        <v>492</v>
-      </c>
+      <c r="H48" s="8"/>
       <c r="I48" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D48,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="C49" s="8" t="s">
         <v>493</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="D49" s="8" t="s">
         <v>494</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>495</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>496</v>
       </c>
       <c r="E49" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>497</v>
-      </c>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8" t="s">
-        <v>498</v>
-      </c>
+        <v>495</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="H49" s="8"/>
       <c r="I49" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D49,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>1</v>
@@ -5716,25 +5688,25 @@
     </row>
     <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="C50" s="8" t="s">
         <v>499</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="D50" s="8" t="s">
         <v>500</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>501</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>502</v>
       </c>
       <c r="E50" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="H50" s="8"/>
       <c r="I50" s="8" t="n">
@@ -5744,25 +5716,25 @@
     </row>
     <row r="51" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="C51" s="8" t="s">
         <v>505</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="D51" s="8" t="s">
         <v>506</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="E51" s="8" t="s">
         <v>507</v>
       </c>
-      <c r="D51" s="8" t="s">
+      <c r="F51" s="8" t="s">
         <v>508</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="G51" s="9" t="s">
         <v>509</v>
-      </c>
-      <c r="F51" s="8" t="s">
-        <v>510</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>511</v>
       </c>
       <c r="H51" s="8"/>
       <c r="I51" s="8" t="n">
@@ -5772,25 +5744,25 @@
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="C52" s="8" t="s">
         <v>512</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="D52" s="8" t="s">
         <v>513</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="E52" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F52" s="8" t="s">
         <v>514</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="G52" s="9" t="s">
         <v>515</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>516</v>
-      </c>
-      <c r="G52" s="9" t="s">
-        <v>517</v>
       </c>
       <c r="H52" s="8"/>
       <c r="I52" s="8" t="n">
@@ -5798,31 +5770,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>321</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E53" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="H53" s="8" t="s">
-        <v>523</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="H53" s="8"/>
       <c r="I53" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D53,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>1</v>
@@ -5830,25 +5800,25 @@
     </row>
     <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="D54" s="8" t="s">
         <v>524</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="E54" s="8" t="s">
         <v>525</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="F54" s="8" t="s">
         <v>526</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="G54" s="9" t="s">
         <v>527</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>528</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>529</v>
-      </c>
-      <c r="G54" s="9" t="s">
-        <v>530</v>
       </c>
       <c r="H54" s="8"/>
       <c r="I54" s="8" t="n">
@@ -5858,25 +5828,25 @@
     </row>
     <row r="55" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>529</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>530</v>
+      </c>
+      <c r="D55" s="8" t="s">
         <v>531</v>
-      </c>
-      <c r="B55" s="8" t="s">
-        <v>532</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>533</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>534</v>
       </c>
       <c r="E55" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="H55" s="8"/>
       <c r="I55" s="8" t="n">
@@ -5889,22 +5859,22 @@
         <v>190</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E56" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="H56" s="8"/>
       <c r="I56" s="8" t="n">
@@ -5912,91 +5882,87 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F57" s="8" t="s">
         <v>542</v>
       </c>
-      <c r="B57" s="8" t="s">
-        <v>397</v>
-      </c>
-      <c r="C57" s="8" t="s">
+      <c r="G57" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="H57" s="8" t="s">
         <v>544</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>545</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>546</v>
-      </c>
-      <c r="H57" s="8" t="s">
-        <v>547</v>
       </c>
       <c r="I57" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D57,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>546</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="D58" s="8" t="s">
         <v>548</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>549</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>550</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>551</v>
       </c>
       <c r="E58" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>553</v>
-      </c>
-      <c r="H58" s="8" t="s">
-        <v>554</v>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="H58" s="8"/>
       <c r="I58" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D58,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
         <v>151</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="E59" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>559</v>
-      </c>
-      <c r="H59" s="8" t="s">
-        <v>560</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="H59" s="8"/>
       <c r="I59" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D59,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>2</v>
@@ -6004,57 +5970,55 @@
     </row>
     <row r="60" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="E60" s="8" t="s">
         <v>348</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>566</v>
-      </c>
-      <c r="H60" s="8" t="s">
-        <v>567</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="H60" s="8"/>
       <c r="I60" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D60,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>572</v>
-      </c>
-      <c r="G61" s="8"/>
-      <c r="H61" s="8" t="s">
-        <v>573</v>
-      </c>
+        <v>566</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="H61" s="8"/>
       <c r="I61" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D61,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>2</v>
@@ -6062,25 +6026,25 @@
     </row>
     <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="B62" s="8" t="s">
         <v>203</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="E62" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="H62" s="8"/>
       <c r="I62" s="8" t="n">
@@ -6090,25 +6054,25 @@
     </row>
     <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="B63" s="8" t="s">
         <v>240</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="H63" s="8"/>
       <c r="I63" s="8" t="n">
@@ -6118,25 +6082,25 @@
     </row>
     <row r="64" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="H64" s="8"/>
       <c r="I64" s="8" t="n">
@@ -6146,25 +6110,25 @@
     </row>
     <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="E65" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="H65" s="8"/>
       <c r="I65" s="8" t="n">
@@ -6174,25 +6138,25 @@
     </row>
     <row r="66" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>590</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>591</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>592</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>593</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>594</v>
+      </c>
+      <c r="G66" s="9" t="s">
         <v>595</v>
-      </c>
-      <c r="B66" s="8" t="s">
-        <v>596</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>597</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>598</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>599</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>600</v>
-      </c>
-      <c r="G66" s="9" t="s">
-        <v>601</v>
       </c>
       <c r="H66" s="8"/>
       <c r="I66" s="8" t="n">
@@ -6202,25 +6166,25 @@
     </row>
     <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="H67" s="8"/>
       <c r="I67" s="8" t="n">
@@ -6230,25 +6194,25 @@
     </row>
     <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="E68" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="H68" s="8"/>
       <c r="I68" s="8" t="n">
@@ -6258,25 +6222,25 @@
     </row>
     <row r="69" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>612</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="G69" s="9" t="s">
         <v>614</v>
-      </c>
-      <c r="B69" s="8" t="s">
-        <v>615</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>616</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>617</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>618</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>619</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>620</v>
       </c>
       <c r="H69" s="8"/>
       <c r="I69" s="8" t="n">
@@ -6286,25 +6250,25 @@
     </row>
     <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="G70" s="9" t="s">
         <v>621</v>
-      </c>
-      <c r="B70" s="8" t="s">
-        <v>622</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>623</v>
-      </c>
-      <c r="D70" s="8" t="s">
-        <v>624</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>625</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>626</v>
-      </c>
-      <c r="G70" s="9" t="s">
-        <v>627</v>
       </c>
       <c r="H70" s="8"/>
       <c r="I70" s="8" t="n">
@@ -6314,25 +6278,25 @@
     </row>
     <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="B71" s="8" t="s">
         <v>309</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="H71" s="8"/>
       <c r="I71" s="8" t="n">
@@ -6342,25 +6306,25 @@
     </row>
     <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="H72" s="8"/>
       <c r="I72" s="8" t="n">
@@ -6370,25 +6334,25 @@
     </row>
     <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="H73" s="8"/>
       <c r="I73" s="8" t="n">
@@ -6398,22 +6362,22 @@
     </row>
     <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="E74" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
@@ -6424,25 +6388,25 @@
     </row>
     <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="H75" s="8"/>
       <c r="I75" s="8" t="n">
@@ -6452,25 +6416,25 @@
     </row>
     <row r="76" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="E76" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="H76" s="8"/>
       <c r="I76" s="8" t="n">
@@ -6480,27 +6444,27 @@
     </row>
     <row r="77" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="E77" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>667</v>
-      </c>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8" t="s">
-        <v>668</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="H77" s="8"/>
       <c r="I77" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D77,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>2</v>
@@ -6508,25 +6472,25 @@
     </row>
     <row r="78" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>664</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>667</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>668</v>
+      </c>
+      <c r="G78" s="9" t="s">
         <v>669</v>
-      </c>
-      <c r="B78" s="8" t="s">
-        <v>670</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>671</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>672</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>673</v>
-      </c>
-      <c r="F78" s="8" t="s">
-        <v>674</v>
-      </c>
-      <c r="G78" s="9" t="s">
-        <v>675</v>
       </c>
       <c r="H78" s="8"/>
       <c r="I78" s="8" t="n">
@@ -6536,25 +6500,25 @@
     </row>
     <row r="79" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>303</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="E79" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="H79" s="8"/>
       <c r="I79" s="8" t="n">
@@ -6564,29 +6528,27 @@
     </row>
     <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="E80" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>686</v>
-      </c>
-      <c r="H80" s="8" t="s">
-        <v>687</v>
-      </c>
+        <v>680</v>
+      </c>
+      <c r="H80" s="8"/>
       <c r="I80" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D80,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>2</v>
@@ -6594,54 +6556,54 @@
     </row>
     <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="E81" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>692</v>
-      </c>
-      <c r="G81" s="8"/>
-      <c r="H81" s="8" t="s">
-        <v>693</v>
-      </c>
+        <v>685</v>
+      </c>
+      <c r="G81" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="H81" s="8"/>
       <c r="I81" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D81,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="G82" s="8"/>
       <c r="H82" s="8" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="I82" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D82,Matrix!$B$3:$B$100,0),0),"x")</f>
@@ -6650,25 +6612,25 @@
     </row>
     <row r="83" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="E83" s="8" t="s">
         <v>348</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="H83" s="8"/>
       <c r="I83" s="8" t="n">
@@ -6678,25 +6640,25 @@
     </row>
     <row r="84" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="H84" s="8"/>
       <c r="I84" s="8" t="n">
@@ -6706,25 +6668,25 @@
     </row>
     <row r="85" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="E85" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="H85" s="8"/>
       <c r="I85" s="8" t="n">
@@ -6734,27 +6696,27 @@
     </row>
     <row r="86" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>719</v>
-      </c>
-      <c r="G86" s="8"/>
-      <c r="H86" s="8" t="s">
-        <v>720</v>
-      </c>
+        <v>712</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>713</v>
+      </c>
+      <c r="H86" s="8"/>
       <c r="I86" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D86,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>2</v>
@@ -6762,25 +6724,25 @@
     </row>
     <row r="87" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="H87" s="8"/>
       <c r="I87" s="8" t="n">
@@ -6790,25 +6752,25 @@
     </row>
     <row r="88" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="B88" s="8" t="s">
         <v>321</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="H88" s="8"/>
       <c r="I88" s="8" t="n">
@@ -6818,27 +6780,27 @@
     </row>
     <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>737</v>
-      </c>
-      <c r="G89" s="8"/>
-      <c r="H89" s="8" t="s">
-        <v>738</v>
-      </c>
+        <v>730</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>731</v>
+      </c>
+      <c r="H89" s="8"/>
       <c r="I89" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D89,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>1</v>
@@ -6846,25 +6808,25 @@
     </row>
     <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="G90" s="9" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="H90" s="8"/>
       <c r="I90" s="8" t="n">
@@ -6874,25 +6836,25 @@
     </row>
     <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="H91" s="8"/>
       <c r="I91" s="8" t="n">
@@ -6902,29 +6864,27 @@
     </row>
     <row r="92" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="G92" s="9" t="s">
-        <v>757</v>
-      </c>
-      <c r="H92" s="8" t="s">
-        <v>282</v>
-      </c>
+        <v>750</v>
+      </c>
+      <c r="H92" s="8"/>
       <c r="I92" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D92,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>3</v>
@@ -6932,22 +6892,22 @@
     </row>
     <row r="93" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="E93" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="G93" s="8"/>
       <c r="H93" s="8"/>
@@ -6958,25 +6918,25 @@
     </row>
     <row r="94" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="E94" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="H94" s="8"/>
       <c r="I94" s="8" t="n">
@@ -6984,29 +6944,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B95" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="D95" s="8" t="s">
         <v>764</v>
       </c>
-      <c r="C95" s="8" t="s">
-        <v>770</v>
-      </c>
-      <c r="D95" s="8" t="s">
-        <v>771</v>
-      </c>
       <c r="E95" s="8" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>773</v>
-      </c>
-      <c r="G95" s="8"/>
-      <c r="H95" s="8" t="s">
-        <v>774</v>
-      </c>
+        <v>766</v>
+      </c>
+      <c r="G95" s="9" t="s">
+        <v>767</v>
+      </c>
+      <c r="H95" s="8"/>
       <c r="I95" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D95,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>1</v>
@@ -7014,29 +6974,27 @@
     </row>
     <row r="96" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="G96" s="9" t="s">
-        <v>780</v>
-      </c>
-      <c r="H96" s="8" t="s">
-        <v>781</v>
-      </c>
+        <v>773</v>
+      </c>
+      <c r="H96" s="8"/>
       <c r="I96" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D96,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>2</v>
@@ -7044,25 +7002,25 @@
     </row>
     <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="s">
-        <v>782</v>
+        <v>774</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="E97" s="8" t="s">
         <v>243</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>786</v>
+        <v>778</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
       <c r="H97" s="8"/>
       <c r="I97" s="8" t="n">
@@ -7072,25 +7030,25 @@
     </row>
     <row r="98" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="s">
-        <v>788</v>
+        <v>780</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>789</v>
+        <v>781</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="G98" s="9" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="H98" s="8"/>
       <c r="I98" s="8" t="n">
@@ -7100,29 +7058,27 @@
     </row>
     <row r="99" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>794</v>
+        <v>786</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>798</v>
-      </c>
-      <c r="H99" s="8" t="s">
-        <v>282</v>
-      </c>
+        <v>790</v>
+      </c>
+      <c r="H99" s="8"/>
       <c r="I99" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D99,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>2</v>
@@ -7137,76 +7093,91 @@
     <hyperlink ref="G5" r:id="rId4" display="https://doi.org/10.1016/j.geb.2016.04.010"/>
     <hyperlink ref="G6" r:id="rId5" display="https://doi.org/10.1093/restud/rdv009"/>
     <hyperlink ref="G8" r:id="rId6" display="https://doi.org/10.1073/pnas.0702634104"/>
-    <hyperlink ref="G10" r:id="rId7" display="https://doi.org/10.1016/j.geb.2015.10.005"/>
-    <hyperlink ref="G11" r:id="rId8" display="https://doi.org/10.1111/1756-2171.12401"/>
-    <hyperlink ref="G12" r:id="rId9" display="https://doi.org/10.3982/TE2118"/>
-    <hyperlink ref="G13" r:id="rId10" display="https://doi.org/10.2307/1961664"/>
-    <hyperlink ref="G14" r:id="rId11" display="https://doi.org/10.1007/BF00303169"/>
-    <hyperlink ref="G16" r:id="rId12" display="https://doi.org/10.1086/256633"/>
-    <hyperlink ref="G17" r:id="rId13" display="https://doi.org/10.1016/j.jet.2014.11.008"/>
-    <hyperlink ref="G18" r:id="rId14" display="https://doi.org/10.1016/j.geb.2016.12.001"/>
-    <hyperlink ref="G19" r:id="rId15" display="https://doi.org/10.1086/695477"/>
-    <hyperlink ref="G20" r:id="rId16" display="https://doi.org/10.2307/1955105"/>
-    <hyperlink ref="G21" r:id="rId17" display="https://doi.org/10.1023/A:1011252808608"/>
-    <hyperlink ref="G22" r:id="rId18" display="https://doi.org/10.3982/ECTA13337"/>
-    <hyperlink ref="G23" r:id="rId19" display="https://doi.org/10.1017/CBO9781107446984"/>
-    <hyperlink ref="G25" r:id="rId20" display="https://doi.org/10.1111/1756-2171.12457"/>
-    <hyperlink ref="G27" r:id="rId21" display="https://doi.org/10.1007/s10058-022-00302-w"/>
-    <hyperlink ref="G28" r:id="rId22" display="https://doi.org/10.2307/1912699"/>
-    <hyperlink ref="G31" r:id="rId23" display="https://www.debian.org/devel/constitution"/>
-    <hyperlink ref="G32" r:id="rId24" display="https://doi.org/10.1086/686747"/>
-    <hyperlink ref="G33" r:id="rId25" display="https://doi.org/10.1007/s00355-015-0892-5"/>
-    <hyperlink ref="G34" r:id="rId26" display="https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX:12016M/TXT"/>
-    <hyperlink ref="G37" r:id="rId27" display="https://doi.org/10.1007/978-3-642-20441-8_3"/>
-    <hyperlink ref="G38" r:id="rId28" display="https://doi.org/10.1137/0133030"/>
-    <hyperlink ref="G41" r:id="rId29" display="https://doi.org/10.1007/3-540-33799-7"/>
-    <hyperlink ref="G42" r:id="rId30" display="https://arxiv.org/abs/2410.20476"/>
-    <hyperlink ref="G43" r:id="rId31" display="https://doi.org/10.1007/s00355-023-01505-y"/>
-    <hyperlink ref="G44" r:id="rId32" display="https://arxiv.org/abs/2506.05998"/>
-    <hyperlink ref="G45" r:id="rId33" display="https://doi.org/10.2307/1914083"/>
-    <hyperlink ref="G46" r:id="rId34" display="https://doi.org/10.1007/s11127-026-01383-9"/>
-    <hyperlink ref="G47" r:id="rId35" display="https://doi.org/10.1007/s00355-015-0909-0"/>
-    <hyperlink ref="G50" r:id="rId36" display="https://doi.org/10.1007/BF00125914"/>
-    <hyperlink ref="G51" r:id="rId37" display="https://doi.org/10.1007/s11127-023-01042-3"/>
-    <hyperlink ref="G52" r:id="rId38" display="https://doi.org/10.1007/s10602-022-09383-9"/>
-    <hyperlink ref="G53" r:id="rId39" display="https://doi.org/10.1007/978-1-349-14540-9_4"/>
-    <hyperlink ref="G54" r:id="rId40" display="https://doi.org/10.1609/aaai.v35i6.16691"/>
-    <hyperlink ref="G55" r:id="rId41" display="https://doi.org/10.1007/s10683-010-9234-8"/>
-    <hyperlink ref="G56" r:id="rId42" display="https://doi.org/10.1257/aer.20201817"/>
-    <hyperlink ref="G57" r:id="rId43" display="https://www.jstor.org/stable/20026529"/>
-    <hyperlink ref="G58" r:id="rId44" display="https://www.ifaamas.org/Proceedings/aamas2024/pdfs/p1020.pdf"/>
-    <hyperlink ref="G59" r:id="rId45" display="https://doi.org/10.1007/s11127-019-00697-1"/>
-    <hyperlink ref="G60" r:id="rId46" display="https://doi.org/10.3917/neg.027.0109"/>
-    <hyperlink ref="G62" r:id="rId47" display="https://doi.org/10.1002/bs.3830360303"/>
-    <hyperlink ref="G63" r:id="rId48" display="https://doi.org/10.1007/978-3-642-02839-7"/>
-    <hyperlink ref="G64" r:id="rId49" display="https://doi.org/10.1007/978-3-642-20441-8_13"/>
-    <hyperlink ref="G65" r:id="rId50" display="https://doi.org/10.1016/j.jet.2021.105261"/>
-    <hyperlink ref="G66" r:id="rId51" display="https://doi.org/10.1093/biomet/44.1-2.114"/>
-    <hyperlink ref="G67" r:id="rId52" display="https://doi.org/10.1007/978-3-642-41575-3_20"/>
-    <hyperlink ref="G68" r:id="rId53" display="https://doi.org/10.2307/1907651"/>
-    <hyperlink ref="G69" r:id="rId54" display="https://doi.org/10.1016/0022-0531(76)90040-5"/>
-    <hyperlink ref="G70" r:id="rId55" display="https://doi.org/10.2307/2110786"/>
-    <hyperlink ref="G71" r:id="rId56" display="https://doi.org/10.1257/mic.20230208"/>
-    <hyperlink ref="G72" r:id="rId57" display="https://doi.org/10.2307/2297154"/>
-    <hyperlink ref="G73" r:id="rId58" display="https://doi.org/10.2307/1912535"/>
-    <hyperlink ref="G75" r:id="rId59" display="https://doi.org/10.1016/0022-0531(88)90253-0"/>
-    <hyperlink ref="G76" r:id="rId60" display="https://doi.org/10.1016/0047-2727(78)90005-1"/>
-    <hyperlink ref="G78" r:id="rId61" display="https://doi.org/10.1016/j.geb.2020.11.006"/>
-    <hyperlink ref="G79" r:id="rId62" display="https://doi.org/10.1016/j.geb.2025.07.010"/>
-    <hyperlink ref="G80" r:id="rId63" display="https://www.jstor.org/stable/1815369"/>
-    <hyperlink ref="G83" r:id="rId64" display="https://doi.org/10.17487/RFC7282"/>
-    <hyperlink ref="G84" r:id="rId65" display="https://doi.org/10.1007/s10602-008-9037-5"/>
-    <hyperlink ref="G85" r:id="rId66" display="https://doi.org/10.1007/BF03187594"/>
-    <hyperlink ref="G87" r:id="rId67" display="https://doi.org/10.1007/s00355-010-0475-4"/>
-    <hyperlink ref="G88" r:id="rId68" display="https://doi.org/10.1007/s003550050164"/>
-    <hyperlink ref="G90" r:id="rId69" display="https://doi.org/10.2307/1914033"/>
-    <hyperlink ref="G91" r:id="rId70" display="https://doi.org/10.1007/978-3-642-20441-8_9"/>
-    <hyperlink ref="G92" r:id="rId71" display="https://doi.org/10.1007/BF00433944"/>
-    <hyperlink ref="G94" r:id="rId72" display="https://doi.org/10.1017/S0007123400007225"/>
-    <hyperlink ref="G96" r:id="rId73" display="https://doi.org/10.1137/0135023"/>
-    <hyperlink ref="G97" r:id="rId74" display="https://doi.org/10.1016/0022-0531(74)90073-8"/>
-    <hyperlink ref="G98" r:id="rId75" display="https://doi.org/10.2307/1961757"/>
-    <hyperlink ref="G99" r:id="rId76" display="https://doi.org/10.1007/BF00303170"/>
+    <hyperlink ref="G9" r:id="rId7" display="https://doi.org/10.7551/mitpress/9780262015134.001.0001"/>
+    <hyperlink ref="G10" r:id="rId8" display="https://doi.org/10.1016/j.geb.2015.10.005"/>
+    <hyperlink ref="G11" r:id="rId9" display="https://doi.org/10.1111/1756-2171.12401"/>
+    <hyperlink ref="G12" r:id="rId10" display="https://doi.org/10.3982/TE2118"/>
+    <hyperlink ref="G13" r:id="rId11" display="https://doi.org/10.2307/1961664"/>
+    <hyperlink ref="G14" r:id="rId12" display="https://doi.org/10.1007/BF00303169"/>
+    <hyperlink ref="G15" r:id="rId13" display="https://doi.org/10.1007/BF00295861"/>
+    <hyperlink ref="G16" r:id="rId14" display="https://doi.org/10.1086/256633"/>
+    <hyperlink ref="G17" r:id="rId15" display="https://doi.org/10.1016/j.jet.2014.11.008"/>
+    <hyperlink ref="G18" r:id="rId16" display="https://doi.org/10.1016/j.geb.2016.12.001"/>
+    <hyperlink ref="G19" r:id="rId17" display="https://doi.org/10.1086/695477"/>
+    <hyperlink ref="G20" r:id="rId18" display="https://doi.org/10.2307/1955105"/>
+    <hyperlink ref="G21" r:id="rId19" display="https://doi.org/10.1023/A:1011252808608"/>
+    <hyperlink ref="G22" r:id="rId20" display="https://doi.org/10.3982/ECTA13337"/>
+    <hyperlink ref="G23" r:id="rId21" display="https://doi.org/10.1017/CBO9781107446984"/>
+    <hyperlink ref="G24" r:id="rId22" display="https://doi.org/10.1016/j.mathsocsci.2016.09.003"/>
+    <hyperlink ref="G25" r:id="rId23" display="https://doi.org/10.1111/1756-2171.12457"/>
+    <hyperlink ref="G27" r:id="rId24" display="https://doi.org/10.1007/s10058-022-00302-w"/>
+    <hyperlink ref="G28" r:id="rId25" display="https://doi.org/10.2307/1912699"/>
+    <hyperlink ref="G29" r:id="rId26" display="https://doi.org/10.1016/j.geb.2004.09.009"/>
+    <hyperlink ref="G31" r:id="rId27" display="https://www.debian.org/devel/constitution"/>
+    <hyperlink ref="G32" r:id="rId28" display="https://doi.org/10.1086/686747"/>
+    <hyperlink ref="G33" r:id="rId29" display="https://doi.org/10.1007/s00355-015-0892-5"/>
+    <hyperlink ref="G34" r:id="rId30" display="https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX:12016M/TXT"/>
+    <hyperlink ref="G35" r:id="rId31" display="https://doi.org/10.1609/aimag.v31i4.2314"/>
+    <hyperlink ref="G37" r:id="rId32" display="https://doi.org/10.1007/978-3-642-20441-8_3"/>
+    <hyperlink ref="G38" r:id="rId33" display="https://doi.org/10.1137/0133030"/>
+    <hyperlink ref="G39" r:id="rId34" display="https://doi.org/10.2307/2297786"/>
+    <hyperlink ref="G40" r:id="rId35" display="https://doi.org/10.1016/0022-0531(76)90063-6"/>
+    <hyperlink ref="G41" r:id="rId36" display="https://doi.org/10.1007/3-540-33799-7"/>
+    <hyperlink ref="G42" r:id="rId37" display="https://arxiv.org/abs/2410.20476"/>
+    <hyperlink ref="G43" r:id="rId38" display="https://doi.org/10.1007/s00355-023-01505-y"/>
+    <hyperlink ref="G44" r:id="rId39" display="https://arxiv.org/abs/2506.05998"/>
+    <hyperlink ref="G45" r:id="rId40" display="https://doi.org/10.2307/1914083"/>
+    <hyperlink ref="G46" r:id="rId41" display="https://doi.org/10.1007/s11127-026-01383-9"/>
+    <hyperlink ref="G47" r:id="rId42" display="https://doi.org/10.1007/s00355-015-0909-0"/>
+    <hyperlink ref="G48" r:id="rId43" display="https://doi.org/10.2307/1910410"/>
+    <hyperlink ref="G49" r:id="rId44" display="https://doi.org/10.3406/ecoap.1952.3831"/>
+    <hyperlink ref="G50" r:id="rId45" display="https://doi.org/10.1007/BF00125914"/>
+    <hyperlink ref="G51" r:id="rId46" display="https://doi.org/10.1007/s11127-023-01042-3"/>
+    <hyperlink ref="G52" r:id="rId47" display="https://doi.org/10.1007/s10602-022-09383-9"/>
+    <hyperlink ref="G53" r:id="rId48" display="https://doi.org/10.1007/978-1-349-14540-9_4"/>
+    <hyperlink ref="G54" r:id="rId49" display="https://doi.org/10.1609/aaai.v35i6.16691"/>
+    <hyperlink ref="G55" r:id="rId50" display="https://doi.org/10.1007/s10683-010-9234-8"/>
+    <hyperlink ref="G56" r:id="rId51" display="https://doi.org/10.1257/aer.20201817"/>
+    <hyperlink ref="G57" r:id="rId52" display="https://www.jstor.org/stable/20026529"/>
+    <hyperlink ref="G58" r:id="rId53" display="https://doi.org/10.65109/hmhq1427"/>
+    <hyperlink ref="G59" r:id="rId54" display="https://doi.org/10.1007/s11127-019-00697-1"/>
+    <hyperlink ref="G60" r:id="rId55" display="https://doi.org/10.3917/neg.027.0109"/>
+    <hyperlink ref="G61" r:id="rId56" display="https://doi.org/10.1006/game.1993.1010"/>
+    <hyperlink ref="G62" r:id="rId57" display="https://doi.org/10.1002/bs.3830360303"/>
+    <hyperlink ref="G63" r:id="rId58" display="https://doi.org/10.1007/978-3-642-02839-7"/>
+    <hyperlink ref="G64" r:id="rId59" display="https://doi.org/10.1007/978-3-642-20441-8_13"/>
+    <hyperlink ref="G65" r:id="rId60" display="https://doi.org/10.1016/j.jet.2021.105261"/>
+    <hyperlink ref="G66" r:id="rId61" display="https://doi.org/10.1093/biomet/44.1-2.114"/>
+    <hyperlink ref="G67" r:id="rId62" display="https://doi.org/10.1007/978-3-642-41575-3_20"/>
+    <hyperlink ref="G68" r:id="rId63" display="https://doi.org/10.2307/1907651"/>
+    <hyperlink ref="G69" r:id="rId64" display="https://doi.org/10.1016/0022-0531(76)90040-5"/>
+    <hyperlink ref="G70" r:id="rId65" display="https://doi.org/10.2307/2110786"/>
+    <hyperlink ref="G71" r:id="rId66" display="https://doi.org/10.1257/mic.20230208"/>
+    <hyperlink ref="G72" r:id="rId67" display="https://doi.org/10.2307/2297154"/>
+    <hyperlink ref="G73" r:id="rId68" display="https://doi.org/10.2307/1912535"/>
+    <hyperlink ref="G75" r:id="rId69" display="https://doi.org/10.1016/0022-0531(88)90253-0"/>
+    <hyperlink ref="G76" r:id="rId70" display="https://doi.org/10.1016/0047-2727(78)90005-1"/>
+    <hyperlink ref="G77" r:id="rId71" display="https://doi.org/10.1007/BF01763051"/>
+    <hyperlink ref="G78" r:id="rId72" display="https://doi.org/10.1016/j.geb.2020.11.006"/>
+    <hyperlink ref="G79" r:id="rId73" display="https://doi.org/10.1016/j.geb.2025.07.010"/>
+    <hyperlink ref="G80" r:id="rId74" display="https://www.jstor.org/stable/1815369"/>
+    <hyperlink ref="G81" r:id="rId75" display="https://doi.org/10.2307/1954283"/>
+    <hyperlink ref="G83" r:id="rId76" display="https://doi.org/10.17487/RFC7282"/>
+    <hyperlink ref="G84" r:id="rId77" display="https://doi.org/10.1007/s10602-008-9037-5"/>
+    <hyperlink ref="G85" r:id="rId78" display="https://doi.org/10.1007/BF03187594"/>
+    <hyperlink ref="G86" r:id="rId79" display="https://doi.org/10.1016/0022-0531(75)90050-2"/>
+    <hyperlink ref="G87" r:id="rId80" display="https://doi.org/10.1007/s00355-010-0475-4"/>
+    <hyperlink ref="G88" r:id="rId81" display="https://doi.org/10.1007/s003550050164"/>
+    <hyperlink ref="G89" r:id="rId82" display="https://doi.org/10.2307/1880533"/>
+    <hyperlink ref="G90" r:id="rId83" display="https://doi.org/10.2307/1914033"/>
+    <hyperlink ref="G91" r:id="rId84" display="https://doi.org/10.1007/978-3-642-20441-8_9"/>
+    <hyperlink ref="G92" r:id="rId85" display="https://doi.org/10.1007/BF00433944"/>
+    <hyperlink ref="G94" r:id="rId86" display="https://doi.org/10.1017/S0007123400007225"/>
+    <hyperlink ref="G95" r:id="rId87" display="https://doi.org/10.1515/9781400831456"/>
+    <hyperlink ref="G96" r:id="rId88" display="https://doi.org/10.1137/0135023"/>
+    <hyperlink ref="G97" r:id="rId89" display="https://doi.org/10.1016/0022-0531(74)90073-8"/>
+    <hyperlink ref="G98" r:id="rId90" display="https://doi.org/10.2307/1961757"/>
+    <hyperlink ref="G99" r:id="rId91" display="https://doi.org/10.1007/BF00303170"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7215,7 +7186,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId77"/>
+  <drawing r:id="rId92"/>
 </worksheet>
 </file>
 
@@ -7463,7 +7434,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>205</v>
@@ -7488,7 +7459,7 @@
       <c r="T3" s="13"/>
       <c r="U3" s="13"/>
       <c r="V3" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
@@ -7503,7 +7474,7 @@
       <c r="AG3" s="13"/>
       <c r="AH3" s="13"/>
       <c r="AI3" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AJ3" s="13"/>
       <c r="AK3" s="13"/>
@@ -7514,7 +7485,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>212</v>
@@ -7544,13 +7515,13 @@
       <c r="Y4" s="13"/>
       <c r="Z4" s="13"/>
       <c r="AA4" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AB4" s="13"/>
       <c r="AC4" s="13"/>
       <c r="AD4" s="13"/>
       <c r="AE4" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AF4" s="13"/>
       <c r="AG4" s="13"/>
@@ -7565,7 +7536,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>218</v>
@@ -7591,11 +7562,11 @@
       <c r="U5" s="13"/>
       <c r="V5" s="13"/>
       <c r="W5" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="X5" s="13"/>
       <c r="Y5" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="Z5" s="13"/>
       <c r="AA5" s="13"/>
@@ -7616,7 +7587,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>803</v>
+        <v>795</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>224</v>
@@ -7642,11 +7613,11 @@
       <c r="U6" s="13"/>
       <c r="V6" s="13"/>
       <c r="W6" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="X6" s="13"/>
       <c r="Y6" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="Z6" s="13"/>
       <c r="AA6" s="13"/>
@@ -7667,7 +7638,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>804</v>
+        <v>796</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>230</v>
@@ -7695,7 +7666,7 @@
       <c r="W7" s="13"/>
       <c r="X7" s="13"/>
       <c r="Y7" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="Z7" s="13"/>
       <c r="AA7" s="13"/>
@@ -7716,7 +7687,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>805</v>
+        <v>797</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>236</v>
@@ -7734,7 +7705,7 @@
       <c r="M8" s="13"/>
       <c r="N8" s="13"/>
       <c r="O8" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="P8" s="13"/>
       <c r="Q8" s="13"/>
@@ -7765,7 +7736,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>806</v>
+        <v>798</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>242</v>
@@ -7780,7 +7751,7 @@
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
       <c r="L9" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
@@ -7814,7 +7785,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>248</v>
@@ -7829,7 +7800,7 @@
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
       <c r="L10" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="M10" s="13"/>
       <c r="N10" s="13"/>
@@ -7863,10 +7834,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>808</v>
+        <v>800</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
@@ -7897,7 +7868,7 @@
       <c r="AC11" s="13"/>
       <c r="AD11" s="13"/>
       <c r="AE11" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AF11" s="13"/>
       <c r="AG11" s="13"/>
@@ -7912,10 +7883,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C12" s="13"/>
       <c r="D12" s="13"/>
@@ -7946,7 +7917,7 @@
       <c r="AC12" s="13"/>
       <c r="AD12" s="13"/>
       <c r="AE12" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AF12" s="13"/>
       <c r="AG12" s="13"/>
@@ -7961,10 +7932,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
@@ -7983,14 +7954,14 @@
       <c r="Q13" s="13"/>
       <c r="R13" s="13"/>
       <c r="S13" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="T13" s="13"/>
       <c r="U13" s="13"/>
       <c r="V13" s="13"/>
       <c r="W13" s="13"/>
       <c r="X13" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="Y13" s="13"/>
       <c r="Z13" s="13"/>
@@ -8012,10 +7983,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
@@ -8039,10 +8010,10 @@
       <c r="V14" s="13"/>
       <c r="W14" s="13"/>
       <c r="X14" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="Y14" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="Z14" s="13"/>
       <c r="AA14" s="13"/>
@@ -8063,10 +8034,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>812</v>
+        <v>804</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C15" s="13"/>
       <c r="D15" s="13"/>
@@ -8075,7 +8046,7 @@
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
       <c r="I15" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="J15" s="13"/>
       <c r="K15" s="13"/>
@@ -8084,7 +8055,7 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13"/>
       <c r="P15" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="13"/>
@@ -8114,7 +8085,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>812</v>
+        <v>804</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>286</v>
@@ -8133,7 +8104,7 @@
       <c r="N16" s="13"/>
       <c r="O16" s="13"/>
       <c r="P16" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="Q16" s="13"/>
       <c r="R16" s="13"/>
@@ -8163,13 +8134,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>292</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
@@ -8186,7 +8157,7 @@
       <c r="P17" s="13"/>
       <c r="Q17" s="13"/>
       <c r="R17" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="S17" s="13"/>
       <c r="T17" s="13"/>
@@ -8214,7 +8185,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>299</v>
@@ -8243,7 +8214,7 @@
       <c r="X18" s="13"/>
       <c r="Y18" s="13"/>
       <c r="Z18" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AA18" s="13"/>
       <c r="AB18" s="13"/>
@@ -8263,7 +8234,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>305</v>
@@ -8288,7 +8259,7 @@
       <c r="T19" s="13"/>
       <c r="U19" s="13"/>
       <c r="V19" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="W19" s="13"/>
       <c r="X19" s="13"/>
@@ -8303,7 +8274,7 @@
       <c r="AG19" s="13"/>
       <c r="AH19" s="13"/>
       <c r="AI19" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AJ19" s="13"/>
       <c r="AK19" s="13"/>
@@ -8314,7 +8285,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>311</v>
@@ -8339,7 +8310,7 @@
       <c r="T20" s="13"/>
       <c r="U20" s="13"/>
       <c r="V20" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="W20" s="13"/>
       <c r="X20" s="13"/>
@@ -8363,7 +8334,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>317</v>
@@ -8378,7 +8349,7 @@
       <c r="J21" s="13"/>
       <c r="K21" s="13"/>
       <c r="L21" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="M21" s="13"/>
       <c r="N21" s="13"/>
@@ -8412,7 +8383,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>323</v>
@@ -8445,7 +8416,7 @@
       <c r="AB22" s="13"/>
       <c r="AC22" s="13"/>
       <c r="AD22" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AE22" s="13"/>
       <c r="AF22" s="13"/>
@@ -8461,7 +8432,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>330</v>
@@ -8477,7 +8448,7 @@
       <c r="K23" s="13"/>
       <c r="L23" s="13"/>
       <c r="M23" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="N23" s="13"/>
       <c r="O23" s="13"/>
@@ -8510,7 +8481,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>336</v>
@@ -8518,13 +8489,13 @@
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
       <c r="E24" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="F24" s="13"/>
       <c r="G24" s="13"/>
       <c r="H24" s="13"/>
       <c r="I24" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="J24" s="13"/>
       <c r="K24" s="13"/>
@@ -8533,7 +8504,7 @@
       <c r="N24" s="13"/>
       <c r="O24" s="13"/>
       <c r="P24" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="Q24" s="13"/>
       <c r="R24" s="13"/>
@@ -8563,7 +8534,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>342</v>
@@ -8583,7 +8554,7 @@
       <c r="O25" s="13"/>
       <c r="P25" s="13"/>
       <c r="Q25" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="R25" s="13"/>
       <c r="S25" s="13"/>
@@ -8612,7 +8583,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>347</v>
@@ -8637,7 +8608,7 @@
       <c r="T26" s="13"/>
       <c r="U26" s="13"/>
       <c r="V26" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="W26" s="13"/>
       <c r="X26" s="13"/>
@@ -8652,7 +8623,7 @@
       <c r="AG26" s="13"/>
       <c r="AH26" s="13"/>
       <c r="AI26" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AJ26" s="13"/>
       <c r="AK26" s="13"/>
@@ -8663,7 +8634,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>354</v>
@@ -8687,11 +8658,11 @@
       <c r="S27" s="13"/>
       <c r="T27" s="13"/>
       <c r="U27" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="V27" s="13"/>
       <c r="W27" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="X27" s="13"/>
       <c r="Y27" s="13"/>
@@ -8714,7 +8685,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>360</v>
@@ -8747,10 +8718,10 @@
       <c r="AB28" s="13"/>
       <c r="AC28" s="13"/>
       <c r="AD28" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AE28" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AF28" s="13"/>
       <c r="AG28" s="13"/>
@@ -8765,10 +8736,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C29" s="13"/>
       <c r="D29" s="13"/>
@@ -8788,10 +8759,10 @@
       <c r="R29" s="13"/>
       <c r="S29" s="13"/>
       <c r="T29" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="U29" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="V29" s="13"/>
       <c r="W29" s="13"/>
@@ -8816,10 +8787,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
@@ -8855,7 +8826,7 @@
       <c r="AH30" s="13"/>
       <c r="AI30" s="13"/>
       <c r="AJ30" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AK30" s="13"/>
       <c r="AL30" s="15" t="n">
@@ -8865,16 +8836,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="E31" s="13"/>
       <c r="F31" s="13"/>
@@ -8916,16 +8887,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C32" s="13"/>
       <c r="D32" s="13"/>
       <c r="E32" s="13"/>
       <c r="F32" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="G32" s="13"/>
       <c r="H32" s="13"/>
@@ -8954,7 +8925,7 @@
       <c r="AE32" s="13"/>
       <c r="AF32" s="13"/>
       <c r="AG32" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AH32" s="13"/>
       <c r="AI32" s="13"/>
@@ -8967,10 +8938,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C33" s="13"/>
       <c r="D33" s="13"/>
@@ -8993,11 +8964,11 @@
       <c r="U33" s="13"/>
       <c r="V33" s="13"/>
       <c r="W33" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="X33" s="13"/>
       <c r="Y33" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="Z33" s="13"/>
       <c r="AA33" s="13"/>
@@ -9018,10 +8989,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C34" s="13"/>
       <c r="D34" s="13"/>
@@ -9030,7 +9001,7 @@
       <c r="G34" s="13"/>
       <c r="H34" s="13"/>
       <c r="I34" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="J34" s="13"/>
       <c r="K34" s="13"/>
@@ -9067,10 +9038,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C35" s="13"/>
       <c r="D35" s="13"/>
@@ -9103,7 +9074,7 @@
       <c r="AE35" s="13"/>
       <c r="AF35" s="13"/>
       <c r="AG35" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AH35" s="13"/>
       <c r="AI35" s="13"/>
@@ -9116,10 +9087,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -9135,7 +9106,7 @@
       <c r="N36" s="13"/>
       <c r="O36" s="13"/>
       <c r="P36" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="Q36" s="13"/>
       <c r="R36" s="13"/>
@@ -9165,10 +9136,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
@@ -9180,13 +9151,13 @@
       <c r="J37" s="13"/>
       <c r="K37" s="13"/>
       <c r="L37" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="13"/>
       <c r="O37" s="13"/>
       <c r="P37" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="Q37" s="13"/>
       <c r="R37" s="13"/>
@@ -9216,10 +9187,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
@@ -9230,17 +9201,17 @@
       <c r="I38" s="13"/>
       <c r="J38" s="13"/>
       <c r="K38" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="L38" s="13"/>
       <c r="M38" s="13"/>
       <c r="N38" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="O38" s="13"/>
       <c r="P38" s="13"/>
       <c r="Q38" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="R38" s="13"/>
       <c r="S38" s="13"/>
@@ -9269,22 +9240,22 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
       <c r="E39" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="F39" s="13"/>
       <c r="G39" s="13"/>
       <c r="H39" s="13"/>
       <c r="I39" s="13"/>
       <c r="J39" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="K39" s="13"/>
       <c r="L39" s="13"/>
@@ -9320,10 +9291,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
@@ -9336,7 +9307,7 @@
       <c r="K40" s="13"/>
       <c r="L40" s="13"/>
       <c r="M40" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="N40" s="13"/>
       <c r="O40" s="13"/>
@@ -9369,14 +9340,14 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C41" s="13"/>
       <c r="D41" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="E41" s="13"/>
       <c r="F41" s="13"/>
@@ -9408,7 +9379,7 @@
       <c r="AF41" s="13"/>
       <c r="AG41" s="13"/>
       <c r="AH41" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AI41" s="13"/>
       <c r="AJ41" s="13"/>
@@ -9420,14 +9391,14 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C42" s="13"/>
       <c r="D42" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
@@ -9459,7 +9430,7 @@
       <c r="AF42" s="13"/>
       <c r="AG42" s="13"/>
       <c r="AH42" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AI42" s="13"/>
       <c r="AJ42" s="13"/>
@@ -9471,10 +9442,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C43" s="13"/>
       <c r="D43" s="13"/>
@@ -9500,7 +9471,7 @@
       <c r="X43" s="13"/>
       <c r="Y43" s="13"/>
       <c r="Z43" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AA43" s="13"/>
       <c r="AB43" s="13"/>
@@ -9520,10 +9491,10 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C44" s="13"/>
       <c r="D44" s="13"/>
@@ -9547,11 +9518,11 @@
       <c r="V44" s="13"/>
       <c r="W44" s="13"/>
       <c r="X44" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="Y44" s="13"/>
       <c r="Z44" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AA44" s="13"/>
       <c r="AB44" s="13"/>
@@ -9571,10 +9542,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C45" s="13"/>
       <c r="D45" s="13"/>
@@ -9592,7 +9563,7 @@
       <c r="P45" s="13"/>
       <c r="Q45" s="13"/>
       <c r="R45" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="S45" s="13"/>
       <c r="T45" s="13"/>
@@ -9602,7 +9573,7 @@
       <c r="X45" s="13"/>
       <c r="Y45" s="13"/>
       <c r="Z45" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AA45" s="13"/>
       <c r="AB45" s="13"/>
@@ -9622,10 +9593,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C46" s="13"/>
       <c r="D46" s="13"/>
@@ -9640,10 +9611,10 @@
       <c r="M46" s="13"/>
       <c r="N46" s="13"/>
       <c r="O46" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="P46" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="Q46" s="13"/>
       <c r="R46" s="13"/>
@@ -9673,10 +9644,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C47" s="13"/>
       <c r="D47" s="13"/>
@@ -9698,11 +9669,11 @@
       <c r="T47" s="13"/>
       <c r="U47" s="13"/>
       <c r="V47" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="W47" s="13"/>
       <c r="X47" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="Y47" s="13"/>
       <c r="Z47" s="13"/>
@@ -9724,10 +9695,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C48" s="13"/>
       <c r="D48" s="13"/>
@@ -9743,7 +9714,7 @@
       <c r="N48" s="13"/>
       <c r="O48" s="13"/>
       <c r="P48" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="Q48" s="13"/>
       <c r="R48" s="13"/>
@@ -9763,7 +9734,7 @@
       <c r="AF48" s="13"/>
       <c r="AG48" s="13"/>
       <c r="AH48" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AI48" s="13"/>
       <c r="AJ48" s="13"/>
@@ -9775,10 +9746,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>845</v>
+        <v>837</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C49" s="13"/>
       <c r="D49" s="13"/>
@@ -9798,7 +9769,7 @@
       <c r="R49" s="13"/>
       <c r="S49" s="13"/>
       <c r="T49" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="U49" s="13"/>
       <c r="V49" s="13"/>
@@ -9824,14 +9795,14 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C50" s="13"/>
       <c r="D50" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="E50" s="13"/>
       <c r="F50" s="13"/>
@@ -9873,10 +9844,10 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="12" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C51" s="13"/>
       <c r="D51" s="13"/>
@@ -9900,7 +9871,7 @@
       <c r="V51" s="13"/>
       <c r="W51" s="13"/>
       <c r="X51" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="Y51" s="13"/>
       <c r="Z51" s="13"/>
@@ -9922,10 +9893,10 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C52" s="13"/>
       <c r="D52" s="13"/>
@@ -9933,7 +9904,7 @@
       <c r="F52" s="13"/>
       <c r="G52" s="13"/>
       <c r="H52" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="I52" s="13"/>
       <c r="J52" s="13"/>
@@ -9941,12 +9912,12 @@
       <c r="L52" s="13"/>
       <c r="M52" s="13"/>
       <c r="N52" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="O52" s="13"/>
       <c r="P52" s="13"/>
       <c r="Q52" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="R52" s="13"/>
       <c r="S52" s="13"/>
@@ -9975,10 +9946,10 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C53" s="13"/>
       <c r="D53" s="13"/>
@@ -9986,7 +9957,7 @@
       <c r="F53" s="13"/>
       <c r="G53" s="13"/>
       <c r="H53" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="I53" s="13"/>
       <c r="J53" s="13"/>
@@ -10024,10 +9995,10 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>849</v>
+        <v>841</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C54" s="13"/>
       <c r="D54" s="13"/>
@@ -10057,7 +10028,7 @@
       <c r="AB54" s="13"/>
       <c r="AC54" s="13"/>
       <c r="AD54" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AE54" s="13"/>
       <c r="AF54" s="13"/>
@@ -10073,10 +10044,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C55" s="13"/>
       <c r="D55" s="13"/>
@@ -10104,7 +10075,7 @@
       <c r="Z55" s="13"/>
       <c r="AA55" s="13"/>
       <c r="AB55" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AC55" s="13"/>
       <c r="AD55" s="13"/>
@@ -10122,10 +10093,10 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C56" s="13"/>
       <c r="D56" s="13"/>
@@ -10147,10 +10118,10 @@
       <c r="T56" s="13"/>
       <c r="U56" s="13"/>
       <c r="V56" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="W56" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="X56" s="13"/>
       <c r="Y56" s="13"/>
@@ -10164,7 +10135,7 @@
       <c r="AG56" s="13"/>
       <c r="AH56" s="13"/>
       <c r="AI56" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AJ56" s="13"/>
       <c r="AK56" s="13"/>
@@ -10175,10 +10146,10 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="s">
-        <v>852</v>
+        <v>844</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C57" s="13"/>
       <c r="D57" s="13"/>
@@ -10215,7 +10186,7 @@
       <c r="AI57" s="13"/>
       <c r="AJ57" s="13"/>
       <c r="AK57" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AL57" s="15" t="n">
         <f aca="false">COUNTIF(C57:AK57,"x")</f>
@@ -10224,10 +10195,10 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="C58" s="13"/>
       <c r="D58" s="13"/>
@@ -10236,7 +10207,7 @@
       <c r="G58" s="13"/>
       <c r="H58" s="13"/>
       <c r="I58" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="J58" s="13"/>
       <c r="K58" s="13"/>
@@ -10273,10 +10244,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
-        <v>854</v>
+        <v>846</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C59" s="13"/>
       <c r="D59" s="13"/>
@@ -10293,7 +10264,7 @@
       <c r="O59" s="13"/>
       <c r="P59" s="13"/>
       <c r="Q59" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="R59" s="13"/>
       <c r="S59" s="13"/>
@@ -10306,7 +10277,7 @@
       <c r="Z59" s="13"/>
       <c r="AA59" s="13"/>
       <c r="AB59" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AC59" s="13"/>
       <c r="AD59" s="13"/>
@@ -10324,10 +10295,10 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>855</v>
+        <v>847</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="C60" s="13"/>
       <c r="D60" s="13"/>
@@ -10355,10 +10326,10 @@
       <c r="Z60" s="13"/>
       <c r="AA60" s="13"/>
       <c r="AB60" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AC60" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AD60" s="13"/>
       <c r="AE60" s="13"/>
@@ -10375,10 +10346,10 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="12" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="C61" s="13"/>
       <c r="D61" s="13"/>
@@ -10410,7 +10381,7 @@
       <c r="AD61" s="13"/>
       <c r="AE61" s="13"/>
       <c r="AF61" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AG61" s="13"/>
       <c r="AH61" s="13"/>
@@ -10424,15 +10395,15 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C62" s="13"/>
       <c r="D62" s="13"/>
       <c r="E62" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="F62" s="13"/>
       <c r="G62" s="13"/>
@@ -10442,7 +10413,7 @@
       <c r="K62" s="13"/>
       <c r="L62" s="13"/>
       <c r="M62" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="N62" s="13"/>
       <c r="O62" s="13"/>
@@ -10475,10 +10446,10 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="12" t="s">
-        <v>858</v>
+        <v>850</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="C63" s="13"/>
       <c r="D63" s="13"/>
@@ -10500,7 +10471,7 @@
       <c r="T63" s="13"/>
       <c r="U63" s="13"/>
       <c r="V63" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="W63" s="13"/>
       <c r="X63" s="13"/>
@@ -10515,7 +10486,7 @@
       <c r="AG63" s="13"/>
       <c r="AH63" s="13"/>
       <c r="AI63" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AJ63" s="13"/>
       <c r="AK63" s="13"/>
@@ -10526,10 +10497,10 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>859</v>
+        <v>851</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="C64" s="13"/>
       <c r="D64" s="13"/>
@@ -10541,7 +10512,7 @@
       <c r="J64" s="13"/>
       <c r="K64" s="13"/>
       <c r="L64" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="M64" s="13"/>
       <c r="N64" s="13"/>
@@ -10575,10 +10546,10 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="12" t="s">
-        <v>860</v>
+        <v>852</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="C65" s="13"/>
       <c r="D65" s="13"/>
@@ -10589,10 +10560,10 @@
       <c r="I65" s="13"/>
       <c r="J65" s="13"/>
       <c r="K65" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="L65" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="M65" s="13"/>
       <c r="N65" s="13"/>
@@ -10616,7 +10587,7 @@
       <c r="AF65" s="13"/>
       <c r="AG65" s="13"/>
       <c r="AH65" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AI65" s="13"/>
       <c r="AJ65" s="13"/>
@@ -10628,10 +10599,10 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="C66" s="13"/>
       <c r="D66" s="13"/>
@@ -10662,7 +10633,7 @@
       <c r="AC66" s="13"/>
       <c r="AD66" s="13"/>
       <c r="AE66" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AF66" s="13"/>
       <c r="AG66" s="13"/>
@@ -10677,10 +10648,10 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="12" t="s">
-        <v>862</v>
+        <v>854</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="C67" s="13"/>
       <c r="D67" s="13"/>
@@ -10714,7 +10685,7 @@
       <c r="AF67" s="13"/>
       <c r="AG67" s="13"/>
       <c r="AH67" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AI67" s="13"/>
       <c r="AJ67" s="13"/>
@@ -10726,10 +10697,10 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="12" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C68" s="13"/>
       <c r="D68" s="13"/>
@@ -10763,7 +10734,7 @@
       <c r="AF68" s="13"/>
       <c r="AG68" s="13"/>
       <c r="AH68" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AI68" s="13"/>
       <c r="AJ68" s="13"/>
@@ -10775,13 +10746,13 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="12" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="D69" s="13"/>
       <c r="E69" s="13"/>
@@ -10824,10 +10795,10 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="12" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="C70" s="13"/>
       <c r="D70" s="13"/>
@@ -10846,14 +10817,14 @@
       <c r="Q70" s="13"/>
       <c r="R70" s="13"/>
       <c r="S70" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="T70" s="13"/>
       <c r="U70" s="13"/>
       <c r="V70" s="13"/>
       <c r="W70" s="13"/>
       <c r="X70" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="Y70" s="13"/>
       <c r="Z70" s="13"/>
@@ -10875,10 +10846,10 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="12" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="C71" s="13"/>
       <c r="D71" s="13"/>
@@ -10889,7 +10860,7 @@
       <c r="I71" s="13"/>
       <c r="J71" s="13"/>
       <c r="K71" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="L71" s="13"/>
       <c r="M71" s="13"/>
@@ -10914,7 +10885,7 @@
       <c r="AF71" s="13"/>
       <c r="AG71" s="13"/>
       <c r="AH71" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AI71" s="13"/>
       <c r="AJ71" s="13"/>
@@ -10926,10 +10897,10 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="C72" s="13"/>
       <c r="D72" s="13"/>
@@ -10951,7 +10922,7 @@
       <c r="T72" s="13"/>
       <c r="U72" s="13"/>
       <c r="V72" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="W72" s="13"/>
       <c r="X72" s="13"/>
@@ -10975,10 +10946,10 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="12" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="C73" s="13"/>
       <c r="D73" s="13"/>
@@ -11006,7 +10977,7 @@
       <c r="Z73" s="13"/>
       <c r="AA73" s="13"/>
       <c r="AB73" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AC73" s="13"/>
       <c r="AD73" s="13"/>
@@ -11024,10 +10995,10 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="C74" s="13"/>
       <c r="D74" s="13"/>
@@ -11054,10 +11025,10 @@
       <c r="Y74" s="13"/>
       <c r="Z74" s="13"/>
       <c r="AA74" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AB74" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AC74" s="13"/>
       <c r="AD74" s="13"/>
@@ -11075,10 +11046,10 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="12" t="s">
-        <v>870</v>
+        <v>862</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="C75" s="13"/>
       <c r="D75" s="13"/>
@@ -11093,7 +11064,7 @@
       <c r="M75" s="13"/>
       <c r="N75" s="13"/>
       <c r="O75" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="P75" s="13"/>
       <c r="Q75" s="13"/>
@@ -11107,10 +11078,10 @@
       <c r="Y75" s="13"/>
       <c r="Z75" s="13"/>
       <c r="AA75" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AB75" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AC75" s="13"/>
       <c r="AD75" s="13"/>
@@ -11128,13 +11099,13 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
-        <v>871</v>
+        <v>863</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="D76" s="13"/>
       <c r="E76" s="13"/>
@@ -11150,7 +11121,7 @@
       <c r="O76" s="13"/>
       <c r="P76" s="13"/>
       <c r="Q76" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="R76" s="13"/>
       <c r="S76" s="13"/>
@@ -11179,10 +11150,10 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="12" t="s">
-        <v>872</v>
+        <v>864</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="C77" s="13"/>
       <c r="D77" s="13"/>
@@ -11209,7 +11180,7 @@
       <c r="Y77" s="13"/>
       <c r="Z77" s="13"/>
       <c r="AA77" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AB77" s="13"/>
       <c r="AC77" s="13"/>
@@ -11228,10 +11199,10 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="s">
-        <v>873</v>
+        <v>865</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="C78" s="13"/>
       <c r="D78" s="13"/>
@@ -11251,12 +11222,12 @@
       <c r="R78" s="13"/>
       <c r="S78" s="13"/>
       <c r="T78" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="U78" s="13"/>
       <c r="V78" s="13"/>
       <c r="W78" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="X78" s="13"/>
       <c r="Y78" s="13"/>
@@ -11279,10 +11250,10 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="12" t="s">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="C79" s="13"/>
       <c r="D79" s="13"/>
@@ -11305,11 +11276,11 @@
       <c r="U79" s="13"/>
       <c r="V79" s="13"/>
       <c r="W79" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="X79" s="13"/>
       <c r="Y79" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="Z79" s="13"/>
       <c r="AA79" s="13"/>
@@ -11321,7 +11292,7 @@
       <c r="AG79" s="13"/>
       <c r="AH79" s="13"/>
       <c r="AI79" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AJ79" s="13"/>
       <c r="AK79" s="13"/>
@@ -11332,10 +11303,10 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="C80" s="13"/>
       <c r="D80" s="13"/>
@@ -11357,7 +11328,7 @@
       <c r="T80" s="13"/>
       <c r="U80" s="13"/>
       <c r="V80" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="W80" s="13"/>
       <c r="X80" s="13"/>
@@ -11372,7 +11343,7 @@
       <c r="AG80" s="13"/>
       <c r="AH80" s="13"/>
       <c r="AI80" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AJ80" s="13"/>
       <c r="AK80" s="13"/>
@@ -11383,10 +11354,10 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="12" t="s">
-        <v>876</v>
+        <v>868</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="C81" s="13"/>
       <c r="D81" s="13"/>
@@ -11405,10 +11376,10 @@
       <c r="Q81" s="13"/>
       <c r="R81" s="13"/>
       <c r="S81" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="T81" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="U81" s="13"/>
       <c r="V81" s="13"/>
@@ -11434,13 +11405,13 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="s">
-        <v>877</v>
+        <v>869</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="D82" s="13"/>
       <c r="E82" s="13"/>
@@ -11460,7 +11431,7 @@
       <c r="S82" s="13"/>
       <c r="T82" s="13"/>
       <c r="U82" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="V82" s="13"/>
       <c r="W82" s="13"/>
@@ -11485,14 +11456,14 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="12" t="s">
-        <v>878</v>
+        <v>870</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="C83" s="13"/>
       <c r="D83" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="E83" s="13"/>
       <c r="F83" s="13"/>
@@ -11524,7 +11495,7 @@
       <c r="AF83" s="13"/>
       <c r="AG83" s="13"/>
       <c r="AH83" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AI83" s="13"/>
       <c r="AJ83" s="13"/>
@@ -11536,10 +11507,10 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="s">
-        <v>879</v>
+        <v>871</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="C84" s="13"/>
       <c r="D84" s="13"/>
@@ -11571,7 +11542,7 @@
       <c r="AD84" s="13"/>
       <c r="AE84" s="13"/>
       <c r="AF84" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AG84" s="13"/>
       <c r="AH84" s="13"/>
@@ -11585,10 +11556,10 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="12" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="C85" s="13"/>
       <c r="D85" s="13"/>
@@ -11611,7 +11582,7 @@
       <c r="U85" s="13"/>
       <c r="V85" s="13"/>
       <c r="W85" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="X85" s="13"/>
       <c r="Y85" s="13"/>
@@ -11623,7 +11594,7 @@
       <c r="AE85" s="13"/>
       <c r="AF85" s="13"/>
       <c r="AG85" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AH85" s="13"/>
       <c r="AI85" s="13"/>
@@ -11636,10 +11607,10 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="12" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="C86" s="13"/>
       <c r="D86" s="13"/>
@@ -11662,10 +11633,10 @@
       <c r="U86" s="13"/>
       <c r="V86" s="13"/>
       <c r="W86" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="X86" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="Y86" s="13"/>
       <c r="Z86" s="13"/>
@@ -11687,10 +11658,10 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="12" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="C87" s="13"/>
       <c r="D87" s="13"/>
@@ -11705,10 +11676,10 @@
       <c r="M87" s="13"/>
       <c r="N87" s="13"/>
       <c r="O87" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="P87" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="Q87" s="13"/>
       <c r="R87" s="13"/>
@@ -11738,18 +11709,18 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="12" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="C88" s="13"/>
       <c r="D88" s="13"/>
       <c r="E88" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="F88" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="G88" s="13"/>
       <c r="H88" s="13"/>
@@ -11759,7 +11730,7 @@
       <c r="L88" s="13"/>
       <c r="M88" s="13"/>
       <c r="N88" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="O88" s="13"/>
       <c r="P88" s="13"/>
@@ -11791,10 +11762,10 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="12" t="s">
-        <v>884</v>
+        <v>876</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="C89" s="13"/>
       <c r="D89" s="13"/>
@@ -11824,7 +11795,7 @@
       <c r="AB89" s="13"/>
       <c r="AC89" s="13"/>
       <c r="AD89" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AE89" s="13"/>
       <c r="AF89" s="13"/>
@@ -11840,10 +11811,10 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="12" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="C90" s="13"/>
       <c r="D90" s="13"/>
@@ -11853,7 +11824,7 @@
       <c r="H90" s="13"/>
       <c r="I90" s="13"/>
       <c r="J90" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="K90" s="13"/>
       <c r="L90" s="13"/>
@@ -11889,15 +11860,15 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="12" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="C91" s="13"/>
       <c r="D91" s="13"/>
       <c r="E91" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="F91" s="13"/>
       <c r="G91" s="13"/>
@@ -11938,14 +11909,14 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="12" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="C92" s="13"/>
       <c r="D92" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="E92" s="13"/>
       <c r="F92" s="13"/>
@@ -11977,7 +11948,7 @@
       <c r="AF92" s="13"/>
       <c r="AG92" s="13"/>
       <c r="AH92" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AI92" s="13"/>
       <c r="AJ92" s="13"/>
@@ -11989,28 +11960,28 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="12" t="s">
-        <v>888</v>
+        <v>880</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="C93" s="13"/>
       <c r="D93" s="13"/>
       <c r="E93" s="13"/>
       <c r="F93" s="13"/>
       <c r="G93" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="H93" s="13"/>
       <c r="I93" s="13"/>
       <c r="J93" s="13"/>
       <c r="K93" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="L93" s="13"/>
       <c r="M93" s="13"/>
       <c r="N93" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="O93" s="13"/>
       <c r="P93" s="13"/>
@@ -12042,19 +12013,19 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="12" t="s">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="C94" s="13"/>
       <c r="D94" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="E94" s="13"/>
       <c r="F94" s="13"/>
       <c r="G94" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="H94" s="13"/>
       <c r="I94" s="13"/>
@@ -12083,7 +12054,7 @@
       <c r="AF94" s="13"/>
       <c r="AG94" s="13"/>
       <c r="AH94" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AI94" s="13"/>
       <c r="AJ94" s="13"/>
@@ -12095,10 +12066,10 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="12" t="s">
-        <v>890</v>
+        <v>882</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="C95" s="13"/>
       <c r="D95" s="13"/>
@@ -12121,7 +12092,7 @@
       <c r="U95" s="13"/>
       <c r="V95" s="13"/>
       <c r="W95" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="X95" s="13"/>
       <c r="Y95" s="13"/>
@@ -12144,10 +12115,10 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="12" t="s">
-        <v>891</v>
+        <v>883</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="C96" s="13"/>
       <c r="D96" s="13"/>
@@ -12170,7 +12141,7 @@
       <c r="U96" s="13"/>
       <c r="V96" s="13"/>
       <c r="W96" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="X96" s="13"/>
       <c r="Y96" s="13"/>
@@ -12193,13 +12164,13 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="12" t="s">
-        <v>892</v>
+        <v>884</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="C97" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="D97" s="13"/>
       <c r="E97" s="13"/>
@@ -12207,7 +12178,7 @@
       <c r="G97" s="13"/>
       <c r="H97" s="13"/>
       <c r="I97" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="J97" s="13"/>
       <c r="K97" s="13"/>
@@ -12244,10 +12215,10 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="12" t="s">
-        <v>893</v>
+        <v>885</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="C98" s="13"/>
       <c r="D98" s="13"/>
@@ -12258,7 +12229,7 @@
       <c r="I98" s="13"/>
       <c r="J98" s="13"/>
       <c r="K98" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="L98" s="13"/>
       <c r="M98" s="13"/>
@@ -12293,13 +12264,13 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="12" t="s">
-        <v>894</v>
+        <v>886</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="C99" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="D99" s="13"/>
       <c r="E99" s="13"/>
@@ -12307,7 +12278,7 @@
       <c r="G99" s="13"/>
       <c r="H99" s="13"/>
       <c r="I99" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="J99" s="13"/>
       <c r="K99" s="13"/>
@@ -12344,17 +12315,17 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="12" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="C100" s="13"/>
       <c r="D100" s="13"/>
       <c r="E100" s="13"/>
       <c r="F100" s="13"/>
       <c r="G100" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="H100" s="13"/>
       <c r="I100" s="13"/>
@@ -12363,7 +12334,7 @@
       <c r="L100" s="13"/>
       <c r="M100" s="13"/>
       <c r="N100" s="14" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="O100" s="13"/>
       <c r="P100" s="13"/>

--- a/literature/concept-map/concept-map.xlsx
+++ b/literature/concept-map/concept-map.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="888">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="893">
   <si>
     <t xml:space="preserve">Concept map of the note “Voting for a consensus with veto rights” (v0.1)</t>
   </si>
@@ -882,6 +882,9 @@
     <t xml:space="preserve">Arrow, K. J. (1951). Social Choice and Individual Values. John Wiley &amp; Sons.</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.loc.gov/item/51009755/</t>
+  </si>
+  <si>
     <t xml:space="preserve">Balinski &amp; Laraki (2007). A Theory of Measuring, Electing, and Ranking</t>
   </si>
   <si>
@@ -1244,6 +1247,9 @@
     <t xml:space="preserve">Buchanan, J. M. &amp; Tullock, G. (1962). The Calculus of Consent: Logical Foundations of Constitutional Democracy. University of Michigan Press.</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.loc.gov/item/62007705/</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cailloux et al. (2023). Compromising as an Equal Loss Principle</t>
   </si>
   <si>
@@ -1322,6 +1328,9 @@
     <t xml:space="preserve">Condorcet (1785). Essai sur l'application de l'analyse à la probabilité des décisions rendues à la pluralité des voix. Imprimerie Royale.</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.loc.gov/item/06005363/</t>
+  </si>
+  <si>
     <t xml:space="preserve">Debian Project (2022). Constitution for the Debian Project (v1.9)</t>
   </si>
   <si>
@@ -1395,13 +1404,10 @@
     <t xml:space="preserve">§2 Setting, §4 Veto literature</t>
   </si>
   <si>
-    <t xml:space="preserve">European Union (2016). Consolidated Version of the Treaty on European Union, Article 16. Official Journal of the European Union, C 202, 7.6.2016.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX:12016M/TXT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OJ page numbers and the CELEX number in the url (12016M/TXT).</t>
+    <t xml:space="preserve">European Union (2016). Consolidated Version of the Treaty on European Union, Article 16. Official Journal of the European Union, C 202, 7.6.2016, p. 24.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://data.europa.eu/eli/treaty/teu_2016/oj</t>
   </si>
   <si>
     <t xml:space="preserve">Faliszewski &amp; Procaccia (2010). AI's War on Manipulation: Are We Winning?</t>
@@ -1433,6 +1439,9 @@
   </si>
   <si>
     <t xml:space="preserve">Felsenthal, D. S. &amp; Machover, M. (2008). The Majority Judgement Voting Procedure: A Critical Evaluation. Homo Oeconomicus 25(3/4): 319–334.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not checked against the journal's record: no Crossref record; the LSE repository record (eprints.lse.ac.uk/24213) is not reachable from the checking environment. Felsenthal (2012, doi 10.1007/978-3-642-20441-8_3) gives pages 319-333; Balinski and Laraki (2014, doi 10.1287/opre.2014.1269) give 25, first page 319</t>
   </si>
   <si>
     <t xml:space="preserve">Felsenthal (2012). Review of Paradoxes Afflicting Procedures for Electing a Single Candidate</t>
@@ -1817,13 +1826,13 @@
     <t xml:space="preserve">Kemeny1959</t>
   </si>
   <si>
-    <t xml:space="preserve">Kemeny, J. G. (1959). Mathematics without Numbers. Daedalus 88(4): 571–591.</t>
+    <t xml:space="preserve">Kemeny, J. G. (1959). Mathematics without Numbers. Daedalus 88(4): 577–591.</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.jstor.org/stable/20026529</t>
   </si>
   <si>
-    <t xml:space="preserve">No Crossref record. First page 571 as cited by Young and Levenglick (1978), Young (1988) and Bartholdi et al. (1989) in their Crossref reference lists; Kondratev and Nesterov (2020) give 577. JSTOR 20026529 not reachable to settle it</t>
+    <t xml:space="preserve">Not checked against the journal's record: no Crossref record, and JSTOR 20026529 refuses automated access. First page 577 in Fishburn (1977), the earliest citing paper found, and in Kondratev and Nesterov (2020); 571 in Young and Levenglick (1978), Young (1988) and Bartholdi et al. (1989)</t>
   </si>
   <si>
     <t xml:space="preserve">Kondratev &amp; Ianovski (2024). Veto Core Consistent Preference Aggregation</t>
@@ -2249,6 +2258,9 @@
     <t xml:space="preserve">https://www.jstor.org/stable/1815369</t>
   </si>
   <si>
+    <t xml:space="preserve">Not checked against the journal's record: no Crossref record, and JSTOR 1815369 refuses automated access. McKelvey (1976, doi 10.1016/0022-0531(76)90040-5) cites it as Amer. Econ. Rev. 57, 1967</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rae (1969). Decision-Rules and Individual Values in Constitutional Choice</t>
   </si>
   <si>
@@ -2280,7 +2292,7 @@
     <t xml:space="preserve">Regenwetter, M., Grofman, B., Marley, A. A. J. &amp; Tsetlin, I. (2006). Behavioral Social Choice: Probabilistic Models, Statistical Inference, and Applications. Cambridge University Press.</t>
   </si>
   <si>
-    <t xml:space="preserve">No DOI found in Crossref. The candidate DOI given earlier (10.1017/CBO9780511617577) belongs to another book. The book is confirmed by its reviews in Social Choice and Welfare 31(2), 2008 (doi 10.1007/s00355-008-0314-z) and Choice 44-3496, 2007</t>
+    <t xml:space="preserve">https://www.loc.gov/item/2005023291/</t>
   </si>
   <si>
     <t xml:space="preserve">Resnick (2014). On Consensus and Humming in the IETF</t>
@@ -2482,6 +2494,9 @@
   </si>
   <si>
     <t xml:space="preserve">Tideman, N. (2006). Collective Decisions and Voting: The Potential for Public Choice. Ashgate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.loc.gov/item/2006021134/</t>
   </si>
   <si>
     <t xml:space="preserve">Tsebelis (1995). Decision Making in Political Systems: Veto Players in Presidentialism, Parliamentarism, Multicameralism and Multipartyism</t>
@@ -4507,7 +4522,9 @@
       <c r="F7" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="G7" s="8"/>
+      <c r="G7" s="9" t="s">
+        <v>239</v>
+      </c>
       <c r="H7" s="8"/>
       <c r="I7" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D7,Matrix!$B$3:$B$100,0),0),"x")</f>
@@ -4516,25 +4533,25 @@
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="8" t="n">
@@ -4544,25 +4561,25 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="8" t="n">
@@ -4572,25 +4589,25 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="8" t="n">
@@ -4600,25 +4617,25 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8" t="n">
@@ -4628,25 +4645,25 @@
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8" t="n">
@@ -4656,25 +4673,25 @@
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8" t="n">
@@ -4684,25 +4701,25 @@
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H14" s="8"/>
       <c r="I14" s="8" t="n">
@@ -4712,25 +4729,25 @@
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="8" t="n">
@@ -4740,25 +4757,25 @@
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H16" s="8"/>
       <c r="I16" s="8" t="n">
@@ -4768,25 +4785,25 @@
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H17" s="8"/>
       <c r="I17" s="8" t="n">
@@ -4796,25 +4813,25 @@
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H18" s="8"/>
       <c r="I18" s="8" t="n">
@@ -4824,25 +4841,25 @@
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H19" s="8"/>
       <c r="I19" s="8" t="n">
@@ -4852,25 +4869,25 @@
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H20" s="8"/>
       <c r="I20" s="8" t="n">
@@ -4880,25 +4897,25 @@
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="8" t="n">
@@ -4908,25 +4925,25 @@
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H22" s="8"/>
       <c r="I22" s="8" t="n">
@@ -4936,25 +4953,25 @@
     </row>
     <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H23" s="8"/>
       <c r="I23" s="8" t="n">
@@ -4964,25 +4981,25 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H24" s="8"/>
       <c r="I24" s="8" t="n">
@@ -4992,25 +5009,25 @@
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>203</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H25" s="8"/>
       <c r="I25" s="8" t="n">
@@ -5020,24 +5037,26 @@
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="G26" s="8"/>
+        <v>357</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>358</v>
+      </c>
       <c r="H26" s="8"/>
       <c r="I26" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D26,Matrix!$B$3:$B$100,0),0),"x")</f>
@@ -5046,25 +5065,25 @@
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H27" s="8"/>
       <c r="I27" s="8" t="n">
@@ -5074,25 +5093,25 @@
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H28" s="8"/>
       <c r="I28" s="8" t="n">
@@ -5105,22 +5124,22 @@
         <v>185</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H29" s="8"/>
       <c r="I29" s="8" t="n">
@@ -5130,24 +5149,26 @@
     </row>
     <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="G30" s="8"/>
+        <v>383</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>384</v>
+      </c>
       <c r="H30" s="8"/>
       <c r="I30" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D30,Matrix!$B$3:$B$100,0),0),"x")</f>
@@ -5156,25 +5177,25 @@
     </row>
     <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="H31" s="8"/>
       <c r="I31" s="8" t="n">
@@ -5184,25 +5205,25 @@
     </row>
     <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>222</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="H32" s="8"/>
       <c r="I32" s="8" t="n">
@@ -5212,25 +5233,25 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="H33" s="8"/>
       <c r="I33" s="8" t="n">
@@ -5238,31 +5259,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>408</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="H34" s="8"/>
       <c r="I34" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D34,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>1</v>
@@ -5270,25 +5289,25 @@
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="H35" s="8"/>
       <c r="I35" s="8" t="n">
@@ -5296,27 +5315,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
+      <c r="H36" s="8" t="s">
+        <v>421</v>
+      </c>
       <c r="I36" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D36,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>2</v>
@@ -5324,25 +5345,25 @@
     </row>
     <row r="37" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H37" s="8"/>
       <c r="I37" s="8" t="n">
@@ -5352,25 +5373,25 @@
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H38" s="8"/>
       <c r="I38" s="8" t="n">
@@ -5380,25 +5401,25 @@
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="H39" s="8"/>
       <c r="I39" s="8" t="n">
@@ -5408,25 +5429,25 @@
     </row>
     <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E40" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="H40" s="8"/>
       <c r="I40" s="8" t="n">
@@ -5436,25 +5457,25 @@
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E41" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="H41" s="8"/>
       <c r="I41" s="8" t="n">
@@ -5464,25 +5485,25 @@
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="H42" s="8"/>
       <c r="I42" s="8" t="n">
@@ -5492,25 +5513,25 @@
     </row>
     <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="E43" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="H43" s="8"/>
       <c r="I43" s="8" t="n">
@@ -5520,25 +5541,25 @@
     </row>
     <row r="44" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="H44" s="8"/>
       <c r="I44" s="8" t="n">
@@ -5548,25 +5569,25 @@
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="H45" s="8"/>
       <c r="I45" s="8" t="n">
@@ -5576,25 +5597,25 @@
     </row>
     <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="H46" s="8"/>
       <c r="I46" s="8" t="n">
@@ -5604,25 +5625,25 @@
     </row>
     <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="H47" s="8"/>
       <c r="I47" s="8" t="n">
@@ -5632,25 +5653,25 @@
     </row>
     <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="H48" s="8"/>
       <c r="I48" s="8" t="n">
@@ -5660,25 +5681,25 @@
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E49" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="H49" s="8"/>
       <c r="I49" s="8" t="n">
@@ -5688,25 +5709,25 @@
     </row>
     <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E50" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="H50" s="8"/>
       <c r="I50" s="8" t="n">
@@ -5716,25 +5737,25 @@
     </row>
     <row r="51" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="H51" s="8"/>
       <c r="I51" s="8" t="n">
@@ -5744,25 +5765,25 @@
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="H52" s="8"/>
       <c r="I52" s="8" t="n">
@@ -5772,25 +5793,25 @@
     </row>
     <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E53" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="H53" s="8"/>
       <c r="I53" s="8" t="n">
@@ -5800,25 +5821,25 @@
     </row>
     <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="H54" s="8"/>
       <c r="I54" s="8" t="n">
@@ -5828,25 +5849,25 @@
     </row>
     <row r="55" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E55" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="H55" s="8"/>
       <c r="I55" s="8" t="n">
@@ -5859,22 +5880,22 @@
         <v>190</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E56" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="H56" s="8"/>
       <c r="I56" s="8" t="n">
@@ -5882,30 +5903,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="I57" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D57,Matrix!$B$3:$B$100,0),0),"x")</f>
@@ -5914,25 +5935,25 @@
     </row>
     <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="E58" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="H58" s="8"/>
       <c r="I58" s="8" t="n">
@@ -5945,22 +5966,22 @@
         <v>151</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="E59" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="H59" s="8"/>
       <c r="I59" s="8" t="n">
@@ -5970,25 +5991,25 @@
     </row>
     <row r="60" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="H60" s="8"/>
       <c r="I60" s="8" t="n">
@@ -5998,25 +6019,25 @@
     </row>
     <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="H61" s="8"/>
       <c r="I61" s="8" t="n">
@@ -6026,25 +6047,25 @@
     </row>
     <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="B62" s="8" t="s">
         <v>203</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="E62" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="H62" s="8"/>
       <c r="I62" s="8" t="n">
@@ -6054,25 +6075,25 @@
     </row>
     <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H63" s="8"/>
       <c r="I63" s="8" t="n">
@@ -6082,25 +6103,25 @@
     </row>
     <row r="64" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="H64" s="8"/>
       <c r="I64" s="8" t="n">
@@ -6110,25 +6131,25 @@
     </row>
     <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E65" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="H65" s="8"/>
       <c r="I65" s="8" t="n">
@@ -6138,25 +6159,25 @@
     </row>
     <row r="66" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="H66" s="8"/>
       <c r="I66" s="8" t="n">
@@ -6166,25 +6187,25 @@
     </row>
     <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="H67" s="8"/>
       <c r="I67" s="8" t="n">
@@ -6194,25 +6215,25 @@
     </row>
     <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="E68" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H68" s="8"/>
       <c r="I68" s="8" t="n">
@@ -6222,25 +6243,25 @@
     </row>
     <row r="69" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="H69" s="8"/>
       <c r="I69" s="8" t="n">
@@ -6250,25 +6271,25 @@
     </row>
     <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="H70" s="8"/>
       <c r="I70" s="8" t="n">
@@ -6278,25 +6299,25 @@
     </row>
     <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="H71" s="8"/>
       <c r="I71" s="8" t="n">
@@ -6306,25 +6327,25 @@
     </row>
     <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H72" s="8"/>
       <c r="I72" s="8" t="n">
@@ -6334,25 +6355,25 @@
     </row>
     <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="E73" s="8" t="s">
         <v>634</v>
       </c>
-      <c r="B73" s="8" t="s">
-        <v>635</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>636</v>
-      </c>
-      <c r="D73" s="8" t="s">
-        <v>637</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>631</v>
-      </c>
       <c r="F73" s="8" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="H73" s="8"/>
       <c r="I73" s="8" t="n">
@@ -6362,22 +6383,22 @@
     </row>
     <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="E74" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
@@ -6388,25 +6409,25 @@
     </row>
     <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="H75" s="8"/>
       <c r="I75" s="8" t="n">
@@ -6416,25 +6437,25 @@
     </row>
     <row r="76" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="E76" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="H76" s="8"/>
       <c r="I76" s="8" t="n">
@@ -6444,25 +6465,25 @@
     </row>
     <row r="77" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="E77" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="H77" s="8"/>
       <c r="I77" s="8" t="n">
@@ -6472,25 +6493,25 @@
     </row>
     <row r="78" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="H78" s="8"/>
       <c r="I78" s="8" t="n">
@@ -6500,25 +6521,25 @@
     </row>
     <row r="79" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="E79" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="H79" s="8"/>
       <c r="I79" s="8" t="n">
@@ -6526,29 +6547,31 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="E80" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>680</v>
-      </c>
-      <c r="H80" s="8"/>
+        <v>683</v>
+      </c>
+      <c r="H80" s="8" t="s">
+        <v>684</v>
+      </c>
       <c r="I80" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D80,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>2</v>
@@ -6556,25 +6579,25 @@
     </row>
     <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E81" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="H81" s="8"/>
       <c r="I81" s="8" t="n">
@@ -6582,29 +6605,29 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>690</v>
-      </c>
-      <c r="G82" s="8"/>
-      <c r="H82" s="8" t="s">
-        <v>691</v>
-      </c>
+        <v>694</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="H82" s="8"/>
       <c r="I82" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D82,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>2</v>
@@ -6612,25 +6635,25 @@
     </row>
     <row r="83" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="H83" s="8"/>
       <c r="I83" s="8" t="n">
@@ -6640,25 +6663,25 @@
     </row>
     <row r="84" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="H84" s="8"/>
       <c r="I84" s="8" t="n">
@@ -6668,25 +6691,25 @@
     </row>
     <row r="85" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="E85" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="H85" s="8"/>
       <c r="I85" s="8" t="n">
@@ -6696,25 +6719,25 @@
     </row>
     <row r="86" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="G86" s="9" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="H86" s="8"/>
       <c r="I86" s="8" t="n">
@@ -6724,25 +6747,25 @@
     </row>
     <row r="87" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="H87" s="8"/>
       <c r="I87" s="8" t="n">
@@ -6752,25 +6775,25 @@
     </row>
     <row r="88" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="H88" s="8"/>
       <c r="I88" s="8" t="n">
@@ -6780,25 +6803,25 @@
     </row>
     <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="H89" s="8"/>
       <c r="I89" s="8" t="n">
@@ -6808,25 +6831,25 @@
     </row>
     <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="G90" s="9" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="H90" s="8"/>
       <c r="I90" s="8" t="n">
@@ -6836,25 +6859,25 @@
     </row>
     <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="H91" s="8"/>
       <c r="I91" s="8" t="n">
@@ -6864,25 +6887,25 @@
     </row>
     <row r="92" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="G92" s="9" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="H92" s="8"/>
       <c r="I92" s="8" t="n">
@@ -6892,24 +6915,26 @@
     </row>
     <row r="93" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="E93" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>755</v>
-      </c>
-      <c r="G93" s="8"/>
+        <v>759</v>
+      </c>
+      <c r="G93" s="9" t="s">
+        <v>760</v>
+      </c>
       <c r="H93" s="8"/>
       <c r="I93" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D93,Matrix!$B$3:$B$100,0),0),"x")</f>
@@ -6918,25 +6943,25 @@
     </row>
     <row r="94" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="E94" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="H94" s="8"/>
       <c r="I94" s="8" t="n">
@@ -6946,25 +6971,25 @@
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="s">
+        <v>767</v>
+      </c>
+      <c r="B95" s="8" t="s">
         <v>762</v>
       </c>
-      <c r="B95" s="8" t="s">
-        <v>757</v>
-      </c>
       <c r="C95" s="8" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="H95" s="8"/>
       <c r="I95" s="8" t="n">
@@ -6974,25 +6999,25 @@
     </row>
     <row r="96" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="G96" s="9" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="H96" s="8"/>
       <c r="I96" s="8" t="n">
@@ -7002,25 +7027,25 @@
     </row>
     <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="H97" s="8"/>
       <c r="I97" s="8" t="n">
@@ -7030,25 +7055,25 @@
     </row>
     <row r="98" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="G98" s="9" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="H98" s="8"/>
       <c r="I98" s="8" t="n">
@@ -7058,25 +7083,25 @@
     </row>
     <row r="99" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="H99" s="8"/>
       <c r="I99" s="8" t="n">
@@ -7092,92 +7117,97 @@
     <hyperlink ref="G4" r:id="rId3" display="https://doi.org/10.1257/mic.20190023"/>
     <hyperlink ref="G5" r:id="rId4" display="https://doi.org/10.1016/j.geb.2016.04.010"/>
     <hyperlink ref="G6" r:id="rId5" display="https://doi.org/10.1093/restud/rdv009"/>
-    <hyperlink ref="G8" r:id="rId6" display="https://doi.org/10.1073/pnas.0702634104"/>
-    <hyperlink ref="G9" r:id="rId7" display="https://doi.org/10.7551/mitpress/9780262015134.001.0001"/>
-    <hyperlink ref="G10" r:id="rId8" display="https://doi.org/10.1016/j.geb.2015.10.005"/>
-    <hyperlink ref="G11" r:id="rId9" display="https://doi.org/10.1111/1756-2171.12401"/>
-    <hyperlink ref="G12" r:id="rId10" display="https://doi.org/10.3982/TE2118"/>
-    <hyperlink ref="G13" r:id="rId11" display="https://doi.org/10.2307/1961664"/>
-    <hyperlink ref="G14" r:id="rId12" display="https://doi.org/10.1007/BF00303169"/>
-    <hyperlink ref="G15" r:id="rId13" display="https://doi.org/10.1007/BF00295861"/>
-    <hyperlink ref="G16" r:id="rId14" display="https://doi.org/10.1086/256633"/>
-    <hyperlink ref="G17" r:id="rId15" display="https://doi.org/10.1016/j.jet.2014.11.008"/>
-    <hyperlink ref="G18" r:id="rId16" display="https://doi.org/10.1016/j.geb.2016.12.001"/>
-    <hyperlink ref="G19" r:id="rId17" display="https://doi.org/10.1086/695477"/>
-    <hyperlink ref="G20" r:id="rId18" display="https://doi.org/10.2307/1955105"/>
-    <hyperlink ref="G21" r:id="rId19" display="https://doi.org/10.1023/A:1011252808608"/>
-    <hyperlink ref="G22" r:id="rId20" display="https://doi.org/10.3982/ECTA13337"/>
-    <hyperlink ref="G23" r:id="rId21" display="https://doi.org/10.1017/CBO9781107446984"/>
-    <hyperlink ref="G24" r:id="rId22" display="https://doi.org/10.1016/j.mathsocsci.2016.09.003"/>
-    <hyperlink ref="G25" r:id="rId23" display="https://doi.org/10.1111/1756-2171.12457"/>
-    <hyperlink ref="G27" r:id="rId24" display="https://doi.org/10.1007/s10058-022-00302-w"/>
-    <hyperlink ref="G28" r:id="rId25" display="https://doi.org/10.2307/1912699"/>
-    <hyperlink ref="G29" r:id="rId26" display="https://doi.org/10.1016/j.geb.2004.09.009"/>
-    <hyperlink ref="G31" r:id="rId27" display="https://www.debian.org/devel/constitution"/>
-    <hyperlink ref="G32" r:id="rId28" display="https://doi.org/10.1086/686747"/>
-    <hyperlink ref="G33" r:id="rId29" display="https://doi.org/10.1007/s00355-015-0892-5"/>
-    <hyperlink ref="G34" r:id="rId30" display="https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX:12016M/TXT"/>
-    <hyperlink ref="G35" r:id="rId31" display="https://doi.org/10.1609/aimag.v31i4.2314"/>
-    <hyperlink ref="G37" r:id="rId32" display="https://doi.org/10.1007/978-3-642-20441-8_3"/>
-    <hyperlink ref="G38" r:id="rId33" display="https://doi.org/10.1137/0133030"/>
-    <hyperlink ref="G39" r:id="rId34" display="https://doi.org/10.2307/2297786"/>
-    <hyperlink ref="G40" r:id="rId35" display="https://doi.org/10.1016/0022-0531(76)90063-6"/>
-    <hyperlink ref="G41" r:id="rId36" display="https://doi.org/10.1007/3-540-33799-7"/>
-    <hyperlink ref="G42" r:id="rId37" display="https://arxiv.org/abs/2410.20476"/>
-    <hyperlink ref="G43" r:id="rId38" display="https://doi.org/10.1007/s00355-023-01505-y"/>
-    <hyperlink ref="G44" r:id="rId39" display="https://arxiv.org/abs/2506.05998"/>
-    <hyperlink ref="G45" r:id="rId40" display="https://doi.org/10.2307/1914083"/>
-    <hyperlink ref="G46" r:id="rId41" display="https://doi.org/10.1007/s11127-026-01383-9"/>
-    <hyperlink ref="G47" r:id="rId42" display="https://doi.org/10.1007/s00355-015-0909-0"/>
-    <hyperlink ref="G48" r:id="rId43" display="https://doi.org/10.2307/1910410"/>
-    <hyperlink ref="G49" r:id="rId44" display="https://doi.org/10.3406/ecoap.1952.3831"/>
-    <hyperlink ref="G50" r:id="rId45" display="https://doi.org/10.1007/BF00125914"/>
-    <hyperlink ref="G51" r:id="rId46" display="https://doi.org/10.1007/s11127-023-01042-3"/>
-    <hyperlink ref="G52" r:id="rId47" display="https://doi.org/10.1007/s10602-022-09383-9"/>
-    <hyperlink ref="G53" r:id="rId48" display="https://doi.org/10.1007/978-1-349-14540-9_4"/>
-    <hyperlink ref="G54" r:id="rId49" display="https://doi.org/10.1609/aaai.v35i6.16691"/>
-    <hyperlink ref="G55" r:id="rId50" display="https://doi.org/10.1007/s10683-010-9234-8"/>
-    <hyperlink ref="G56" r:id="rId51" display="https://doi.org/10.1257/aer.20201817"/>
-    <hyperlink ref="G57" r:id="rId52" display="https://www.jstor.org/stable/20026529"/>
-    <hyperlink ref="G58" r:id="rId53" display="https://doi.org/10.65109/hmhq1427"/>
-    <hyperlink ref="G59" r:id="rId54" display="https://doi.org/10.1007/s11127-019-00697-1"/>
-    <hyperlink ref="G60" r:id="rId55" display="https://doi.org/10.3917/neg.027.0109"/>
-    <hyperlink ref="G61" r:id="rId56" display="https://doi.org/10.1006/game.1993.1010"/>
-    <hyperlink ref="G62" r:id="rId57" display="https://doi.org/10.1002/bs.3830360303"/>
-    <hyperlink ref="G63" r:id="rId58" display="https://doi.org/10.1007/978-3-642-02839-7"/>
-    <hyperlink ref="G64" r:id="rId59" display="https://doi.org/10.1007/978-3-642-20441-8_13"/>
-    <hyperlink ref="G65" r:id="rId60" display="https://doi.org/10.1016/j.jet.2021.105261"/>
-    <hyperlink ref="G66" r:id="rId61" display="https://doi.org/10.1093/biomet/44.1-2.114"/>
-    <hyperlink ref="G67" r:id="rId62" display="https://doi.org/10.1007/978-3-642-41575-3_20"/>
-    <hyperlink ref="G68" r:id="rId63" display="https://doi.org/10.2307/1907651"/>
-    <hyperlink ref="G69" r:id="rId64" display="https://doi.org/10.1016/0022-0531(76)90040-5"/>
-    <hyperlink ref="G70" r:id="rId65" display="https://doi.org/10.2307/2110786"/>
-    <hyperlink ref="G71" r:id="rId66" display="https://doi.org/10.1257/mic.20230208"/>
-    <hyperlink ref="G72" r:id="rId67" display="https://doi.org/10.2307/2297154"/>
-    <hyperlink ref="G73" r:id="rId68" display="https://doi.org/10.2307/1912535"/>
-    <hyperlink ref="G75" r:id="rId69" display="https://doi.org/10.1016/0022-0531(88)90253-0"/>
-    <hyperlink ref="G76" r:id="rId70" display="https://doi.org/10.1016/0047-2727(78)90005-1"/>
-    <hyperlink ref="G77" r:id="rId71" display="https://doi.org/10.1007/BF01763051"/>
-    <hyperlink ref="G78" r:id="rId72" display="https://doi.org/10.1016/j.geb.2020.11.006"/>
-    <hyperlink ref="G79" r:id="rId73" display="https://doi.org/10.1016/j.geb.2025.07.010"/>
-    <hyperlink ref="G80" r:id="rId74" display="https://www.jstor.org/stable/1815369"/>
-    <hyperlink ref="G81" r:id="rId75" display="https://doi.org/10.2307/1954283"/>
-    <hyperlink ref="G83" r:id="rId76" display="https://doi.org/10.17487/RFC7282"/>
-    <hyperlink ref="G84" r:id="rId77" display="https://doi.org/10.1007/s10602-008-9037-5"/>
-    <hyperlink ref="G85" r:id="rId78" display="https://doi.org/10.1007/BF03187594"/>
-    <hyperlink ref="G86" r:id="rId79" display="https://doi.org/10.1016/0022-0531(75)90050-2"/>
-    <hyperlink ref="G87" r:id="rId80" display="https://doi.org/10.1007/s00355-010-0475-4"/>
-    <hyperlink ref="G88" r:id="rId81" display="https://doi.org/10.1007/s003550050164"/>
-    <hyperlink ref="G89" r:id="rId82" display="https://doi.org/10.2307/1880533"/>
-    <hyperlink ref="G90" r:id="rId83" display="https://doi.org/10.2307/1914033"/>
-    <hyperlink ref="G91" r:id="rId84" display="https://doi.org/10.1007/978-3-642-20441-8_9"/>
-    <hyperlink ref="G92" r:id="rId85" display="https://doi.org/10.1007/BF00433944"/>
-    <hyperlink ref="G94" r:id="rId86" display="https://doi.org/10.1017/S0007123400007225"/>
-    <hyperlink ref="G95" r:id="rId87" display="https://doi.org/10.1515/9781400831456"/>
-    <hyperlink ref="G96" r:id="rId88" display="https://doi.org/10.1137/0135023"/>
-    <hyperlink ref="G97" r:id="rId89" display="https://doi.org/10.1016/0022-0531(74)90073-8"/>
-    <hyperlink ref="G98" r:id="rId90" display="https://doi.org/10.2307/1961757"/>
-    <hyperlink ref="G99" r:id="rId91" display="https://doi.org/10.1007/BF00303170"/>
+    <hyperlink ref="G7" r:id="rId6" display="https://www.loc.gov/item/51009755/"/>
+    <hyperlink ref="G8" r:id="rId7" display="https://doi.org/10.1073/pnas.0702634104"/>
+    <hyperlink ref="G9" r:id="rId8" display="https://doi.org/10.7551/mitpress/9780262015134.001.0001"/>
+    <hyperlink ref="G10" r:id="rId9" display="https://doi.org/10.1016/j.geb.2015.10.005"/>
+    <hyperlink ref="G11" r:id="rId10" display="https://doi.org/10.1111/1756-2171.12401"/>
+    <hyperlink ref="G12" r:id="rId11" display="https://doi.org/10.3982/TE2118"/>
+    <hyperlink ref="G13" r:id="rId12" display="https://doi.org/10.2307/1961664"/>
+    <hyperlink ref="G14" r:id="rId13" display="https://doi.org/10.1007/BF00303169"/>
+    <hyperlink ref="G15" r:id="rId14" display="https://doi.org/10.1007/BF00295861"/>
+    <hyperlink ref="G16" r:id="rId15" display="https://doi.org/10.1086/256633"/>
+    <hyperlink ref="G17" r:id="rId16" display="https://doi.org/10.1016/j.jet.2014.11.008"/>
+    <hyperlink ref="G18" r:id="rId17" display="https://doi.org/10.1016/j.geb.2016.12.001"/>
+    <hyperlink ref="G19" r:id="rId18" display="https://doi.org/10.1086/695477"/>
+    <hyperlink ref="G20" r:id="rId19" display="https://doi.org/10.2307/1955105"/>
+    <hyperlink ref="G21" r:id="rId20" display="https://doi.org/10.1023/A:1011252808608"/>
+    <hyperlink ref="G22" r:id="rId21" display="https://doi.org/10.3982/ECTA13337"/>
+    <hyperlink ref="G23" r:id="rId22" display="https://doi.org/10.1017/CBO9781107446984"/>
+    <hyperlink ref="G24" r:id="rId23" display="https://doi.org/10.1016/j.mathsocsci.2016.09.003"/>
+    <hyperlink ref="G25" r:id="rId24" display="https://doi.org/10.1111/1756-2171.12457"/>
+    <hyperlink ref="G26" r:id="rId25" display="https://www.loc.gov/item/62007705/"/>
+    <hyperlink ref="G27" r:id="rId26" display="https://doi.org/10.1007/s10058-022-00302-w"/>
+    <hyperlink ref="G28" r:id="rId27" display="https://doi.org/10.2307/1912699"/>
+    <hyperlink ref="G29" r:id="rId28" display="https://doi.org/10.1016/j.geb.2004.09.009"/>
+    <hyperlink ref="G30" r:id="rId29" display="https://www.loc.gov/item/06005363/"/>
+    <hyperlink ref="G31" r:id="rId30" display="https://www.debian.org/devel/constitution"/>
+    <hyperlink ref="G32" r:id="rId31" display="https://doi.org/10.1086/686747"/>
+    <hyperlink ref="G33" r:id="rId32" display="https://doi.org/10.1007/s00355-015-0892-5"/>
+    <hyperlink ref="G34" r:id="rId33" display="http://data.europa.eu/eli/treaty/teu_2016/oj"/>
+    <hyperlink ref="G35" r:id="rId34" display="https://doi.org/10.1609/aimag.v31i4.2314"/>
+    <hyperlink ref="G37" r:id="rId35" display="https://doi.org/10.1007/978-3-642-20441-8_3"/>
+    <hyperlink ref="G38" r:id="rId36" display="https://doi.org/10.1137/0133030"/>
+    <hyperlink ref="G39" r:id="rId37" display="https://doi.org/10.2307/2297786"/>
+    <hyperlink ref="G40" r:id="rId38" display="https://doi.org/10.1016/0022-0531(76)90063-6"/>
+    <hyperlink ref="G41" r:id="rId39" display="https://doi.org/10.1007/3-540-33799-7"/>
+    <hyperlink ref="G42" r:id="rId40" display="https://arxiv.org/abs/2410.20476"/>
+    <hyperlink ref="G43" r:id="rId41" display="https://doi.org/10.1007/s00355-023-01505-y"/>
+    <hyperlink ref="G44" r:id="rId42" display="https://arxiv.org/abs/2506.05998"/>
+    <hyperlink ref="G45" r:id="rId43" display="https://doi.org/10.2307/1914083"/>
+    <hyperlink ref="G46" r:id="rId44" display="https://doi.org/10.1007/s11127-026-01383-9"/>
+    <hyperlink ref="G47" r:id="rId45" display="https://doi.org/10.1007/s00355-015-0909-0"/>
+    <hyperlink ref="G48" r:id="rId46" display="https://doi.org/10.2307/1910410"/>
+    <hyperlink ref="G49" r:id="rId47" display="https://doi.org/10.3406/ecoap.1952.3831"/>
+    <hyperlink ref="G50" r:id="rId48" display="https://doi.org/10.1007/BF00125914"/>
+    <hyperlink ref="G51" r:id="rId49" display="https://doi.org/10.1007/s11127-023-01042-3"/>
+    <hyperlink ref="G52" r:id="rId50" display="https://doi.org/10.1007/s10602-022-09383-9"/>
+    <hyperlink ref="G53" r:id="rId51" display="https://doi.org/10.1007/978-1-349-14540-9_4"/>
+    <hyperlink ref="G54" r:id="rId52" display="https://doi.org/10.1609/aaai.v35i6.16691"/>
+    <hyperlink ref="G55" r:id="rId53" display="https://doi.org/10.1007/s10683-010-9234-8"/>
+    <hyperlink ref="G56" r:id="rId54" display="https://doi.org/10.1257/aer.20201817"/>
+    <hyperlink ref="G57" r:id="rId55" display="https://www.jstor.org/stable/20026529"/>
+    <hyperlink ref="G58" r:id="rId56" display="https://doi.org/10.65109/hmhq1427"/>
+    <hyperlink ref="G59" r:id="rId57" display="https://doi.org/10.1007/s11127-019-00697-1"/>
+    <hyperlink ref="G60" r:id="rId58" display="https://doi.org/10.3917/neg.027.0109"/>
+    <hyperlink ref="G61" r:id="rId59" display="https://doi.org/10.1006/game.1993.1010"/>
+    <hyperlink ref="G62" r:id="rId60" display="https://doi.org/10.1002/bs.3830360303"/>
+    <hyperlink ref="G63" r:id="rId61" display="https://doi.org/10.1007/978-3-642-02839-7"/>
+    <hyperlink ref="G64" r:id="rId62" display="https://doi.org/10.1007/978-3-642-20441-8_13"/>
+    <hyperlink ref="G65" r:id="rId63" display="https://doi.org/10.1016/j.jet.2021.105261"/>
+    <hyperlink ref="G66" r:id="rId64" display="https://doi.org/10.1093/biomet/44.1-2.114"/>
+    <hyperlink ref="G67" r:id="rId65" display="https://doi.org/10.1007/978-3-642-41575-3_20"/>
+    <hyperlink ref="G68" r:id="rId66" display="https://doi.org/10.2307/1907651"/>
+    <hyperlink ref="G69" r:id="rId67" display="https://doi.org/10.1016/0022-0531(76)90040-5"/>
+    <hyperlink ref="G70" r:id="rId68" display="https://doi.org/10.2307/2110786"/>
+    <hyperlink ref="G71" r:id="rId69" display="https://doi.org/10.1257/mic.20230208"/>
+    <hyperlink ref="G72" r:id="rId70" display="https://doi.org/10.2307/2297154"/>
+    <hyperlink ref="G73" r:id="rId71" display="https://doi.org/10.2307/1912535"/>
+    <hyperlink ref="G75" r:id="rId72" display="https://doi.org/10.1016/0022-0531(88)90253-0"/>
+    <hyperlink ref="G76" r:id="rId73" display="https://doi.org/10.1016/0047-2727(78)90005-1"/>
+    <hyperlink ref="G77" r:id="rId74" display="https://doi.org/10.1007/BF01763051"/>
+    <hyperlink ref="G78" r:id="rId75" display="https://doi.org/10.1016/j.geb.2020.11.006"/>
+    <hyperlink ref="G79" r:id="rId76" display="https://doi.org/10.1016/j.geb.2025.07.010"/>
+    <hyperlink ref="G80" r:id="rId77" display="https://www.jstor.org/stable/1815369"/>
+    <hyperlink ref="G81" r:id="rId78" display="https://doi.org/10.2307/1954283"/>
+    <hyperlink ref="G82" r:id="rId79" display="https://www.loc.gov/item/2005023291/"/>
+    <hyperlink ref="G83" r:id="rId80" display="https://doi.org/10.17487/RFC7282"/>
+    <hyperlink ref="G84" r:id="rId81" display="https://doi.org/10.1007/s10602-008-9037-5"/>
+    <hyperlink ref="G85" r:id="rId82" display="https://doi.org/10.1007/BF03187594"/>
+    <hyperlink ref="G86" r:id="rId83" display="https://doi.org/10.1016/0022-0531(75)90050-2"/>
+    <hyperlink ref="G87" r:id="rId84" display="https://doi.org/10.1007/s00355-010-0475-4"/>
+    <hyperlink ref="G88" r:id="rId85" display="https://doi.org/10.1007/s003550050164"/>
+    <hyperlink ref="G89" r:id="rId86" display="https://doi.org/10.2307/1880533"/>
+    <hyperlink ref="G90" r:id="rId87" display="https://doi.org/10.2307/1914033"/>
+    <hyperlink ref="G91" r:id="rId88" display="https://doi.org/10.1007/978-3-642-20441-8_9"/>
+    <hyperlink ref="G92" r:id="rId89" display="https://doi.org/10.1007/BF00433944"/>
+    <hyperlink ref="G93" r:id="rId90" display="https://www.loc.gov/item/2006021134/"/>
+    <hyperlink ref="G94" r:id="rId91" display="https://doi.org/10.1017/S0007123400007225"/>
+    <hyperlink ref="G95" r:id="rId92" display="https://doi.org/10.1515/9781400831456"/>
+    <hyperlink ref="G96" r:id="rId93" display="https://doi.org/10.1137/0135023"/>
+    <hyperlink ref="G97" r:id="rId94" display="https://doi.org/10.1016/0022-0531(74)90073-8"/>
+    <hyperlink ref="G98" r:id="rId95" display="https://doi.org/10.2307/1961757"/>
+    <hyperlink ref="G99" r:id="rId96" display="https://doi.org/10.1007/BF00303170"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7186,7 +7216,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId92"/>
+  <drawing r:id="rId97"/>
 </worksheet>
 </file>
 
@@ -7434,7 +7464,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>205</v>
@@ -7459,7 +7489,7 @@
       <c r="T3" s="13"/>
       <c r="U3" s="13"/>
       <c r="V3" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
@@ -7474,7 +7504,7 @@
       <c r="AG3" s="13"/>
       <c r="AH3" s="13"/>
       <c r="AI3" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AJ3" s="13"/>
       <c r="AK3" s="13"/>
@@ -7485,7 +7515,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>212</v>
@@ -7515,13 +7545,13 @@
       <c r="Y4" s="13"/>
       <c r="Z4" s="13"/>
       <c r="AA4" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AB4" s="13"/>
       <c r="AC4" s="13"/>
       <c r="AD4" s="13"/>
       <c r="AE4" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AF4" s="13"/>
       <c r="AG4" s="13"/>
@@ -7536,7 +7566,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>218</v>
@@ -7562,11 +7592,11 @@
       <c r="U5" s="13"/>
       <c r="V5" s="13"/>
       <c r="W5" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="X5" s="13"/>
       <c r="Y5" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="Z5" s="13"/>
       <c r="AA5" s="13"/>
@@ -7587,7 +7617,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>224</v>
@@ -7613,11 +7643,11 @@
       <c r="U6" s="13"/>
       <c r="V6" s="13"/>
       <c r="W6" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="X6" s="13"/>
       <c r="Y6" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="Z6" s="13"/>
       <c r="AA6" s="13"/>
@@ -7638,7 +7668,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>230</v>
@@ -7666,7 +7696,7 @@
       <c r="W7" s="13"/>
       <c r="X7" s="13"/>
       <c r="Y7" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="Z7" s="13"/>
       <c r="AA7" s="13"/>
@@ -7687,7 +7717,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>236</v>
@@ -7705,7 +7735,7 @@
       <c r="M8" s="13"/>
       <c r="N8" s="13"/>
       <c r="O8" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="P8" s="13"/>
       <c r="Q8" s="13"/>
@@ -7736,10 +7766,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
@@ -7751,7 +7781,7 @@
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
       <c r="L9" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
@@ -7785,10 +7815,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
@@ -7800,7 +7830,7 @@
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
       <c r="L10" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="M10" s="13"/>
       <c r="N10" s="13"/>
@@ -7834,10 +7864,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
@@ -7868,7 +7898,7 @@
       <c r="AC11" s="13"/>
       <c r="AD11" s="13"/>
       <c r="AE11" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AF11" s="13"/>
       <c r="AG11" s="13"/>
@@ -7883,10 +7913,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C12" s="13"/>
       <c r="D12" s="13"/>
@@ -7917,7 +7947,7 @@
       <c r="AC12" s="13"/>
       <c r="AD12" s="13"/>
       <c r="AE12" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AF12" s="13"/>
       <c r="AG12" s="13"/>
@@ -7932,10 +7962,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
@@ -7954,14 +7984,14 @@
       <c r="Q13" s="13"/>
       <c r="R13" s="13"/>
       <c r="S13" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="T13" s="13"/>
       <c r="U13" s="13"/>
       <c r="V13" s="13"/>
       <c r="W13" s="13"/>
       <c r="X13" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="Y13" s="13"/>
       <c r="Z13" s="13"/>
@@ -7983,10 +8013,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
@@ -8010,10 +8040,10 @@
       <c r="V14" s="13"/>
       <c r="W14" s="13"/>
       <c r="X14" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="Y14" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="Z14" s="13"/>
       <c r="AA14" s="13"/>
@@ -8034,10 +8064,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C15" s="13"/>
       <c r="D15" s="13"/>
@@ -8046,7 +8076,7 @@
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
       <c r="I15" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="J15" s="13"/>
       <c r="K15" s="13"/>
@@ -8055,7 +8085,7 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13"/>
       <c r="P15" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="13"/>
@@ -8085,10 +8115,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
@@ -8104,7 +8134,7 @@
       <c r="N16" s="13"/>
       <c r="O16" s="13"/>
       <c r="P16" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="Q16" s="13"/>
       <c r="R16" s="13"/>
@@ -8134,13 +8164,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
@@ -8157,7 +8187,7 @@
       <c r="P17" s="13"/>
       <c r="Q17" s="13"/>
       <c r="R17" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="S17" s="13"/>
       <c r="T17" s="13"/>
@@ -8185,10 +8215,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
@@ -8214,7 +8244,7 @@
       <c r="X18" s="13"/>
       <c r="Y18" s="13"/>
       <c r="Z18" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AA18" s="13"/>
       <c r="AB18" s="13"/>
@@ -8234,10 +8264,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
@@ -8259,7 +8289,7 @@
       <c r="T19" s="13"/>
       <c r="U19" s="13"/>
       <c r="V19" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="W19" s="13"/>
       <c r="X19" s="13"/>
@@ -8274,7 +8304,7 @@
       <c r="AG19" s="13"/>
       <c r="AH19" s="13"/>
       <c r="AI19" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AJ19" s="13"/>
       <c r="AK19" s="13"/>
@@ -8285,10 +8315,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
@@ -8310,7 +8340,7 @@
       <c r="T20" s="13"/>
       <c r="U20" s="13"/>
       <c r="V20" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="W20" s="13"/>
       <c r="X20" s="13"/>
@@ -8334,10 +8364,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
@@ -8349,7 +8379,7 @@
       <c r="J21" s="13"/>
       <c r="K21" s="13"/>
       <c r="L21" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="M21" s="13"/>
       <c r="N21" s="13"/>
@@ -8383,10 +8413,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -8416,7 +8446,7 @@
       <c r="AB22" s="13"/>
       <c r="AC22" s="13"/>
       <c r="AD22" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AE22" s="13"/>
       <c r="AF22" s="13"/>
@@ -8432,10 +8462,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
@@ -8448,7 +8478,7 @@
       <c r="K23" s="13"/>
       <c r="L23" s="13"/>
       <c r="M23" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="N23" s="13"/>
       <c r="O23" s="13"/>
@@ -8481,21 +8511,21 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
       <c r="E24" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="F24" s="13"/>
       <c r="G24" s="13"/>
       <c r="H24" s="13"/>
       <c r="I24" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="J24" s="13"/>
       <c r="K24" s="13"/>
@@ -8504,7 +8534,7 @@
       <c r="N24" s="13"/>
       <c r="O24" s="13"/>
       <c r="P24" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="Q24" s="13"/>
       <c r="R24" s="13"/>
@@ -8534,10 +8564,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
@@ -8554,7 +8584,7 @@
       <c r="O25" s="13"/>
       <c r="P25" s="13"/>
       <c r="Q25" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="R25" s="13"/>
       <c r="S25" s="13"/>
@@ -8583,10 +8613,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
@@ -8608,7 +8638,7 @@
       <c r="T26" s="13"/>
       <c r="U26" s="13"/>
       <c r="V26" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="W26" s="13"/>
       <c r="X26" s="13"/>
@@ -8623,7 +8653,7 @@
       <c r="AG26" s="13"/>
       <c r="AH26" s="13"/>
       <c r="AI26" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AJ26" s="13"/>
       <c r="AK26" s="13"/>
@@ -8634,10 +8664,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -8658,11 +8688,11 @@
       <c r="S27" s="13"/>
       <c r="T27" s="13"/>
       <c r="U27" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="V27" s="13"/>
       <c r="W27" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="X27" s="13"/>
       <c r="Y27" s="13"/>
@@ -8685,10 +8715,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -8718,10 +8748,10 @@
       <c r="AB28" s="13"/>
       <c r="AC28" s="13"/>
       <c r="AD28" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AE28" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AF28" s="13"/>
       <c r="AG28" s="13"/>
@@ -8736,10 +8766,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C29" s="13"/>
       <c r="D29" s="13"/>
@@ -8759,10 +8789,10 @@
       <c r="R29" s="13"/>
       <c r="S29" s="13"/>
       <c r="T29" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="U29" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="V29" s="13"/>
       <c r="W29" s="13"/>
@@ -8787,10 +8817,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
@@ -8826,7 +8856,7 @@
       <c r="AH30" s="13"/>
       <c r="AI30" s="13"/>
       <c r="AJ30" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AK30" s="13"/>
       <c r="AL30" s="15" t="n">
@@ -8836,16 +8866,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="E31" s="13"/>
       <c r="F31" s="13"/>
@@ -8887,16 +8917,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C32" s="13"/>
       <c r="D32" s="13"/>
       <c r="E32" s="13"/>
       <c r="F32" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="G32" s="13"/>
       <c r="H32" s="13"/>
@@ -8925,7 +8955,7 @@
       <c r="AE32" s="13"/>
       <c r="AF32" s="13"/>
       <c r="AG32" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AH32" s="13"/>
       <c r="AI32" s="13"/>
@@ -8938,10 +8968,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C33" s="13"/>
       <c r="D33" s="13"/>
@@ -8964,11 +8994,11 @@
       <c r="U33" s="13"/>
       <c r="V33" s="13"/>
       <c r="W33" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="X33" s="13"/>
       <c r="Y33" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="Z33" s="13"/>
       <c r="AA33" s="13"/>
@@ -8989,10 +9019,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C34" s="13"/>
       <c r="D34" s="13"/>
@@ -9001,7 +9031,7 @@
       <c r="G34" s="13"/>
       <c r="H34" s="13"/>
       <c r="I34" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="J34" s="13"/>
       <c r="K34" s="13"/>
@@ -9038,10 +9068,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C35" s="13"/>
       <c r="D35" s="13"/>
@@ -9074,7 +9104,7 @@
       <c r="AE35" s="13"/>
       <c r="AF35" s="13"/>
       <c r="AG35" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AH35" s="13"/>
       <c r="AI35" s="13"/>
@@ -9087,10 +9117,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -9106,7 +9136,7 @@
       <c r="N36" s="13"/>
       <c r="O36" s="13"/>
       <c r="P36" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="Q36" s="13"/>
       <c r="R36" s="13"/>
@@ -9136,10 +9166,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
@@ -9151,13 +9181,13 @@
       <c r="J37" s="13"/>
       <c r="K37" s="13"/>
       <c r="L37" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="13"/>
       <c r="O37" s="13"/>
       <c r="P37" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="Q37" s="13"/>
       <c r="R37" s="13"/>
@@ -9187,10 +9217,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
@@ -9201,17 +9231,17 @@
       <c r="I38" s="13"/>
       <c r="J38" s="13"/>
       <c r="K38" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="L38" s="13"/>
       <c r="M38" s="13"/>
       <c r="N38" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="O38" s="13"/>
       <c r="P38" s="13"/>
       <c r="Q38" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="R38" s="13"/>
       <c r="S38" s="13"/>
@@ -9240,22 +9270,22 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
       <c r="E39" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="F39" s="13"/>
       <c r="G39" s="13"/>
       <c r="H39" s="13"/>
       <c r="I39" s="13"/>
       <c r="J39" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="K39" s="13"/>
       <c r="L39" s="13"/>
@@ -9291,10 +9321,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
@@ -9307,7 +9337,7 @@
       <c r="K40" s="13"/>
       <c r="L40" s="13"/>
       <c r="M40" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="N40" s="13"/>
       <c r="O40" s="13"/>
@@ -9340,14 +9370,14 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C41" s="13"/>
       <c r="D41" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="E41" s="13"/>
       <c r="F41" s="13"/>
@@ -9379,7 +9409,7 @@
       <c r="AF41" s="13"/>
       <c r="AG41" s="13"/>
       <c r="AH41" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AI41" s="13"/>
       <c r="AJ41" s="13"/>
@@ -9391,14 +9421,14 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C42" s="13"/>
       <c r="D42" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
@@ -9430,7 +9460,7 @@
       <c r="AF42" s="13"/>
       <c r="AG42" s="13"/>
       <c r="AH42" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AI42" s="13"/>
       <c r="AJ42" s="13"/>
@@ -9442,10 +9472,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C43" s="13"/>
       <c r="D43" s="13"/>
@@ -9471,7 +9501,7 @@
       <c r="X43" s="13"/>
       <c r="Y43" s="13"/>
       <c r="Z43" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AA43" s="13"/>
       <c r="AB43" s="13"/>
@@ -9491,10 +9521,10 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C44" s="13"/>
       <c r="D44" s="13"/>
@@ -9518,11 +9548,11 @@
       <c r="V44" s="13"/>
       <c r="W44" s="13"/>
       <c r="X44" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="Y44" s="13"/>
       <c r="Z44" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AA44" s="13"/>
       <c r="AB44" s="13"/>
@@ -9542,10 +9572,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C45" s="13"/>
       <c r="D45" s="13"/>
@@ -9563,7 +9593,7 @@
       <c r="P45" s="13"/>
       <c r="Q45" s="13"/>
       <c r="R45" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="S45" s="13"/>
       <c r="T45" s="13"/>
@@ -9573,7 +9603,7 @@
       <c r="X45" s="13"/>
       <c r="Y45" s="13"/>
       <c r="Z45" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AA45" s="13"/>
       <c r="AB45" s="13"/>
@@ -9593,10 +9623,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C46" s="13"/>
       <c r="D46" s="13"/>
@@ -9611,10 +9641,10 @@
       <c r="M46" s="13"/>
       <c r="N46" s="13"/>
       <c r="O46" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="P46" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="Q46" s="13"/>
       <c r="R46" s="13"/>
@@ -9644,10 +9674,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C47" s="13"/>
       <c r="D47" s="13"/>
@@ -9669,11 +9699,11 @@
       <c r="T47" s="13"/>
       <c r="U47" s="13"/>
       <c r="V47" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="W47" s="13"/>
       <c r="X47" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="Y47" s="13"/>
       <c r="Z47" s="13"/>
@@ -9695,10 +9725,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C48" s="13"/>
       <c r="D48" s="13"/>
@@ -9714,7 +9744,7 @@
       <c r="N48" s="13"/>
       <c r="O48" s="13"/>
       <c r="P48" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="Q48" s="13"/>
       <c r="R48" s="13"/>
@@ -9734,7 +9764,7 @@
       <c r="AF48" s="13"/>
       <c r="AG48" s="13"/>
       <c r="AH48" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AI48" s="13"/>
       <c r="AJ48" s="13"/>
@@ -9746,10 +9776,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C49" s="13"/>
       <c r="D49" s="13"/>
@@ -9769,7 +9799,7 @@
       <c r="R49" s="13"/>
       <c r="S49" s="13"/>
       <c r="T49" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="U49" s="13"/>
       <c r="V49" s="13"/>
@@ -9795,14 +9825,14 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C50" s="13"/>
       <c r="D50" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="E50" s="13"/>
       <c r="F50" s="13"/>
@@ -9844,10 +9874,10 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="12" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C51" s="13"/>
       <c r="D51" s="13"/>
@@ -9871,7 +9901,7 @@
       <c r="V51" s="13"/>
       <c r="W51" s="13"/>
       <c r="X51" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="Y51" s="13"/>
       <c r="Z51" s="13"/>
@@ -9893,10 +9923,10 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C52" s="13"/>
       <c r="D52" s="13"/>
@@ -9904,7 +9934,7 @@
       <c r="F52" s="13"/>
       <c r="G52" s="13"/>
       <c r="H52" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="I52" s="13"/>
       <c r="J52" s="13"/>
@@ -9912,12 +9942,12 @@
       <c r="L52" s="13"/>
       <c r="M52" s="13"/>
       <c r="N52" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="O52" s="13"/>
       <c r="P52" s="13"/>
       <c r="Q52" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="R52" s="13"/>
       <c r="S52" s="13"/>
@@ -9946,10 +9976,10 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C53" s="13"/>
       <c r="D53" s="13"/>
@@ -9957,7 +9987,7 @@
       <c r="F53" s="13"/>
       <c r="G53" s="13"/>
       <c r="H53" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="I53" s="13"/>
       <c r="J53" s="13"/>
@@ -9995,10 +10025,10 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C54" s="13"/>
       <c r="D54" s="13"/>
@@ -10028,7 +10058,7 @@
       <c r="AB54" s="13"/>
       <c r="AC54" s="13"/>
       <c r="AD54" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AE54" s="13"/>
       <c r="AF54" s="13"/>
@@ -10044,10 +10074,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C55" s="13"/>
       <c r="D55" s="13"/>
@@ -10075,7 +10105,7 @@
       <c r="Z55" s="13"/>
       <c r="AA55" s="13"/>
       <c r="AB55" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AC55" s="13"/>
       <c r="AD55" s="13"/>
@@ -10093,10 +10123,10 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C56" s="13"/>
       <c r="D56" s="13"/>
@@ -10118,10 +10148,10 @@
       <c r="T56" s="13"/>
       <c r="U56" s="13"/>
       <c r="V56" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="W56" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="X56" s="13"/>
       <c r="Y56" s="13"/>
@@ -10135,7 +10165,7 @@
       <c r="AG56" s="13"/>
       <c r="AH56" s="13"/>
       <c r="AI56" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AJ56" s="13"/>
       <c r="AK56" s="13"/>
@@ -10146,10 +10176,10 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C57" s="13"/>
       <c r="D57" s="13"/>
@@ -10186,7 +10216,7 @@
       <c r="AI57" s="13"/>
       <c r="AJ57" s="13"/>
       <c r="AK57" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AL57" s="15" t="n">
         <f aca="false">COUNTIF(C57:AK57,"x")</f>
@@ -10195,10 +10225,10 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C58" s="13"/>
       <c r="D58" s="13"/>
@@ -10207,7 +10237,7 @@
       <c r="G58" s="13"/>
       <c r="H58" s="13"/>
       <c r="I58" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="J58" s="13"/>
       <c r="K58" s="13"/>
@@ -10244,10 +10274,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C59" s="13"/>
       <c r="D59" s="13"/>
@@ -10264,7 +10294,7 @@
       <c r="O59" s="13"/>
       <c r="P59" s="13"/>
       <c r="Q59" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="R59" s="13"/>
       <c r="S59" s="13"/>
@@ -10277,7 +10307,7 @@
       <c r="Z59" s="13"/>
       <c r="AA59" s="13"/>
       <c r="AB59" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AC59" s="13"/>
       <c r="AD59" s="13"/>
@@ -10295,10 +10325,10 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C60" s="13"/>
       <c r="D60" s="13"/>
@@ -10326,10 +10356,10 @@
       <c r="Z60" s="13"/>
       <c r="AA60" s="13"/>
       <c r="AB60" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AC60" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AD60" s="13"/>
       <c r="AE60" s="13"/>
@@ -10346,10 +10376,10 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="12" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C61" s="13"/>
       <c r="D61" s="13"/>
@@ -10381,7 +10411,7 @@
       <c r="AD61" s="13"/>
       <c r="AE61" s="13"/>
       <c r="AF61" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AG61" s="13"/>
       <c r="AH61" s="13"/>
@@ -10395,15 +10425,15 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C62" s="13"/>
       <c r="D62" s="13"/>
       <c r="E62" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="F62" s="13"/>
       <c r="G62" s="13"/>
@@ -10413,7 +10443,7 @@
       <c r="K62" s="13"/>
       <c r="L62" s="13"/>
       <c r="M62" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="N62" s="13"/>
       <c r="O62" s="13"/>
@@ -10446,10 +10476,10 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="12" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C63" s="13"/>
       <c r="D63" s="13"/>
@@ -10471,7 +10501,7 @@
       <c r="T63" s="13"/>
       <c r="U63" s="13"/>
       <c r="V63" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="W63" s="13"/>
       <c r="X63" s="13"/>
@@ -10486,7 +10516,7 @@
       <c r="AG63" s="13"/>
       <c r="AH63" s="13"/>
       <c r="AI63" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AJ63" s="13"/>
       <c r="AK63" s="13"/>
@@ -10497,10 +10527,10 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C64" s="13"/>
       <c r="D64" s="13"/>
@@ -10512,7 +10542,7 @@
       <c r="J64" s="13"/>
       <c r="K64" s="13"/>
       <c r="L64" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="M64" s="13"/>
       <c r="N64" s="13"/>
@@ -10546,10 +10576,10 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="12" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C65" s="13"/>
       <c r="D65" s="13"/>
@@ -10560,10 +10590,10 @@
       <c r="I65" s="13"/>
       <c r="J65" s="13"/>
       <c r="K65" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="L65" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="M65" s="13"/>
       <c r="N65" s="13"/>
@@ -10587,7 +10617,7 @@
       <c r="AF65" s="13"/>
       <c r="AG65" s="13"/>
       <c r="AH65" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AI65" s="13"/>
       <c r="AJ65" s="13"/>
@@ -10599,10 +10629,10 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C66" s="13"/>
       <c r="D66" s="13"/>
@@ -10633,7 +10663,7 @@
       <c r="AC66" s="13"/>
       <c r="AD66" s="13"/>
       <c r="AE66" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AF66" s="13"/>
       <c r="AG66" s="13"/>
@@ -10648,10 +10678,10 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="12" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C67" s="13"/>
       <c r="D67" s="13"/>
@@ -10685,7 +10715,7 @@
       <c r="AF67" s="13"/>
       <c r="AG67" s="13"/>
       <c r="AH67" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AI67" s="13"/>
       <c r="AJ67" s="13"/>
@@ -10697,10 +10727,10 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="12" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C68" s="13"/>
       <c r="D68" s="13"/>
@@ -10734,7 +10764,7 @@
       <c r="AF68" s="13"/>
       <c r="AG68" s="13"/>
       <c r="AH68" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AI68" s="13"/>
       <c r="AJ68" s="13"/>
@@ -10746,13 +10776,13 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="12" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="D69" s="13"/>
       <c r="E69" s="13"/>
@@ -10795,10 +10825,10 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="12" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="C70" s="13"/>
       <c r="D70" s="13"/>
@@ -10817,14 +10847,14 @@
       <c r="Q70" s="13"/>
       <c r="R70" s="13"/>
       <c r="S70" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="T70" s="13"/>
       <c r="U70" s="13"/>
       <c r="V70" s="13"/>
       <c r="W70" s="13"/>
       <c r="X70" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="Y70" s="13"/>
       <c r="Z70" s="13"/>
@@ -10846,10 +10876,10 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="12" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C71" s="13"/>
       <c r="D71" s="13"/>
@@ -10860,7 +10890,7 @@
       <c r="I71" s="13"/>
       <c r="J71" s="13"/>
       <c r="K71" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="L71" s="13"/>
       <c r="M71" s="13"/>
@@ -10885,7 +10915,7 @@
       <c r="AF71" s="13"/>
       <c r="AG71" s="13"/>
       <c r="AH71" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AI71" s="13"/>
       <c r="AJ71" s="13"/>
@@ -10897,10 +10927,10 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C72" s="13"/>
       <c r="D72" s="13"/>
@@ -10922,7 +10952,7 @@
       <c r="T72" s="13"/>
       <c r="U72" s="13"/>
       <c r="V72" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="W72" s="13"/>
       <c r="X72" s="13"/>
@@ -10946,10 +10976,10 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="12" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C73" s="13"/>
       <c r="D73" s="13"/>
@@ -10977,7 +11007,7 @@
       <c r="Z73" s="13"/>
       <c r="AA73" s="13"/>
       <c r="AB73" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AC73" s="13"/>
       <c r="AD73" s="13"/>
@@ -10995,10 +11025,10 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C74" s="13"/>
       <c r="D74" s="13"/>
@@ -11025,10 +11055,10 @@
       <c r="Y74" s="13"/>
       <c r="Z74" s="13"/>
       <c r="AA74" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AB74" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AC74" s="13"/>
       <c r="AD74" s="13"/>
@@ -11046,10 +11076,10 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="12" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C75" s="13"/>
       <c r="D75" s="13"/>
@@ -11064,7 +11094,7 @@
       <c r="M75" s="13"/>
       <c r="N75" s="13"/>
       <c r="O75" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="P75" s="13"/>
       <c r="Q75" s="13"/>
@@ -11078,10 +11108,10 @@
       <c r="Y75" s="13"/>
       <c r="Z75" s="13"/>
       <c r="AA75" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AB75" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AC75" s="13"/>
       <c r="AD75" s="13"/>
@@ -11099,13 +11129,13 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="D76" s="13"/>
       <c r="E76" s="13"/>
@@ -11121,7 +11151,7 @@
       <c r="O76" s="13"/>
       <c r="P76" s="13"/>
       <c r="Q76" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="R76" s="13"/>
       <c r="S76" s="13"/>
@@ -11150,10 +11180,10 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="12" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C77" s="13"/>
       <c r="D77" s="13"/>
@@ -11180,7 +11210,7 @@
       <c r="Y77" s="13"/>
       <c r="Z77" s="13"/>
       <c r="AA77" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AB77" s="13"/>
       <c r="AC77" s="13"/>
@@ -11199,10 +11229,10 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="C78" s="13"/>
       <c r="D78" s="13"/>
@@ -11222,12 +11252,12 @@
       <c r="R78" s="13"/>
       <c r="S78" s="13"/>
       <c r="T78" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="U78" s="13"/>
       <c r="V78" s="13"/>
       <c r="W78" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="X78" s="13"/>
       <c r="Y78" s="13"/>
@@ -11250,10 +11280,10 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="12" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="C79" s="13"/>
       <c r="D79" s="13"/>
@@ -11276,11 +11306,11 @@
       <c r="U79" s="13"/>
       <c r="V79" s="13"/>
       <c r="W79" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="X79" s="13"/>
       <c r="Y79" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="Z79" s="13"/>
       <c r="AA79" s="13"/>
@@ -11292,7 +11322,7 @@
       <c r="AG79" s="13"/>
       <c r="AH79" s="13"/>
       <c r="AI79" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AJ79" s="13"/>
       <c r="AK79" s="13"/>
@@ -11303,10 +11333,10 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="C80" s="13"/>
       <c r="D80" s="13"/>
@@ -11328,7 +11358,7 @@
       <c r="T80" s="13"/>
       <c r="U80" s="13"/>
       <c r="V80" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="W80" s="13"/>
       <c r="X80" s="13"/>
@@ -11343,7 +11373,7 @@
       <c r="AG80" s="13"/>
       <c r="AH80" s="13"/>
       <c r="AI80" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AJ80" s="13"/>
       <c r="AK80" s="13"/>
@@ -11354,10 +11384,10 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="12" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C81" s="13"/>
       <c r="D81" s="13"/>
@@ -11376,10 +11406,10 @@
       <c r="Q81" s="13"/>
       <c r="R81" s="13"/>
       <c r="S81" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="T81" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="U81" s="13"/>
       <c r="V81" s="13"/>
@@ -11405,13 +11435,13 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="D82" s="13"/>
       <c r="E82" s="13"/>
@@ -11431,7 +11461,7 @@
       <c r="S82" s="13"/>
       <c r="T82" s="13"/>
       <c r="U82" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="V82" s="13"/>
       <c r="W82" s="13"/>
@@ -11456,14 +11486,14 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="12" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="C83" s="13"/>
       <c r="D83" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="E83" s="13"/>
       <c r="F83" s="13"/>
@@ -11495,7 +11525,7 @@
       <c r="AF83" s="13"/>
       <c r="AG83" s="13"/>
       <c r="AH83" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AI83" s="13"/>
       <c r="AJ83" s="13"/>
@@ -11507,10 +11537,10 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="C84" s="13"/>
       <c r="D84" s="13"/>
@@ -11542,7 +11572,7 @@
       <c r="AD84" s="13"/>
       <c r="AE84" s="13"/>
       <c r="AF84" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AG84" s="13"/>
       <c r="AH84" s="13"/>
@@ -11556,10 +11586,10 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="12" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="C85" s="13"/>
       <c r="D85" s="13"/>
@@ -11582,7 +11612,7 @@
       <c r="U85" s="13"/>
       <c r="V85" s="13"/>
       <c r="W85" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="X85" s="13"/>
       <c r="Y85" s="13"/>
@@ -11594,7 +11624,7 @@
       <c r="AE85" s="13"/>
       <c r="AF85" s="13"/>
       <c r="AG85" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AH85" s="13"/>
       <c r="AI85" s="13"/>
@@ -11607,10 +11637,10 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="12" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="C86" s="13"/>
       <c r="D86" s="13"/>
@@ -11633,10 +11663,10 @@
       <c r="U86" s="13"/>
       <c r="V86" s="13"/>
       <c r="W86" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="X86" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="Y86" s="13"/>
       <c r="Z86" s="13"/>
@@ -11658,10 +11688,10 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="12" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="C87" s="13"/>
       <c r="D87" s="13"/>
@@ -11676,10 +11706,10 @@
       <c r="M87" s="13"/>
       <c r="N87" s="13"/>
       <c r="O87" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="P87" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="Q87" s="13"/>
       <c r="R87" s="13"/>
@@ -11709,18 +11739,18 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="12" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C88" s="13"/>
       <c r="D88" s="13"/>
       <c r="E88" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="F88" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="G88" s="13"/>
       <c r="H88" s="13"/>
@@ -11730,7 +11760,7 @@
       <c r="L88" s="13"/>
       <c r="M88" s="13"/>
       <c r="N88" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="O88" s="13"/>
       <c r="P88" s="13"/>
@@ -11762,10 +11792,10 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="12" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="C89" s="13"/>
       <c r="D89" s="13"/>
@@ -11795,7 +11825,7 @@
       <c r="AB89" s="13"/>
       <c r="AC89" s="13"/>
       <c r="AD89" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AE89" s="13"/>
       <c r="AF89" s="13"/>
@@ -11811,10 +11841,10 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="12" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="C90" s="13"/>
       <c r="D90" s="13"/>
@@ -11824,7 +11854,7 @@
       <c r="H90" s="13"/>
       <c r="I90" s="13"/>
       <c r="J90" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="K90" s="13"/>
       <c r="L90" s="13"/>
@@ -11860,15 +11890,15 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="12" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="C91" s="13"/>
       <c r="D91" s="13"/>
       <c r="E91" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="F91" s="13"/>
       <c r="G91" s="13"/>
@@ -11909,14 +11939,14 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="12" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="C92" s="13"/>
       <c r="D92" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="E92" s="13"/>
       <c r="F92" s="13"/>
@@ -11948,7 +11978,7 @@
       <c r="AF92" s="13"/>
       <c r="AG92" s="13"/>
       <c r="AH92" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AI92" s="13"/>
       <c r="AJ92" s="13"/>
@@ -11960,28 +11990,28 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="12" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="C93" s="13"/>
       <c r="D93" s="13"/>
       <c r="E93" s="13"/>
       <c r="F93" s="13"/>
       <c r="G93" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="H93" s="13"/>
       <c r="I93" s="13"/>
       <c r="J93" s="13"/>
       <c r="K93" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="L93" s="13"/>
       <c r="M93" s="13"/>
       <c r="N93" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="O93" s="13"/>
       <c r="P93" s="13"/>
@@ -12013,19 +12043,19 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="12" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C94" s="13"/>
       <c r="D94" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="E94" s="13"/>
       <c r="F94" s="13"/>
       <c r="G94" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="H94" s="13"/>
       <c r="I94" s="13"/>
@@ -12054,7 +12084,7 @@
       <c r="AF94" s="13"/>
       <c r="AG94" s="13"/>
       <c r="AH94" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AI94" s="13"/>
       <c r="AJ94" s="13"/>
@@ -12066,10 +12096,10 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="12" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="C95" s="13"/>
       <c r="D95" s="13"/>
@@ -12092,7 +12122,7 @@
       <c r="U95" s="13"/>
       <c r="V95" s="13"/>
       <c r="W95" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="X95" s="13"/>
       <c r="Y95" s="13"/>
@@ -12115,10 +12145,10 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="12" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="C96" s="13"/>
       <c r="D96" s="13"/>
@@ -12141,7 +12171,7 @@
       <c r="U96" s="13"/>
       <c r="V96" s="13"/>
       <c r="W96" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="X96" s="13"/>
       <c r="Y96" s="13"/>
@@ -12164,13 +12194,13 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="12" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="C97" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="D97" s="13"/>
       <c r="E97" s="13"/>
@@ -12178,7 +12208,7 @@
       <c r="G97" s="13"/>
       <c r="H97" s="13"/>
       <c r="I97" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="J97" s="13"/>
       <c r="K97" s="13"/>
@@ -12215,10 +12245,10 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="12" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="C98" s="13"/>
       <c r="D98" s="13"/>
@@ -12229,7 +12259,7 @@
       <c r="I98" s="13"/>
       <c r="J98" s="13"/>
       <c r="K98" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="L98" s="13"/>
       <c r="M98" s="13"/>
@@ -12264,13 +12294,13 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="12" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="C99" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="D99" s="13"/>
       <c r="E99" s="13"/>
@@ -12278,7 +12308,7 @@
       <c r="G99" s="13"/>
       <c r="H99" s="13"/>
       <c r="I99" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="J99" s="13"/>
       <c r="K99" s="13"/>
@@ -12315,17 +12345,17 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="12" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="C100" s="13"/>
       <c r="D100" s="13"/>
       <c r="E100" s="13"/>
       <c r="F100" s="13"/>
       <c r="G100" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="H100" s="13"/>
       <c r="I100" s="13"/>
@@ -12334,7 +12364,7 @@
       <c r="L100" s="13"/>
       <c r="M100" s="13"/>
       <c r="N100" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="O100" s="13"/>
       <c r="P100" s="13"/>

--- a/literature/concept-map/concept-map.xlsx
+++ b/literature/concept-map/concept-map.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="893">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="892">
   <si>
     <t xml:space="preserve">Concept map of the note “Voting for a consensus with veto rights” (v0.1)</t>
   </si>
@@ -1441,7 +1441,7 @@
     <t xml:space="preserve">Felsenthal, D. S. &amp; Machover, M. (2008). The Majority Judgement Voting Procedure: A Critical Evaluation. Homo Oeconomicus 25(3/4): 319–334.</t>
   </si>
   <si>
-    <t xml:space="preserve">Not checked against the journal's record: no Crossref record; the LSE repository record (eprints.lse.ac.uk/24213) is not reachable from the checking environment. Felsenthal (2012, doi 10.1007/978-3-642-20441-8_3) gives pages 319-333; Balinski and Laraki (2014, doi 10.1287/opre.2014.1269) give 25, first page 319</t>
+    <t xml:space="preserve">https://researchonline.lse.ac.uk/id/eprint/24213/</t>
   </si>
   <si>
     <t xml:space="preserve">Felsenthal (2012). Review of Paradoxes Afflicting Procedures for Electing a Single Candidate</t>
@@ -2256,9 +2256,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.jstor.org/stable/1815369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not checked against the journal's record: no Crossref record, and JSTOR 1815369 refuses automated access. McKelvey (1976, doi 10.1016/0022-0531(76)90040-5) cites it as Amer. Econ. Rev. 57, 1967</t>
   </si>
   <si>
     <t xml:space="preserve">Rae (1969). Decision-Rules and Individual Values in Constitutional Choice</t>
@@ -5315,7 +5312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
         <v>416</v>
       </c>
@@ -5334,10 +5331,10 @@
       <c r="F36" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8" t="s">
+      <c r="G36" s="9" t="s">
         <v>421</v>
       </c>
+      <c r="H36" s="8"/>
       <c r="I36" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D36,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>2</v>
@@ -6547,7 +6544,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="s">
         <v>678</v>
       </c>
@@ -6569,9 +6566,7 @@
       <c r="G80" s="9" t="s">
         <v>683</v>
       </c>
-      <c r="H80" s="8" t="s">
-        <v>684</v>
-      </c>
+      <c r="H80" s="8"/>
       <c r="I80" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D80,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>2</v>
@@ -6579,25 +6574,25 @@
     </row>
     <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="s">
+        <v>684</v>
+      </c>
+      <c r="B81" s="8" t="s">
         <v>685</v>
       </c>
-      <c r="B81" s="8" t="s">
+      <c r="C81" s="8" t="s">
         <v>686</v>
       </c>
-      <c r="C81" s="8" t="s">
+      <c r="D81" s="8" t="s">
         <v>687</v>
-      </c>
-      <c r="D81" s="8" t="s">
-        <v>688</v>
       </c>
       <c r="E81" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F81" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="G81" s="9" t="s">
         <v>689</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>690</v>
       </c>
       <c r="H81" s="8"/>
       <c r="I81" s="8" t="n">
@@ -6607,25 +6602,25 @@
     </row>
     <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B82" s="8" t="s">
         <v>441</v>
       </c>
       <c r="C82" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="D82" s="8" t="s">
         <v>692</v>
-      </c>
-      <c r="D82" s="8" t="s">
-        <v>693</v>
       </c>
       <c r="E82" s="8" t="s">
         <v>615</v>
       </c>
       <c r="F82" s="8" t="s">
+        <v>693</v>
+      </c>
+      <c r="G82" s="9" t="s">
         <v>694</v>
-      </c>
-      <c r="G82" s="9" t="s">
-        <v>695</v>
       </c>
       <c r="H82" s="8"/>
       <c r="I82" s="8" t="n">
@@ -6635,25 +6630,25 @@
     </row>
     <row r="83" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B83" s="8" t="s">
         <v>560</v>
       </c>
       <c r="C83" s="8" t="s">
+        <v>696</v>
+      </c>
+      <c r="D83" s="8" t="s">
         <v>697</v>
-      </c>
-      <c r="D83" s="8" t="s">
-        <v>698</v>
       </c>
       <c r="E83" s="8" t="s">
         <v>349</v>
       </c>
       <c r="F83" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="G83" s="9" t="s">
         <v>699</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>700</v>
       </c>
       <c r="H83" s="8"/>
       <c r="I83" s="8" t="n">
@@ -6663,25 +6658,25 @@
     </row>
     <row r="84" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="B84" s="8" t="s">
         <v>701</v>
       </c>
-      <c r="B84" s="8" t="s">
+      <c r="C84" s="8" t="s">
         <v>702</v>
       </c>
-      <c r="C84" s="8" t="s">
+      <c r="D84" s="8" t="s">
         <v>703</v>
-      </c>
-      <c r="D84" s="8" t="s">
-        <v>704</v>
       </c>
       <c r="E84" s="8" t="s">
         <v>628</v>
       </c>
       <c r="F84" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="G84" s="9" t="s">
         <v>705</v>
-      </c>
-      <c r="G84" s="9" t="s">
-        <v>706</v>
       </c>
       <c r="H84" s="8"/>
       <c r="I84" s="8" t="n">
@@ -6691,25 +6686,25 @@
     </row>
     <row r="85" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="s">
+        <v>706</v>
+      </c>
+      <c r="B85" s="8" t="s">
         <v>707</v>
       </c>
-      <c r="B85" s="8" t="s">
+      <c r="C85" s="8" t="s">
         <v>708</v>
       </c>
-      <c r="C85" s="8" t="s">
+      <c r="D85" s="8" t="s">
         <v>709</v>
-      </c>
-      <c r="D85" s="8" t="s">
-        <v>710</v>
       </c>
       <c r="E85" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F85" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="G85" s="9" t="s">
         <v>711</v>
-      </c>
-      <c r="G85" s="9" t="s">
-        <v>712</v>
       </c>
       <c r="H85" s="8"/>
       <c r="I85" s="8" t="n">
@@ -6719,25 +6714,25 @@
     </row>
     <row r="86" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B86" s="8" t="s">
         <v>469</v>
       </c>
       <c r="C86" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="D86" s="8" t="s">
         <v>714</v>
-      </c>
-      <c r="D86" s="8" t="s">
-        <v>715</v>
       </c>
       <c r="E86" s="8" t="s">
         <v>472</v>
       </c>
       <c r="F86" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="G86" s="9" t="s">
         <v>716</v>
-      </c>
-      <c r="G86" s="9" t="s">
-        <v>717</v>
       </c>
       <c r="H86" s="8"/>
       <c r="I86" s="8" t="n">
@@ -6747,25 +6742,25 @@
     </row>
     <row r="87" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="s">
+        <v>717</v>
+      </c>
+      <c r="B87" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="C87" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C87" s="8" t="s">
+      <c r="D87" s="8" t="s">
         <v>720</v>
       </c>
-      <c r="D87" s="8" t="s">
+      <c r="E87" s="8" t="s">
         <v>721</v>
       </c>
-      <c r="E87" s="8" t="s">
+      <c r="F87" s="8" t="s">
         <v>722</v>
       </c>
-      <c r="F87" s="8" t="s">
+      <c r="G87" s="9" t="s">
         <v>723</v>
-      </c>
-      <c r="G87" s="9" t="s">
-        <v>724</v>
       </c>
       <c r="H87" s="8"/>
       <c r="I87" s="8" t="n">
@@ -6775,25 +6770,25 @@
     </row>
     <row r="88" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B88" s="8" t="s">
         <v>322</v>
       </c>
       <c r="C88" s="8" t="s">
+        <v>725</v>
+      </c>
+      <c r="D88" s="8" t="s">
         <v>726</v>
-      </c>
-      <c r="D88" s="8" t="s">
-        <v>727</v>
       </c>
       <c r="E88" s="8" t="s">
         <v>408</v>
       </c>
       <c r="F88" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="G88" s="9" t="s">
         <v>728</v>
-      </c>
-      <c r="G88" s="9" t="s">
-        <v>729</v>
       </c>
       <c r="H88" s="8"/>
       <c r="I88" s="8" t="n">
@@ -6803,25 +6798,25 @@
     </row>
     <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="s">
+        <v>729</v>
+      </c>
+      <c r="B89" s="8" t="s">
         <v>730</v>
       </c>
-      <c r="B89" s="8" t="s">
+      <c r="C89" s="8" t="s">
         <v>731</v>
       </c>
-      <c r="C89" s="8" t="s">
+      <c r="D89" s="8" t="s">
         <v>732</v>
-      </c>
-      <c r="D89" s="8" t="s">
-        <v>733</v>
       </c>
       <c r="E89" s="8" t="s">
         <v>281</v>
       </c>
       <c r="F89" s="8" t="s">
+        <v>733</v>
+      </c>
+      <c r="G89" s="9" t="s">
         <v>734</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>735</v>
       </c>
       <c r="H89" s="8"/>
       <c r="I89" s="8" t="n">
@@ -6831,25 +6826,25 @@
     </row>
     <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="s">
+        <v>735</v>
+      </c>
+      <c r="B90" s="8" t="s">
         <v>736</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="C90" s="8" t="s">
         <v>737</v>
       </c>
-      <c r="C90" s="8" t="s">
+      <c r="D90" s="8" t="s">
         <v>738</v>
-      </c>
-      <c r="D90" s="8" t="s">
-        <v>739</v>
       </c>
       <c r="E90" s="8" t="s">
         <v>432</v>
       </c>
       <c r="F90" s="8" t="s">
+        <v>739</v>
+      </c>
+      <c r="G90" s="9" t="s">
         <v>740</v>
-      </c>
-      <c r="G90" s="9" t="s">
-        <v>741</v>
       </c>
       <c r="H90" s="8"/>
       <c r="I90" s="8" t="n">
@@ -6859,25 +6854,25 @@
     </row>
     <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="s">
+        <v>741</v>
+      </c>
+      <c r="B91" s="8" t="s">
         <v>742</v>
       </c>
-      <c r="B91" s="8" t="s">
+      <c r="C91" s="8" t="s">
         <v>743</v>
       </c>
-      <c r="C91" s="8" t="s">
+      <c r="D91" s="8" t="s">
         <v>744</v>
-      </c>
-      <c r="D91" s="8" t="s">
-        <v>745</v>
       </c>
       <c r="E91" s="8" t="s">
         <v>615</v>
       </c>
       <c r="F91" s="8" t="s">
+        <v>745</v>
+      </c>
+      <c r="G91" s="9" t="s">
         <v>746</v>
-      </c>
-      <c r="G91" s="9" t="s">
-        <v>747</v>
       </c>
       <c r="H91" s="8"/>
       <c r="I91" s="8" t="n">
@@ -6887,25 +6882,25 @@
     </row>
     <row r="92" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="s">
+        <v>747</v>
+      </c>
+      <c r="B92" s="8" t="s">
         <v>748</v>
       </c>
-      <c r="B92" s="8" t="s">
+      <c r="C92" s="8" t="s">
         <v>749</v>
       </c>
-      <c r="C92" s="8" t="s">
+      <c r="D92" s="8" t="s">
         <v>750</v>
       </c>
-      <c r="D92" s="8" t="s">
+      <c r="E92" s="8" t="s">
         <v>751</v>
       </c>
-      <c r="E92" s="8" t="s">
+      <c r="F92" s="8" t="s">
         <v>752</v>
       </c>
-      <c r="F92" s="8" t="s">
+      <c r="G92" s="9" t="s">
         <v>753</v>
-      </c>
-      <c r="G92" s="9" t="s">
-        <v>754</v>
       </c>
       <c r="H92" s="8"/>
       <c r="I92" s="8" t="n">
@@ -6915,25 +6910,25 @@
     </row>
     <row r="93" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="s">
+        <v>754</v>
+      </c>
+      <c r="B93" s="8" t="s">
         <v>755</v>
       </c>
-      <c r="B93" s="8" t="s">
+      <c r="C93" s="8" t="s">
         <v>756</v>
       </c>
-      <c r="C93" s="8" t="s">
+      <c r="D93" s="8" t="s">
         <v>757</v>
-      </c>
-      <c r="D93" s="8" t="s">
-        <v>758</v>
       </c>
       <c r="E93" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F93" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="G93" s="9" t="s">
         <v>759</v>
-      </c>
-      <c r="G93" s="9" t="s">
-        <v>760</v>
       </c>
       <c r="H93" s="8"/>
       <c r="I93" s="8" t="n">
@@ -6943,25 +6938,25 @@
     </row>
     <row r="94" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="s">
+        <v>760</v>
+      </c>
+      <c r="B94" s="8" t="s">
         <v>761</v>
       </c>
-      <c r="B94" s="8" t="s">
+      <c r="C94" s="8" t="s">
         <v>762</v>
       </c>
-      <c r="C94" s="8" t="s">
+      <c r="D94" s="8" t="s">
         <v>763</v>
-      </c>
-      <c r="D94" s="8" t="s">
-        <v>764</v>
       </c>
       <c r="E94" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F94" s="8" t="s">
+        <v>764</v>
+      </c>
+      <c r="G94" s="9" t="s">
         <v>765</v>
-      </c>
-      <c r="G94" s="9" t="s">
-        <v>766</v>
       </c>
       <c r="H94" s="8"/>
       <c r="I94" s="8" t="n">
@@ -6971,25 +6966,25 @@
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="s">
+        <v>766</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>761</v>
+      </c>
+      <c r="C95" s="8" t="s">
         <v>767</v>
       </c>
-      <c r="B95" s="8" t="s">
-        <v>762</v>
-      </c>
-      <c r="C95" s="8" t="s">
+      <c r="D95" s="8" t="s">
         <v>768</v>
       </c>
-      <c r="D95" s="8" t="s">
+      <c r="E95" s="8" t="s">
         <v>769</v>
       </c>
-      <c r="E95" s="8" t="s">
+      <c r="F95" s="8" t="s">
         <v>770</v>
       </c>
-      <c r="F95" s="8" t="s">
+      <c r="G95" s="9" t="s">
         <v>771</v>
-      </c>
-      <c r="G95" s="9" t="s">
-        <v>772</v>
       </c>
       <c r="H95" s="8"/>
       <c r="I95" s="8" t="n">
@@ -6999,25 +6994,25 @@
     </row>
     <row r="96" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="s">
+        <v>772</v>
+      </c>
+      <c r="B96" s="8" t="s">
         <v>773</v>
       </c>
-      <c r="B96" s="8" t="s">
+      <c r="C96" s="8" t="s">
         <v>774</v>
       </c>
-      <c r="C96" s="8" t="s">
+      <c r="D96" s="8" t="s">
         <v>775</v>
-      </c>
-      <c r="D96" s="8" t="s">
-        <v>776</v>
       </c>
       <c r="E96" s="8" t="s">
         <v>281</v>
       </c>
       <c r="F96" s="8" t="s">
+        <v>776</v>
+      </c>
+      <c r="G96" s="9" t="s">
         <v>777</v>
-      </c>
-      <c r="G96" s="9" t="s">
-        <v>778</v>
       </c>
       <c r="H96" s="8"/>
       <c r="I96" s="8" t="n">
@@ -7027,25 +7022,25 @@
     </row>
     <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="B97" s="8" t="s">
         <v>779</v>
       </c>
-      <c r="B97" s="8" t="s">
+      <c r="C97" s="8" t="s">
         <v>780</v>
       </c>
-      <c r="C97" s="8" t="s">
+      <c r="D97" s="8" t="s">
         <v>781</v>
-      </c>
-      <c r="D97" s="8" t="s">
-        <v>782</v>
       </c>
       <c r="E97" s="8" t="s">
         <v>244</v>
       </c>
       <c r="F97" s="8" t="s">
+        <v>782</v>
+      </c>
+      <c r="G97" s="9" t="s">
         <v>783</v>
-      </c>
-      <c r="G97" s="9" t="s">
-        <v>784</v>
       </c>
       <c r="H97" s="8"/>
       <c r="I97" s="8" t="n">
@@ -7055,25 +7050,25 @@
     </row>
     <row r="98" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="s">
+        <v>784</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>773</v>
+      </c>
+      <c r="C98" s="8" t="s">
         <v>785</v>
       </c>
-      <c r="B98" s="8" t="s">
-        <v>774</v>
-      </c>
-      <c r="C98" s="8" t="s">
+      <c r="D98" s="8" t="s">
         <v>786</v>
-      </c>
-      <c r="D98" s="8" t="s">
-        <v>787</v>
       </c>
       <c r="E98" s="8" t="s">
         <v>432</v>
       </c>
       <c r="F98" s="8" t="s">
+        <v>787</v>
+      </c>
+      <c r="G98" s="9" t="s">
         <v>788</v>
-      </c>
-      <c r="G98" s="9" t="s">
-        <v>789</v>
       </c>
       <c r="H98" s="8"/>
       <c r="I98" s="8" t="n">
@@ -7083,25 +7078,25 @@
     </row>
     <row r="99" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="s">
+        <v>789</v>
+      </c>
+      <c r="B99" s="8" t="s">
         <v>790</v>
       </c>
-      <c r="B99" s="8" t="s">
+      <c r="C99" s="8" t="s">
         <v>791</v>
       </c>
-      <c r="C99" s="8" t="s">
+      <c r="D99" s="8" t="s">
         <v>792</v>
-      </c>
-      <c r="D99" s="8" t="s">
-        <v>793</v>
       </c>
       <c r="E99" s="8" t="s">
         <v>281</v>
       </c>
       <c r="F99" s="8" t="s">
+        <v>793</v>
+      </c>
+      <c r="G99" s="9" t="s">
         <v>794</v>
-      </c>
-      <c r="G99" s="9" t="s">
-        <v>795</v>
       </c>
       <c r="H99" s="8"/>
       <c r="I99" s="8" t="n">
@@ -7146,68 +7141,69 @@
     <hyperlink ref="G33" r:id="rId32" display="https://doi.org/10.1007/s00355-015-0892-5"/>
     <hyperlink ref="G34" r:id="rId33" display="http://data.europa.eu/eli/treaty/teu_2016/oj"/>
     <hyperlink ref="G35" r:id="rId34" display="https://doi.org/10.1609/aimag.v31i4.2314"/>
-    <hyperlink ref="G37" r:id="rId35" display="https://doi.org/10.1007/978-3-642-20441-8_3"/>
-    <hyperlink ref="G38" r:id="rId36" display="https://doi.org/10.1137/0133030"/>
-    <hyperlink ref="G39" r:id="rId37" display="https://doi.org/10.2307/2297786"/>
-    <hyperlink ref="G40" r:id="rId38" display="https://doi.org/10.1016/0022-0531(76)90063-6"/>
-    <hyperlink ref="G41" r:id="rId39" display="https://doi.org/10.1007/3-540-33799-7"/>
-    <hyperlink ref="G42" r:id="rId40" display="https://arxiv.org/abs/2410.20476"/>
-    <hyperlink ref="G43" r:id="rId41" display="https://doi.org/10.1007/s00355-023-01505-y"/>
-    <hyperlink ref="G44" r:id="rId42" display="https://arxiv.org/abs/2506.05998"/>
-    <hyperlink ref="G45" r:id="rId43" display="https://doi.org/10.2307/1914083"/>
-    <hyperlink ref="G46" r:id="rId44" display="https://doi.org/10.1007/s11127-026-01383-9"/>
-    <hyperlink ref="G47" r:id="rId45" display="https://doi.org/10.1007/s00355-015-0909-0"/>
-    <hyperlink ref="G48" r:id="rId46" display="https://doi.org/10.2307/1910410"/>
-    <hyperlink ref="G49" r:id="rId47" display="https://doi.org/10.3406/ecoap.1952.3831"/>
-    <hyperlink ref="G50" r:id="rId48" display="https://doi.org/10.1007/BF00125914"/>
-    <hyperlink ref="G51" r:id="rId49" display="https://doi.org/10.1007/s11127-023-01042-3"/>
-    <hyperlink ref="G52" r:id="rId50" display="https://doi.org/10.1007/s10602-022-09383-9"/>
-    <hyperlink ref="G53" r:id="rId51" display="https://doi.org/10.1007/978-1-349-14540-9_4"/>
-    <hyperlink ref="G54" r:id="rId52" display="https://doi.org/10.1609/aaai.v35i6.16691"/>
-    <hyperlink ref="G55" r:id="rId53" display="https://doi.org/10.1007/s10683-010-9234-8"/>
-    <hyperlink ref="G56" r:id="rId54" display="https://doi.org/10.1257/aer.20201817"/>
-    <hyperlink ref="G57" r:id="rId55" display="https://www.jstor.org/stable/20026529"/>
-    <hyperlink ref="G58" r:id="rId56" display="https://doi.org/10.65109/hmhq1427"/>
-    <hyperlink ref="G59" r:id="rId57" display="https://doi.org/10.1007/s11127-019-00697-1"/>
-    <hyperlink ref="G60" r:id="rId58" display="https://doi.org/10.3917/neg.027.0109"/>
-    <hyperlink ref="G61" r:id="rId59" display="https://doi.org/10.1006/game.1993.1010"/>
-    <hyperlink ref="G62" r:id="rId60" display="https://doi.org/10.1002/bs.3830360303"/>
-    <hyperlink ref="G63" r:id="rId61" display="https://doi.org/10.1007/978-3-642-02839-7"/>
-    <hyperlink ref="G64" r:id="rId62" display="https://doi.org/10.1007/978-3-642-20441-8_13"/>
-    <hyperlink ref="G65" r:id="rId63" display="https://doi.org/10.1016/j.jet.2021.105261"/>
-    <hyperlink ref="G66" r:id="rId64" display="https://doi.org/10.1093/biomet/44.1-2.114"/>
-    <hyperlink ref="G67" r:id="rId65" display="https://doi.org/10.1007/978-3-642-41575-3_20"/>
-    <hyperlink ref="G68" r:id="rId66" display="https://doi.org/10.2307/1907651"/>
-    <hyperlink ref="G69" r:id="rId67" display="https://doi.org/10.1016/0022-0531(76)90040-5"/>
-    <hyperlink ref="G70" r:id="rId68" display="https://doi.org/10.2307/2110786"/>
-    <hyperlink ref="G71" r:id="rId69" display="https://doi.org/10.1257/mic.20230208"/>
-    <hyperlink ref="G72" r:id="rId70" display="https://doi.org/10.2307/2297154"/>
-    <hyperlink ref="G73" r:id="rId71" display="https://doi.org/10.2307/1912535"/>
-    <hyperlink ref="G75" r:id="rId72" display="https://doi.org/10.1016/0022-0531(88)90253-0"/>
-    <hyperlink ref="G76" r:id="rId73" display="https://doi.org/10.1016/0047-2727(78)90005-1"/>
-    <hyperlink ref="G77" r:id="rId74" display="https://doi.org/10.1007/BF01763051"/>
-    <hyperlink ref="G78" r:id="rId75" display="https://doi.org/10.1016/j.geb.2020.11.006"/>
-    <hyperlink ref="G79" r:id="rId76" display="https://doi.org/10.1016/j.geb.2025.07.010"/>
-    <hyperlink ref="G80" r:id="rId77" display="https://www.jstor.org/stable/1815369"/>
-    <hyperlink ref="G81" r:id="rId78" display="https://doi.org/10.2307/1954283"/>
-    <hyperlink ref="G82" r:id="rId79" display="https://www.loc.gov/item/2005023291/"/>
-    <hyperlink ref="G83" r:id="rId80" display="https://doi.org/10.17487/RFC7282"/>
-    <hyperlink ref="G84" r:id="rId81" display="https://doi.org/10.1007/s10602-008-9037-5"/>
-    <hyperlink ref="G85" r:id="rId82" display="https://doi.org/10.1007/BF03187594"/>
-    <hyperlink ref="G86" r:id="rId83" display="https://doi.org/10.1016/0022-0531(75)90050-2"/>
-    <hyperlink ref="G87" r:id="rId84" display="https://doi.org/10.1007/s00355-010-0475-4"/>
-    <hyperlink ref="G88" r:id="rId85" display="https://doi.org/10.1007/s003550050164"/>
-    <hyperlink ref="G89" r:id="rId86" display="https://doi.org/10.2307/1880533"/>
-    <hyperlink ref="G90" r:id="rId87" display="https://doi.org/10.2307/1914033"/>
-    <hyperlink ref="G91" r:id="rId88" display="https://doi.org/10.1007/978-3-642-20441-8_9"/>
-    <hyperlink ref="G92" r:id="rId89" display="https://doi.org/10.1007/BF00433944"/>
-    <hyperlink ref="G93" r:id="rId90" display="https://www.loc.gov/item/2006021134/"/>
-    <hyperlink ref="G94" r:id="rId91" display="https://doi.org/10.1017/S0007123400007225"/>
-    <hyperlink ref="G95" r:id="rId92" display="https://doi.org/10.1515/9781400831456"/>
-    <hyperlink ref="G96" r:id="rId93" display="https://doi.org/10.1137/0135023"/>
-    <hyperlink ref="G97" r:id="rId94" display="https://doi.org/10.1016/0022-0531(74)90073-8"/>
-    <hyperlink ref="G98" r:id="rId95" display="https://doi.org/10.2307/1961757"/>
-    <hyperlink ref="G99" r:id="rId96" display="https://doi.org/10.1007/BF00303170"/>
+    <hyperlink ref="G36" r:id="rId35" display="https://researchonline.lse.ac.uk/id/eprint/24213/"/>
+    <hyperlink ref="G37" r:id="rId36" display="https://doi.org/10.1007/978-3-642-20441-8_3"/>
+    <hyperlink ref="G38" r:id="rId37" display="https://doi.org/10.1137/0133030"/>
+    <hyperlink ref="G39" r:id="rId38" display="https://doi.org/10.2307/2297786"/>
+    <hyperlink ref="G40" r:id="rId39" display="https://doi.org/10.1016/0022-0531(76)90063-6"/>
+    <hyperlink ref="G41" r:id="rId40" display="https://doi.org/10.1007/3-540-33799-7"/>
+    <hyperlink ref="G42" r:id="rId41" display="https://arxiv.org/abs/2410.20476"/>
+    <hyperlink ref="G43" r:id="rId42" display="https://doi.org/10.1007/s00355-023-01505-y"/>
+    <hyperlink ref="G44" r:id="rId43" display="https://arxiv.org/abs/2506.05998"/>
+    <hyperlink ref="G45" r:id="rId44" display="https://doi.org/10.2307/1914083"/>
+    <hyperlink ref="G46" r:id="rId45" display="https://doi.org/10.1007/s11127-026-01383-9"/>
+    <hyperlink ref="G47" r:id="rId46" display="https://doi.org/10.1007/s00355-015-0909-0"/>
+    <hyperlink ref="G48" r:id="rId47" display="https://doi.org/10.2307/1910410"/>
+    <hyperlink ref="G49" r:id="rId48" display="https://doi.org/10.3406/ecoap.1952.3831"/>
+    <hyperlink ref="G50" r:id="rId49" display="https://doi.org/10.1007/BF00125914"/>
+    <hyperlink ref="G51" r:id="rId50" display="https://doi.org/10.1007/s11127-023-01042-3"/>
+    <hyperlink ref="G52" r:id="rId51" display="https://doi.org/10.1007/s10602-022-09383-9"/>
+    <hyperlink ref="G53" r:id="rId52" display="https://doi.org/10.1007/978-1-349-14540-9_4"/>
+    <hyperlink ref="G54" r:id="rId53" display="https://doi.org/10.1609/aaai.v35i6.16691"/>
+    <hyperlink ref="G55" r:id="rId54" display="https://doi.org/10.1007/s10683-010-9234-8"/>
+    <hyperlink ref="G56" r:id="rId55" display="https://doi.org/10.1257/aer.20201817"/>
+    <hyperlink ref="G57" r:id="rId56" display="https://www.jstor.org/stable/20026529"/>
+    <hyperlink ref="G58" r:id="rId57" display="https://doi.org/10.65109/hmhq1427"/>
+    <hyperlink ref="G59" r:id="rId58" display="https://doi.org/10.1007/s11127-019-00697-1"/>
+    <hyperlink ref="G60" r:id="rId59" display="https://doi.org/10.3917/neg.027.0109"/>
+    <hyperlink ref="G61" r:id="rId60" display="https://doi.org/10.1006/game.1993.1010"/>
+    <hyperlink ref="G62" r:id="rId61" display="https://doi.org/10.1002/bs.3830360303"/>
+    <hyperlink ref="G63" r:id="rId62" display="https://doi.org/10.1007/978-3-642-02839-7"/>
+    <hyperlink ref="G64" r:id="rId63" display="https://doi.org/10.1007/978-3-642-20441-8_13"/>
+    <hyperlink ref="G65" r:id="rId64" display="https://doi.org/10.1016/j.jet.2021.105261"/>
+    <hyperlink ref="G66" r:id="rId65" display="https://doi.org/10.1093/biomet/44.1-2.114"/>
+    <hyperlink ref="G67" r:id="rId66" display="https://doi.org/10.1007/978-3-642-41575-3_20"/>
+    <hyperlink ref="G68" r:id="rId67" display="https://doi.org/10.2307/1907651"/>
+    <hyperlink ref="G69" r:id="rId68" display="https://doi.org/10.1016/0022-0531(76)90040-5"/>
+    <hyperlink ref="G70" r:id="rId69" display="https://doi.org/10.2307/2110786"/>
+    <hyperlink ref="G71" r:id="rId70" display="https://doi.org/10.1257/mic.20230208"/>
+    <hyperlink ref="G72" r:id="rId71" display="https://doi.org/10.2307/2297154"/>
+    <hyperlink ref="G73" r:id="rId72" display="https://doi.org/10.2307/1912535"/>
+    <hyperlink ref="G75" r:id="rId73" display="https://doi.org/10.1016/0022-0531(88)90253-0"/>
+    <hyperlink ref="G76" r:id="rId74" display="https://doi.org/10.1016/0047-2727(78)90005-1"/>
+    <hyperlink ref="G77" r:id="rId75" display="https://doi.org/10.1007/BF01763051"/>
+    <hyperlink ref="G78" r:id="rId76" display="https://doi.org/10.1016/j.geb.2020.11.006"/>
+    <hyperlink ref="G79" r:id="rId77" display="https://doi.org/10.1016/j.geb.2025.07.010"/>
+    <hyperlink ref="G80" r:id="rId78" display="https://www.jstor.org/stable/1815369"/>
+    <hyperlink ref="G81" r:id="rId79" display="https://doi.org/10.2307/1954283"/>
+    <hyperlink ref="G82" r:id="rId80" display="https://www.loc.gov/item/2005023291/"/>
+    <hyperlink ref="G83" r:id="rId81" display="https://doi.org/10.17487/RFC7282"/>
+    <hyperlink ref="G84" r:id="rId82" display="https://doi.org/10.1007/s10602-008-9037-5"/>
+    <hyperlink ref="G85" r:id="rId83" display="https://doi.org/10.1007/BF03187594"/>
+    <hyperlink ref="G86" r:id="rId84" display="https://doi.org/10.1016/0022-0531(75)90050-2"/>
+    <hyperlink ref="G87" r:id="rId85" display="https://doi.org/10.1007/s00355-010-0475-4"/>
+    <hyperlink ref="G88" r:id="rId86" display="https://doi.org/10.1007/s003550050164"/>
+    <hyperlink ref="G89" r:id="rId87" display="https://doi.org/10.2307/1880533"/>
+    <hyperlink ref="G90" r:id="rId88" display="https://doi.org/10.2307/1914033"/>
+    <hyperlink ref="G91" r:id="rId89" display="https://doi.org/10.1007/978-3-642-20441-8_9"/>
+    <hyperlink ref="G92" r:id="rId90" display="https://doi.org/10.1007/BF00433944"/>
+    <hyperlink ref="G93" r:id="rId91" display="https://www.loc.gov/item/2006021134/"/>
+    <hyperlink ref="G94" r:id="rId92" display="https://doi.org/10.1017/S0007123400007225"/>
+    <hyperlink ref="G95" r:id="rId93" display="https://doi.org/10.1515/9781400831456"/>
+    <hyperlink ref="G96" r:id="rId94" display="https://doi.org/10.1137/0135023"/>
+    <hyperlink ref="G97" r:id="rId95" display="https://doi.org/10.1016/0022-0531(74)90073-8"/>
+    <hyperlink ref="G98" r:id="rId96" display="https://doi.org/10.2307/1961757"/>
+    <hyperlink ref="G99" r:id="rId97" display="https://doi.org/10.1007/BF00303170"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7216,7 +7212,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId97"/>
+  <drawing r:id="rId98"/>
 </worksheet>
 </file>
 
@@ -7464,7 +7460,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>205</v>
@@ -7489,7 +7485,7 @@
       <c r="T3" s="13"/>
       <c r="U3" s="13"/>
       <c r="V3" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
@@ -7504,7 +7500,7 @@
       <c r="AG3" s="13"/>
       <c r="AH3" s="13"/>
       <c r="AI3" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AJ3" s="13"/>
       <c r="AK3" s="13"/>
@@ -7515,7 +7511,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>212</v>
@@ -7545,13 +7541,13 @@
       <c r="Y4" s="13"/>
       <c r="Z4" s="13"/>
       <c r="AA4" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AB4" s="13"/>
       <c r="AC4" s="13"/>
       <c r="AD4" s="13"/>
       <c r="AE4" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AF4" s="13"/>
       <c r="AG4" s="13"/>
@@ -7566,7 +7562,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>218</v>
@@ -7592,11 +7588,11 @@
       <c r="U5" s="13"/>
       <c r="V5" s="13"/>
       <c r="W5" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="X5" s="13"/>
       <c r="Y5" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="Z5" s="13"/>
       <c r="AA5" s="13"/>
@@ -7617,7 +7613,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>224</v>
@@ -7643,11 +7639,11 @@
       <c r="U6" s="13"/>
       <c r="V6" s="13"/>
       <c r="W6" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="X6" s="13"/>
       <c r="Y6" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="Z6" s="13"/>
       <c r="AA6" s="13"/>
@@ -7668,7 +7664,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>230</v>
@@ -7696,7 +7692,7 @@
       <c r="W7" s="13"/>
       <c r="X7" s="13"/>
       <c r="Y7" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="Z7" s="13"/>
       <c r="AA7" s="13"/>
@@ -7717,7 +7713,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>236</v>
@@ -7735,7 +7731,7 @@
       <c r="M8" s="13"/>
       <c r="N8" s="13"/>
       <c r="O8" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="P8" s="13"/>
       <c r="Q8" s="13"/>
@@ -7766,7 +7762,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>243</v>
@@ -7781,7 +7777,7 @@
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
       <c r="L9" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
@@ -7815,7 +7811,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>249</v>
@@ -7830,7 +7826,7 @@
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
       <c r="L10" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="M10" s="13"/>
       <c r="N10" s="13"/>
@@ -7864,7 +7860,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>255</v>
@@ -7898,7 +7894,7 @@
       <c r="AC11" s="13"/>
       <c r="AD11" s="13"/>
       <c r="AE11" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AF11" s="13"/>
       <c r="AG11" s="13"/>
@@ -7913,7 +7909,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>260</v>
@@ -7947,7 +7943,7 @@
       <c r="AC12" s="13"/>
       <c r="AD12" s="13"/>
       <c r="AE12" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AF12" s="13"/>
       <c r="AG12" s="13"/>
@@ -7962,7 +7958,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>267</v>
@@ -7984,14 +7980,14 @@
       <c r="Q13" s="13"/>
       <c r="R13" s="13"/>
       <c r="S13" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="T13" s="13"/>
       <c r="U13" s="13"/>
       <c r="V13" s="13"/>
       <c r="W13" s="13"/>
       <c r="X13" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="Y13" s="13"/>
       <c r="Z13" s="13"/>
@@ -8013,7 +8009,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>274</v>
@@ -8040,10 +8036,10 @@
       <c r="V14" s="13"/>
       <c r="W14" s="13"/>
       <c r="X14" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="Y14" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="Z14" s="13"/>
       <c r="AA14" s="13"/>
@@ -8064,7 +8060,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>280</v>
@@ -8076,7 +8072,7 @@
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
       <c r="I15" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J15" s="13"/>
       <c r="K15" s="13"/>
@@ -8085,7 +8081,7 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13"/>
       <c r="P15" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="13"/>
@@ -8115,7 +8111,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>287</v>
@@ -8134,7 +8130,7 @@
       <c r="N16" s="13"/>
       <c r="O16" s="13"/>
       <c r="P16" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="Q16" s="13"/>
       <c r="R16" s="13"/>
@@ -8164,13 +8160,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>293</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
@@ -8187,7 +8183,7 @@
       <c r="P17" s="13"/>
       <c r="Q17" s="13"/>
       <c r="R17" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="S17" s="13"/>
       <c r="T17" s="13"/>
@@ -8215,7 +8211,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>300</v>
@@ -8244,7 +8240,7 @@
       <c r="X18" s="13"/>
       <c r="Y18" s="13"/>
       <c r="Z18" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AA18" s="13"/>
       <c r="AB18" s="13"/>
@@ -8264,7 +8260,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>306</v>
@@ -8289,7 +8285,7 @@
       <c r="T19" s="13"/>
       <c r="U19" s="13"/>
       <c r="V19" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="W19" s="13"/>
       <c r="X19" s="13"/>
@@ -8304,7 +8300,7 @@
       <c r="AG19" s="13"/>
       <c r="AH19" s="13"/>
       <c r="AI19" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AJ19" s="13"/>
       <c r="AK19" s="13"/>
@@ -8315,7 +8311,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>312</v>
@@ -8340,7 +8336,7 @@
       <c r="T20" s="13"/>
       <c r="U20" s="13"/>
       <c r="V20" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="W20" s="13"/>
       <c r="X20" s="13"/>
@@ -8364,7 +8360,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>318</v>
@@ -8379,7 +8375,7 @@
       <c r="J21" s="13"/>
       <c r="K21" s="13"/>
       <c r="L21" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="M21" s="13"/>
       <c r="N21" s="13"/>
@@ -8413,7 +8409,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>324</v>
@@ -8446,7 +8442,7 @@
       <c r="AB22" s="13"/>
       <c r="AC22" s="13"/>
       <c r="AD22" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AE22" s="13"/>
       <c r="AF22" s="13"/>
@@ -8462,7 +8458,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>331</v>
@@ -8478,7 +8474,7 @@
       <c r="K23" s="13"/>
       <c r="L23" s="13"/>
       <c r="M23" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="N23" s="13"/>
       <c r="O23" s="13"/>
@@ -8511,7 +8507,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>337</v>
@@ -8519,13 +8515,13 @@
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
       <c r="E24" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="F24" s="13"/>
       <c r="G24" s="13"/>
       <c r="H24" s="13"/>
       <c r="I24" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J24" s="13"/>
       <c r="K24" s="13"/>
@@ -8534,7 +8530,7 @@
       <c r="N24" s="13"/>
       <c r="O24" s="13"/>
       <c r="P24" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="Q24" s="13"/>
       <c r="R24" s="13"/>
@@ -8564,7 +8560,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>343</v>
@@ -8584,7 +8580,7 @@
       <c r="O25" s="13"/>
       <c r="P25" s="13"/>
       <c r="Q25" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="R25" s="13"/>
       <c r="S25" s="13"/>
@@ -8613,7 +8609,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>348</v>
@@ -8638,7 +8634,7 @@
       <c r="T26" s="13"/>
       <c r="U26" s="13"/>
       <c r="V26" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="W26" s="13"/>
       <c r="X26" s="13"/>
@@ -8653,7 +8649,7 @@
       <c r="AG26" s="13"/>
       <c r="AH26" s="13"/>
       <c r="AI26" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AJ26" s="13"/>
       <c r="AK26" s="13"/>
@@ -8664,7 +8660,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>355</v>
@@ -8688,11 +8684,11 @@
       <c r="S27" s="13"/>
       <c r="T27" s="13"/>
       <c r="U27" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="V27" s="13"/>
       <c r="W27" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="X27" s="13"/>
       <c r="Y27" s="13"/>
@@ -8715,7 +8711,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>362</v>
@@ -8748,10 +8744,10 @@
       <c r="AB28" s="13"/>
       <c r="AC28" s="13"/>
       <c r="AD28" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AE28" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AF28" s="13"/>
       <c r="AG28" s="13"/>
@@ -8766,7 +8762,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>368</v>
@@ -8789,10 +8785,10 @@
       <c r="R29" s="13"/>
       <c r="S29" s="13"/>
       <c r="T29" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="U29" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="V29" s="13"/>
       <c r="W29" s="13"/>
@@ -8817,7 +8813,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>374</v>
@@ -8856,7 +8852,7 @@
       <c r="AH30" s="13"/>
       <c r="AI30" s="13"/>
       <c r="AJ30" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AK30" s="13"/>
       <c r="AL30" s="15" t="n">
@@ -8866,16 +8862,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>381</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E31" s="13"/>
       <c r="F31" s="13"/>
@@ -8917,7 +8913,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>388</v>
@@ -8926,7 +8922,7 @@
       <c r="D32" s="13"/>
       <c r="E32" s="13"/>
       <c r="F32" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="G32" s="13"/>
       <c r="H32" s="13"/>
@@ -8955,7 +8951,7 @@
       <c r="AE32" s="13"/>
       <c r="AF32" s="13"/>
       <c r="AG32" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AH32" s="13"/>
       <c r="AI32" s="13"/>
@@ -8968,7 +8964,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>394</v>
@@ -8994,11 +8990,11 @@
       <c r="U33" s="13"/>
       <c r="V33" s="13"/>
       <c r="W33" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="X33" s="13"/>
       <c r="Y33" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="Z33" s="13"/>
       <c r="AA33" s="13"/>
@@ -9019,7 +9015,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>401</v>
@@ -9031,7 +9027,7 @@
       <c r="G34" s="13"/>
       <c r="H34" s="13"/>
       <c r="I34" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J34" s="13"/>
       <c r="K34" s="13"/>
@@ -9068,7 +9064,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>407</v>
@@ -9104,7 +9100,7 @@
       <c r="AE35" s="13"/>
       <c r="AF35" s="13"/>
       <c r="AG35" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AH35" s="13"/>
       <c r="AI35" s="13"/>
@@ -9117,7 +9113,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>413</v>
@@ -9136,7 +9132,7 @@
       <c r="N36" s="13"/>
       <c r="O36" s="13"/>
       <c r="P36" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="Q36" s="13"/>
       <c r="R36" s="13"/>
@@ -9166,7 +9162,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>419</v>
@@ -9181,13 +9177,13 @@
       <c r="J37" s="13"/>
       <c r="K37" s="13"/>
       <c r="L37" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="13"/>
       <c r="O37" s="13"/>
       <c r="P37" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="Q37" s="13"/>
       <c r="R37" s="13"/>
@@ -9217,7 +9213,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>425</v>
@@ -9231,17 +9227,17 @@
       <c r="I38" s="13"/>
       <c r="J38" s="13"/>
       <c r="K38" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L38" s="13"/>
       <c r="M38" s="13"/>
       <c r="N38" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O38" s="13"/>
       <c r="P38" s="13"/>
       <c r="Q38" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="R38" s="13"/>
       <c r="S38" s="13"/>
@@ -9270,7 +9266,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B39" s="12" t="s">
         <v>431</v>
@@ -9278,14 +9274,14 @@
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
       <c r="E39" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="F39" s="13"/>
       <c r="G39" s="13"/>
       <c r="H39" s="13"/>
       <c r="I39" s="13"/>
       <c r="J39" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="K39" s="13"/>
       <c r="L39" s="13"/>
@@ -9321,7 +9317,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>437</v>
@@ -9337,7 +9333,7 @@
       <c r="K40" s="13"/>
       <c r="L40" s="13"/>
       <c r="M40" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="N40" s="13"/>
       <c r="O40" s="13"/>
@@ -9370,14 +9366,14 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B41" s="12" t="s">
         <v>443</v>
       </c>
       <c r="C41" s="13"/>
       <c r="D41" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E41" s="13"/>
       <c r="F41" s="13"/>
@@ -9409,7 +9405,7 @@
       <c r="AF41" s="13"/>
       <c r="AG41" s="13"/>
       <c r="AH41" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AI41" s="13"/>
       <c r="AJ41" s="13"/>
@@ -9421,14 +9417,14 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>448</v>
       </c>
       <c r="C42" s="13"/>
       <c r="D42" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
@@ -9460,7 +9456,7 @@
       <c r="AF42" s="13"/>
       <c r="AG42" s="13"/>
       <c r="AH42" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AI42" s="13"/>
       <c r="AJ42" s="13"/>
@@ -9472,7 +9468,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B43" s="12" t="s">
         <v>453</v>
@@ -9501,7 +9497,7 @@
       <c r="X43" s="13"/>
       <c r="Y43" s="13"/>
       <c r="Z43" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AA43" s="13"/>
       <c r="AB43" s="13"/>
@@ -9521,7 +9517,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>459</v>
@@ -9548,11 +9544,11 @@
       <c r="V44" s="13"/>
       <c r="W44" s="13"/>
       <c r="X44" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="Y44" s="13"/>
       <c r="Z44" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AA44" s="13"/>
       <c r="AB44" s="13"/>
@@ -9572,7 +9568,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>465</v>
@@ -9593,7 +9589,7 @@
       <c r="P45" s="13"/>
       <c r="Q45" s="13"/>
       <c r="R45" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="S45" s="13"/>
       <c r="T45" s="13"/>
@@ -9603,7 +9599,7 @@
       <c r="X45" s="13"/>
       <c r="Y45" s="13"/>
       <c r="Z45" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AA45" s="13"/>
       <c r="AB45" s="13"/>
@@ -9623,7 +9619,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>471</v>
@@ -9641,10 +9637,10 @@
       <c r="M46" s="13"/>
       <c r="N46" s="13"/>
       <c r="O46" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="P46" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="Q46" s="13"/>
       <c r="R46" s="13"/>
@@ -9674,7 +9670,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B47" s="12" t="s">
         <v>478</v>
@@ -9699,11 +9695,11 @@
       <c r="T47" s="13"/>
       <c r="U47" s="13"/>
       <c r="V47" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="W47" s="13"/>
       <c r="X47" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="Y47" s="13"/>
       <c r="Z47" s="13"/>
@@ -9725,7 +9721,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>484</v>
@@ -9744,7 +9740,7 @@
       <c r="N48" s="13"/>
       <c r="O48" s="13"/>
       <c r="P48" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="Q48" s="13"/>
       <c r="R48" s="13"/>
@@ -9764,7 +9760,7 @@
       <c r="AF48" s="13"/>
       <c r="AG48" s="13"/>
       <c r="AH48" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AI48" s="13"/>
       <c r="AJ48" s="13"/>
@@ -9776,7 +9772,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B49" s="12" t="s">
         <v>491</v>
@@ -9799,7 +9795,7 @@
       <c r="R49" s="13"/>
       <c r="S49" s="13"/>
       <c r="T49" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="U49" s="13"/>
       <c r="V49" s="13"/>
@@ -9825,14 +9821,14 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>497</v>
       </c>
       <c r="C50" s="13"/>
       <c r="D50" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E50" s="13"/>
       <c r="F50" s="13"/>
@@ -9874,7 +9870,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="12" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B51" s="12" t="s">
         <v>503</v>
@@ -9901,7 +9897,7 @@
       <c r="V51" s="13"/>
       <c r="W51" s="13"/>
       <c r="X51" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="Y51" s="13"/>
       <c r="Z51" s="13"/>
@@ -9923,7 +9919,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>509</v>
@@ -9934,7 +9930,7 @@
       <c r="F52" s="13"/>
       <c r="G52" s="13"/>
       <c r="H52" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="I52" s="13"/>
       <c r="J52" s="13"/>
@@ -9942,12 +9938,12 @@
       <c r="L52" s="13"/>
       <c r="M52" s="13"/>
       <c r="N52" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O52" s="13"/>
       <c r="P52" s="13"/>
       <c r="Q52" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="R52" s="13"/>
       <c r="S52" s="13"/>
@@ -9976,7 +9972,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B53" s="12" t="s">
         <v>516</v>
@@ -9987,7 +9983,7 @@
       <c r="F53" s="13"/>
       <c r="G53" s="13"/>
       <c r="H53" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="I53" s="13"/>
       <c r="J53" s="13"/>
@@ -10025,7 +10021,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>521</v>
@@ -10058,7 +10054,7 @@
       <c r="AB54" s="13"/>
       <c r="AC54" s="13"/>
       <c r="AD54" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AE54" s="13"/>
       <c r="AF54" s="13"/>
@@ -10074,7 +10070,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B55" s="12" t="s">
         <v>527</v>
@@ -10105,7 +10101,7 @@
       <c r="Z55" s="13"/>
       <c r="AA55" s="13"/>
       <c r="AB55" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AC55" s="13"/>
       <c r="AD55" s="13"/>
@@ -10123,7 +10119,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>534</v>
@@ -10148,10 +10144,10 @@
       <c r="T56" s="13"/>
       <c r="U56" s="13"/>
       <c r="V56" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="W56" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="X56" s="13"/>
       <c r="Y56" s="13"/>
@@ -10165,7 +10161,7 @@
       <c r="AG56" s="13"/>
       <c r="AH56" s="13"/>
       <c r="AI56" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AJ56" s="13"/>
       <c r="AK56" s="13"/>
@@ -10176,7 +10172,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B57" s="12" t="s">
         <v>539</v>
@@ -10216,7 +10212,7 @@
       <c r="AI57" s="13"/>
       <c r="AJ57" s="13"/>
       <c r="AK57" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AL57" s="15" t="n">
         <f aca="false">COUNTIF(C57:AK57,"x")</f>
@@ -10225,7 +10221,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>544</v>
@@ -10237,7 +10233,7 @@
       <c r="G58" s="13"/>
       <c r="H58" s="13"/>
       <c r="I58" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J58" s="13"/>
       <c r="K58" s="13"/>
@@ -10274,7 +10270,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B59" s="12" t="s">
         <v>551</v>
@@ -10294,7 +10290,7 @@
       <c r="O59" s="13"/>
       <c r="P59" s="13"/>
       <c r="Q59" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="R59" s="13"/>
       <c r="S59" s="13"/>
@@ -10307,7 +10303,7 @@
       <c r="Z59" s="13"/>
       <c r="AA59" s="13"/>
       <c r="AB59" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AC59" s="13"/>
       <c r="AD59" s="13"/>
@@ -10325,7 +10321,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>556</v>
@@ -10356,10 +10352,10 @@
       <c r="Z60" s="13"/>
       <c r="AA60" s="13"/>
       <c r="AB60" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AC60" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AD60" s="13"/>
       <c r="AE60" s="13"/>
@@ -10376,7 +10372,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="12" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B61" s="12" t="s">
         <v>562</v>
@@ -10411,7 +10407,7 @@
       <c r="AD61" s="13"/>
       <c r="AE61" s="13"/>
       <c r="AF61" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AG61" s="13"/>
       <c r="AH61" s="13"/>
@@ -10425,7 +10421,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>568</v>
@@ -10433,7 +10429,7 @@
       <c r="C62" s="13"/>
       <c r="D62" s="13"/>
       <c r="E62" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="F62" s="13"/>
       <c r="G62" s="13"/>
@@ -10443,7 +10439,7 @@
       <c r="K62" s="13"/>
       <c r="L62" s="13"/>
       <c r="M62" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="N62" s="13"/>
       <c r="O62" s="13"/>
@@ -10476,7 +10472,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="12" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B63" s="12" t="s">
         <v>573</v>
@@ -10501,7 +10497,7 @@
       <c r="T63" s="13"/>
       <c r="U63" s="13"/>
       <c r="V63" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="W63" s="13"/>
       <c r="X63" s="13"/>
@@ -10516,7 +10512,7 @@
       <c r="AG63" s="13"/>
       <c r="AH63" s="13"/>
       <c r="AI63" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AJ63" s="13"/>
       <c r="AK63" s="13"/>
@@ -10527,7 +10523,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>578</v>
@@ -10542,7 +10538,7 @@
       <c r="J64" s="13"/>
       <c r="K64" s="13"/>
       <c r="L64" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="M64" s="13"/>
       <c r="N64" s="13"/>
@@ -10576,7 +10572,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="12" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B65" s="12" t="s">
         <v>584</v>
@@ -10590,10 +10586,10 @@
       <c r="I65" s="13"/>
       <c r="J65" s="13"/>
       <c r="K65" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L65" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="M65" s="13"/>
       <c r="N65" s="13"/>
@@ -10617,7 +10613,7 @@
       <c r="AF65" s="13"/>
       <c r="AG65" s="13"/>
       <c r="AH65" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AI65" s="13"/>
       <c r="AJ65" s="13"/>
@@ -10629,7 +10625,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>589</v>
@@ -10663,7 +10659,7 @@
       <c r="AC66" s="13"/>
       <c r="AD66" s="13"/>
       <c r="AE66" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AF66" s="13"/>
       <c r="AG66" s="13"/>
@@ -10678,7 +10674,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="12" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B67" s="12" t="s">
         <v>595</v>
@@ -10715,7 +10711,7 @@
       <c r="AF67" s="13"/>
       <c r="AG67" s="13"/>
       <c r="AH67" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AI67" s="13"/>
       <c r="AJ67" s="13"/>
@@ -10727,7 +10723,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>601</v>
@@ -10764,7 +10760,7 @@
       <c r="AF68" s="13"/>
       <c r="AG68" s="13"/>
       <c r="AH68" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AI68" s="13"/>
       <c r="AJ68" s="13"/>
@@ -10776,13 +10772,13 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="12" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>608</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D69" s="13"/>
       <c r="E69" s="13"/>
@@ -10825,7 +10821,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="12" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>614</v>
@@ -10847,14 +10843,14 @@
       <c r="Q70" s="13"/>
       <c r="R70" s="13"/>
       <c r="S70" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="T70" s="13"/>
       <c r="U70" s="13"/>
       <c r="V70" s="13"/>
       <c r="W70" s="13"/>
       <c r="X70" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="Y70" s="13"/>
       <c r="Z70" s="13"/>
@@ -10876,7 +10872,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="12" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B71" s="12" t="s">
         <v>621</v>
@@ -10890,7 +10886,7 @@
       <c r="I71" s="13"/>
       <c r="J71" s="13"/>
       <c r="K71" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L71" s="13"/>
       <c r="M71" s="13"/>
@@ -10915,7 +10911,7 @@
       <c r="AF71" s="13"/>
       <c r="AG71" s="13"/>
       <c r="AH71" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AI71" s="13"/>
       <c r="AJ71" s="13"/>
@@ -10927,7 +10923,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>627</v>
@@ -10952,7 +10948,7 @@
       <c r="T72" s="13"/>
       <c r="U72" s="13"/>
       <c r="V72" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="W72" s="13"/>
       <c r="X72" s="13"/>
@@ -10976,7 +10972,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="12" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B73" s="12" t="s">
         <v>633</v>
@@ -11007,7 +11003,7 @@
       <c r="Z73" s="13"/>
       <c r="AA73" s="13"/>
       <c r="AB73" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AC73" s="13"/>
       <c r="AD73" s="13"/>
@@ -11025,7 +11021,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>640</v>
@@ -11055,10 +11051,10 @@
       <c r="Y74" s="13"/>
       <c r="Z74" s="13"/>
       <c r="AA74" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AB74" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AC74" s="13"/>
       <c r="AD74" s="13"/>
@@ -11076,7 +11072,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="12" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B75" s="12" t="s">
         <v>646</v>
@@ -11094,7 +11090,7 @@
       <c r="M75" s="13"/>
       <c r="N75" s="13"/>
       <c r="O75" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="P75" s="13"/>
       <c r="Q75" s="13"/>
@@ -11108,10 +11104,10 @@
       <c r="Y75" s="13"/>
       <c r="Z75" s="13"/>
       <c r="AA75" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AB75" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AC75" s="13"/>
       <c r="AD75" s="13"/>
@@ -11129,13 +11125,13 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>651</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D76" s="13"/>
       <c r="E76" s="13"/>
@@ -11151,7 +11147,7 @@
       <c r="O76" s="13"/>
       <c r="P76" s="13"/>
       <c r="Q76" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="R76" s="13"/>
       <c r="S76" s="13"/>
@@ -11180,7 +11176,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="12" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B77" s="12" t="s">
         <v>657</v>
@@ -11210,7 +11206,7 @@
       <c r="Y77" s="13"/>
       <c r="Z77" s="13"/>
       <c r="AA77" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AB77" s="13"/>
       <c r="AC77" s="13"/>
@@ -11229,7 +11225,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B78" s="12" t="s">
         <v>663</v>
@@ -11252,12 +11248,12 @@
       <c r="R78" s="13"/>
       <c r="S78" s="13"/>
       <c r="T78" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="U78" s="13"/>
       <c r="V78" s="13"/>
       <c r="W78" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="X78" s="13"/>
       <c r="Y78" s="13"/>
@@ -11280,7 +11276,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="12" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B79" s="12" t="s">
         <v>669</v>
@@ -11306,11 +11302,11 @@
       <c r="U79" s="13"/>
       <c r="V79" s="13"/>
       <c r="W79" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="X79" s="13"/>
       <c r="Y79" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="Z79" s="13"/>
       <c r="AA79" s="13"/>
@@ -11322,7 +11318,7 @@
       <c r="AG79" s="13"/>
       <c r="AH79" s="13"/>
       <c r="AI79" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AJ79" s="13"/>
       <c r="AK79" s="13"/>
@@ -11333,7 +11329,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>675</v>
@@ -11358,7 +11354,7 @@
       <c r="T80" s="13"/>
       <c r="U80" s="13"/>
       <c r="V80" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="W80" s="13"/>
       <c r="X80" s="13"/>
@@ -11373,7 +11369,7 @@
       <c r="AG80" s="13"/>
       <c r="AH80" s="13"/>
       <c r="AI80" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AJ80" s="13"/>
       <c r="AK80" s="13"/>
@@ -11384,7 +11380,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="12" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B81" s="12" t="s">
         <v>681</v>
@@ -11406,10 +11402,10 @@
       <c r="Q81" s="13"/>
       <c r="R81" s="13"/>
       <c r="S81" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="T81" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="U81" s="13"/>
       <c r="V81" s="13"/>
@@ -11435,13 +11431,13 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D82" s="13"/>
       <c r="E82" s="13"/>
@@ -11461,7 +11457,7 @@
       <c r="S82" s="13"/>
       <c r="T82" s="13"/>
       <c r="U82" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="V82" s="13"/>
       <c r="W82" s="13"/>
@@ -11486,14 +11482,14 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="12" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C83" s="13"/>
       <c r="D83" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E83" s="13"/>
       <c r="F83" s="13"/>
@@ -11525,7 +11521,7 @@
       <c r="AF83" s="13"/>
       <c r="AG83" s="13"/>
       <c r="AH83" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AI83" s="13"/>
       <c r="AJ83" s="13"/>
@@ -11537,10 +11533,10 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C84" s="13"/>
       <c r="D84" s="13"/>
@@ -11572,7 +11568,7 @@
       <c r="AD84" s="13"/>
       <c r="AE84" s="13"/>
       <c r="AF84" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AG84" s="13"/>
       <c r="AH84" s="13"/>
@@ -11586,10 +11582,10 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="12" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C85" s="13"/>
       <c r="D85" s="13"/>
@@ -11612,7 +11608,7 @@
       <c r="U85" s="13"/>
       <c r="V85" s="13"/>
       <c r="W85" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="X85" s="13"/>
       <c r="Y85" s="13"/>
@@ -11624,7 +11620,7 @@
       <c r="AE85" s="13"/>
       <c r="AF85" s="13"/>
       <c r="AG85" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AH85" s="13"/>
       <c r="AI85" s="13"/>
@@ -11637,10 +11633,10 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="12" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C86" s="13"/>
       <c r="D86" s="13"/>
@@ -11663,10 +11659,10 @@
       <c r="U86" s="13"/>
       <c r="V86" s="13"/>
       <c r="W86" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="X86" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="Y86" s="13"/>
       <c r="Z86" s="13"/>
@@ -11688,10 +11684,10 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="12" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C87" s="13"/>
       <c r="D87" s="13"/>
@@ -11706,10 +11702,10 @@
       <c r="M87" s="13"/>
       <c r="N87" s="13"/>
       <c r="O87" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="P87" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="Q87" s="13"/>
       <c r="R87" s="13"/>
@@ -11739,18 +11735,18 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="12" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C88" s="13"/>
       <c r="D88" s="13"/>
       <c r="E88" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="F88" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="G88" s="13"/>
       <c r="H88" s="13"/>
@@ -11760,7 +11756,7 @@
       <c r="L88" s="13"/>
       <c r="M88" s="13"/>
       <c r="N88" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O88" s="13"/>
       <c r="P88" s="13"/>
@@ -11792,10 +11788,10 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="12" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C89" s="13"/>
       <c r="D89" s="13"/>
@@ -11825,7 +11821,7 @@
       <c r="AB89" s="13"/>
       <c r="AC89" s="13"/>
       <c r="AD89" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AE89" s="13"/>
       <c r="AF89" s="13"/>
@@ -11841,10 +11837,10 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="12" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C90" s="13"/>
       <c r="D90" s="13"/>
@@ -11854,7 +11850,7 @@
       <c r="H90" s="13"/>
       <c r="I90" s="13"/>
       <c r="J90" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="K90" s="13"/>
       <c r="L90" s="13"/>
@@ -11890,15 +11886,15 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="12" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C91" s="13"/>
       <c r="D91" s="13"/>
       <c r="E91" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="F91" s="13"/>
       <c r="G91" s="13"/>
@@ -11939,14 +11935,14 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="12" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C92" s="13"/>
       <c r="D92" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E92" s="13"/>
       <c r="F92" s="13"/>
@@ -11978,7 +11974,7 @@
       <c r="AF92" s="13"/>
       <c r="AG92" s="13"/>
       <c r="AH92" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AI92" s="13"/>
       <c r="AJ92" s="13"/>
@@ -11990,28 +11986,28 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="12" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C93" s="13"/>
       <c r="D93" s="13"/>
       <c r="E93" s="13"/>
       <c r="F93" s="13"/>
       <c r="G93" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H93" s="13"/>
       <c r="I93" s="13"/>
       <c r="J93" s="13"/>
       <c r="K93" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L93" s="13"/>
       <c r="M93" s="13"/>
       <c r="N93" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O93" s="13"/>
       <c r="P93" s="13"/>
@@ -12043,19 +12039,19 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="12" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C94" s="13"/>
       <c r="D94" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E94" s="13"/>
       <c r="F94" s="13"/>
       <c r="G94" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H94" s="13"/>
       <c r="I94" s="13"/>
@@ -12084,7 +12080,7 @@
       <c r="AF94" s="13"/>
       <c r="AG94" s="13"/>
       <c r="AH94" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AI94" s="13"/>
       <c r="AJ94" s="13"/>
@@ -12096,10 +12092,10 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="12" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C95" s="13"/>
       <c r="D95" s="13"/>
@@ -12122,7 +12118,7 @@
       <c r="U95" s="13"/>
       <c r="V95" s="13"/>
       <c r="W95" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="X95" s="13"/>
       <c r="Y95" s="13"/>
@@ -12145,10 +12141,10 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="12" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C96" s="13"/>
       <c r="D96" s="13"/>
@@ -12171,7 +12167,7 @@
       <c r="U96" s="13"/>
       <c r="V96" s="13"/>
       <c r="W96" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="X96" s="13"/>
       <c r="Y96" s="13"/>
@@ -12194,13 +12190,13 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="12" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C97" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D97" s="13"/>
       <c r="E97" s="13"/>
@@ -12208,7 +12204,7 @@
       <c r="G97" s="13"/>
       <c r="H97" s="13"/>
       <c r="I97" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J97" s="13"/>
       <c r="K97" s="13"/>
@@ -12245,10 +12241,10 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="12" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C98" s="13"/>
       <c r="D98" s="13"/>
@@ -12259,7 +12255,7 @@
       <c r="I98" s="13"/>
       <c r="J98" s="13"/>
       <c r="K98" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L98" s="13"/>
       <c r="M98" s="13"/>
@@ -12294,13 +12290,13 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="12" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C99" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D99" s="13"/>
       <c r="E99" s="13"/>
@@ -12308,7 +12304,7 @@
       <c r="G99" s="13"/>
       <c r="H99" s="13"/>
       <c r="I99" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J99" s="13"/>
       <c r="K99" s="13"/>
@@ -12345,17 +12341,17 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="12" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C100" s="13"/>
       <c r="D100" s="13"/>
       <c r="E100" s="13"/>
       <c r="F100" s="13"/>
       <c r="G100" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H100" s="13"/>
       <c r="I100" s="13"/>
@@ -12364,7 +12360,7 @@
       <c r="L100" s="13"/>
       <c r="M100" s="13"/>
       <c r="N100" s="14" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O100" s="13"/>
       <c r="P100" s="13"/>

--- a/literature/concept-map/concept-map.xlsx
+++ b/literature/concept-map/concept-map.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="892">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="891">
   <si>
     <t xml:space="preserve">Concept map of the note “Voting for a consensus with veto rights” (v0.1)</t>
   </si>
@@ -1830,9 +1830,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.jstor.org/stable/20026529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not checked against the journal's record: no Crossref record, and JSTOR 20026529 refuses automated access. First page 577 in Fishburn (1977), the earliest citing paper found, and in Kondratev and Nesterov (2020); 571 in Young and Levenglick (1978), Young (1988) and Bartholdi et al. (1989)</t>
   </si>
   <si>
     <t xml:space="preserve">Kondratev &amp; Ianovski (2024). Veto Core Consistent Preference Aggregation</t>
@@ -5900,7 +5897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
         <v>542</v>
       </c>
@@ -5922,9 +5919,7 @@
       <c r="G57" s="9" t="s">
         <v>546</v>
       </c>
-      <c r="H57" s="8" t="s">
-        <v>547</v>
-      </c>
+      <c r="H57" s="8"/>
       <c r="I57" s="8" t="n">
         <f aca="false">COUNTIF(INDEX(Matrix!$C$3:$AK$100,MATCH(D57,Matrix!$B$3:$B$100,0),0),"x")</f>
         <v>1</v>
@@ -5932,25 +5927,25 @@
     </row>
     <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="B58" s="8" t="s">
         <v>548</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="C58" s="8" t="s">
         <v>549</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="D58" s="8" t="s">
         <v>550</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>551</v>
       </c>
       <c r="E58" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F58" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="G58" s="9" t="s">
         <v>552</v>
-      </c>
-      <c r="G58" s="9" t="s">
-        <v>553</v>
       </c>
       <c r="H58" s="8"/>
       <c r="I58" s="8" t="n">
@@ -5963,22 +5958,22 @@
         <v>151</v>
       </c>
       <c r="B59" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="C59" s="8" t="s">
         <v>554</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="D59" s="8" t="s">
         <v>555</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>556</v>
       </c>
       <c r="E59" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F59" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="G59" s="9" t="s">
         <v>557</v>
-      </c>
-      <c r="G59" s="9" t="s">
-        <v>558</v>
       </c>
       <c r="H59" s="8"/>
       <c r="I59" s="8" t="n">
@@ -5988,25 +5983,25 @@
     </row>
     <row r="60" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="s">
+        <v>558</v>
+      </c>
+      <c r="B60" s="8" t="s">
         <v>559</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="C60" s="8" t="s">
         <v>560</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="D60" s="8" t="s">
         <v>561</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>562</v>
       </c>
       <c r="E60" s="8" t="s">
         <v>349</v>
       </c>
       <c r="F60" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="G60" s="9" t="s">
         <v>563</v>
-      </c>
-      <c r="G60" s="9" t="s">
-        <v>564</v>
       </c>
       <c r="H60" s="8"/>
       <c r="I60" s="8" t="n">
@@ -6016,25 +6011,25 @@
     </row>
     <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="B61" s="8" t="s">
         <v>565</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="C61" s="8" t="s">
         <v>566</v>
       </c>
-      <c r="C61" s="8" t="s">
+      <c r="D61" s="8" t="s">
         <v>567</v>
-      </c>
-      <c r="D61" s="8" t="s">
-        <v>568</v>
       </c>
       <c r="E61" s="8" t="s">
         <v>281</v>
       </c>
       <c r="F61" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="G61" s="9" t="s">
         <v>569</v>
-      </c>
-      <c r="G61" s="9" t="s">
-        <v>570</v>
       </c>
       <c r="H61" s="8"/>
       <c r="I61" s="8" t="n">
@@ -6044,25 +6039,25 @@
     </row>
     <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B62" s="8" t="s">
         <v>203</v>
       </c>
       <c r="C62" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="D62" s="8" t="s">
         <v>572</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>573</v>
       </c>
       <c r="E62" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F62" s="8" t="s">
+        <v>573</v>
+      </c>
+      <c r="G62" s="9" t="s">
         <v>574</v>
-      </c>
-      <c r="G62" s="9" t="s">
-        <v>575</v>
       </c>
       <c r="H62" s="8"/>
       <c r="I62" s="8" t="n">
@@ -6072,25 +6067,25 @@
     </row>
     <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B63" s="8" t="s">
         <v>241</v>
       </c>
       <c r="C63" s="8" t="s">
+        <v>576</v>
+      </c>
+      <c r="D63" s="8" t="s">
         <v>577</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>578</v>
       </c>
       <c r="E63" s="8" t="s">
         <v>281</v>
       </c>
       <c r="F63" s="8" t="s">
+        <v>578</v>
+      </c>
+      <c r="G63" s="9" t="s">
         <v>579</v>
-      </c>
-      <c r="G63" s="9" t="s">
-        <v>580</v>
       </c>
       <c r="H63" s="8"/>
       <c r="I63" s="8" t="n">
@@ -6100,25 +6095,25 @@
     </row>
     <row r="64" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="B64" s="8" t="s">
         <v>581</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="C64" s="8" t="s">
         <v>582</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="D64" s="8" t="s">
         <v>583</v>
-      </c>
-      <c r="D64" s="8" t="s">
-        <v>584</v>
       </c>
       <c r="E64" s="8" t="s">
         <v>281</v>
       </c>
       <c r="F64" s="8" t="s">
+        <v>584</v>
+      </c>
+      <c r="G64" s="9" t="s">
         <v>585</v>
-      </c>
-      <c r="G64" s="9" t="s">
-        <v>586</v>
       </c>
       <c r="H64" s="8"/>
       <c r="I64" s="8" t="n">
@@ -6128,25 +6123,25 @@
     </row>
     <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B65" s="8" t="s">
         <v>253</v>
       </c>
       <c r="C65" s="8" t="s">
+        <v>587</v>
+      </c>
+      <c r="D65" s="8" t="s">
         <v>588</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>589</v>
       </c>
       <c r="E65" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F65" s="8" t="s">
+        <v>589</v>
+      </c>
+      <c r="G65" s="9" t="s">
         <v>590</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>591</v>
       </c>
       <c r="H65" s="8"/>
       <c r="I65" s="8" t="n">
@@ -6156,25 +6151,25 @@
     </row>
     <row r="66" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="B66" s="8" t="s">
         <v>592</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="C66" s="8" t="s">
         <v>593</v>
       </c>
-      <c r="C66" s="8" t="s">
+      <c r="D66" s="8" t="s">
         <v>594</v>
       </c>
-      <c r="D66" s="8" t="s">
+      <c r="E66" s="8" t="s">
         <v>595</v>
       </c>
-      <c r="E66" s="8" t="s">
+      <c r="F66" s="8" t="s">
         <v>596</v>
       </c>
-      <c r="F66" s="8" t="s">
+      <c r="G66" s="9" t="s">
         <v>597</v>
-      </c>
-      <c r="G66" s="9" t="s">
-        <v>598</v>
       </c>
       <c r="H66" s="8"/>
       <c r="I66" s="8" t="n">
@@ -6184,25 +6179,25 @@
     </row>
     <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>592</v>
+      </c>
+      <c r="C67" s="8" t="s">
         <v>599</v>
       </c>
-      <c r="B67" s="8" t="s">
-        <v>593</v>
-      </c>
-      <c r="C67" s="8" t="s">
+      <c r="D67" s="8" t="s">
         <v>600</v>
       </c>
-      <c r="D67" s="8" t="s">
+      <c r="E67" s="8" t="s">
         <v>601</v>
       </c>
-      <c r="E67" s="8" t="s">
+      <c r="F67" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="F67" s="8" t="s">
+      <c r="G67" s="9" t="s">
         <v>603</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>604</v>
       </c>
       <c r="H67" s="8"/>
       <c r="I67" s="8" t="n">
@@ -6212,25 +6207,25 @@
     </row>
     <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="s">
+        <v>604</v>
+      </c>
+      <c r="B68" s="8" t="s">
         <v>605</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="C68" s="8" t="s">
         <v>606</v>
       </c>
-      <c r="C68" s="8" t="s">
+      <c r="D68" s="8" t="s">
         <v>607</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>608</v>
       </c>
       <c r="E68" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F68" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="G68" s="9" t="s">
         <v>609</v>
-      </c>
-      <c r="G68" s="9" t="s">
-        <v>610</v>
       </c>
       <c r="H68" s="8"/>
       <c r="I68" s="8" t="n">
@@ -6240,25 +6235,25 @@
     </row>
     <row r="69" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="B69" s="8" t="s">
         <v>611</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="C69" s="8" t="s">
         <v>612</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="D69" s="8" t="s">
         <v>613</v>
       </c>
-      <c r="D69" s="8" t="s">
+      <c r="E69" s="8" t="s">
         <v>614</v>
       </c>
-      <c r="E69" s="8" t="s">
+      <c r="F69" s="8" t="s">
         <v>615</v>
       </c>
-      <c r="F69" s="8" t="s">
+      <c r="G69" s="9" t="s">
         <v>616</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>617</v>
       </c>
       <c r="H69" s="8"/>
       <c r="I69" s="8" t="n">
@@ -6268,25 +6263,25 @@
     </row>
     <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="B70" s="8" t="s">
         <v>618</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="C70" s="8" t="s">
         <v>619</v>
       </c>
-      <c r="C70" s="8" t="s">
+      <c r="D70" s="8" t="s">
         <v>620</v>
       </c>
-      <c r="D70" s="8" t="s">
+      <c r="E70" s="8" t="s">
         <v>621</v>
       </c>
-      <c r="E70" s="8" t="s">
+      <c r="F70" s="8" t="s">
         <v>622</v>
       </c>
-      <c r="F70" s="8" t="s">
+      <c r="G70" s="9" t="s">
         <v>623</v>
-      </c>
-      <c r="G70" s="9" t="s">
-        <v>624</v>
       </c>
       <c r="H70" s="8"/>
       <c r="I70" s="8" t="n">
@@ -6296,25 +6291,25 @@
     </row>
     <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B71" s="8" t="s">
         <v>310</v>
       </c>
       <c r="C71" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="D71" s="8" t="s">
         <v>626</v>
       </c>
-      <c r="D71" s="8" t="s">
+      <c r="E71" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="E71" s="8" t="s">
+      <c r="F71" s="8" t="s">
         <v>628</v>
       </c>
-      <c r="F71" s="8" t="s">
+      <c r="G71" s="9" t="s">
         <v>629</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>630</v>
       </c>
       <c r="H71" s="8"/>
       <c r="I71" s="8" t="n">
@@ -6324,25 +6319,25 @@
     </row>
     <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B72" s="8" t="s">
         <v>525</v>
       </c>
       <c r="C72" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="D72" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="D72" s="8" t="s">
+      <c r="E72" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="E72" s="8" t="s">
+      <c r="F72" s="8" t="s">
         <v>634</v>
       </c>
-      <c r="F72" s="8" t="s">
+      <c r="G72" s="9" t="s">
         <v>635</v>
-      </c>
-      <c r="G72" s="9" t="s">
-        <v>636</v>
       </c>
       <c r="H72" s="8"/>
       <c r="I72" s="8" t="n">
@@ -6352,25 +6347,25 @@
     </row>
     <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="s">
+        <v>636</v>
+      </c>
+      <c r="B73" s="8" t="s">
         <v>637</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="C73" s="8" t="s">
         <v>638</v>
       </c>
-      <c r="C73" s="8" t="s">
+      <c r="D73" s="8" t="s">
         <v>639</v>
       </c>
-      <c r="D73" s="8" t="s">
+      <c r="E73" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="F73" s="8" t="s">
         <v>640</v>
       </c>
-      <c r="E73" s="8" t="s">
-        <v>634</v>
-      </c>
-      <c r="F73" s="8" t="s">
+      <c r="G73" s="9" t="s">
         <v>641</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>642</v>
       </c>
       <c r="H73" s="8"/>
       <c r="I73" s="8" t="n">
@@ -6380,22 +6375,22 @@
     </row>
     <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="B74" s="8" t="s">
         <v>643</v>
       </c>
-      <c r="B74" s="8" t="s">
+      <c r="C74" s="8" t="s">
         <v>644</v>
       </c>
-      <c r="C74" s="8" t="s">
+      <c r="D74" s="8" t="s">
         <v>645</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>646</v>
       </c>
       <c r="E74" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
@@ -6406,25 +6401,25 @@
     </row>
     <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="B75" s="8" t="s">
         <v>648</v>
       </c>
-      <c r="B75" s="8" t="s">
+      <c r="C75" s="8" t="s">
         <v>649</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="D75" s="8" t="s">
         <v>650</v>
-      </c>
-      <c r="D75" s="8" t="s">
-        <v>651</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F75" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="G75" s="9" t="s">
         <v>652</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>653</v>
       </c>
       <c r="H75" s="8"/>
       <c r="I75" s="8" t="n">
@@ -6434,25 +6429,25 @@
     </row>
     <row r="76" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="s">
+        <v>653</v>
+      </c>
+      <c r="B76" s="8" t="s">
         <v>654</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="C76" s="8" t="s">
         <v>655</v>
       </c>
-      <c r="C76" s="8" t="s">
+      <c r="D76" s="8" t="s">
         <v>656</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>657</v>
       </c>
       <c r="E76" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F76" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="G76" s="9" t="s">
         <v>658</v>
-      </c>
-      <c r="G76" s="9" t="s">
-        <v>659</v>
       </c>
       <c r="H76" s="8"/>
       <c r="I76" s="8" t="n">
@@ -6462,25 +6457,25 @@
     </row>
     <row r="77" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="B77" s="8" t="s">
         <v>660</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="C77" s="8" t="s">
         <v>661</v>
       </c>
-      <c r="C77" s="8" t="s">
+      <c r="D77" s="8" t="s">
         <v>662</v>
-      </c>
-      <c r="D77" s="8" t="s">
-        <v>663</v>
       </c>
       <c r="E77" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F77" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="G77" s="9" t="s">
         <v>664</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>665</v>
       </c>
       <c r="H77" s="8"/>
       <c r="I77" s="8" t="n">
@@ -6490,25 +6485,25 @@
     </row>
     <row r="78" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="B78" s="8" t="s">
         <v>666</v>
       </c>
-      <c r="B78" s="8" t="s">
+      <c r="C78" s="8" t="s">
         <v>667</v>
       </c>
-      <c r="C78" s="8" t="s">
+      <c r="D78" s="8" t="s">
         <v>668</v>
       </c>
-      <c r="D78" s="8" t="s">
+      <c r="E78" s="8" t="s">
         <v>669</v>
       </c>
-      <c r="E78" s="8" t="s">
+      <c r="F78" s="8" t="s">
         <v>670</v>
       </c>
-      <c r="F78" s="8" t="s">
+      <c r="G78" s="9" t="s">
         <v>671</v>
-      </c>
-      <c r="G78" s="9" t="s">
-        <v>672</v>
       </c>
       <c r="H78" s="8"/>
       <c r="I78" s="8" t="n">
@@ -6518,25 +6513,25 @@
     </row>
     <row r="79" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>304</v>
       </c>
       <c r="C79" s="8" t="s">
+        <v>673</v>
+      </c>
+      <c r="D79" s="8" t="s">
         <v>674</v>
-      </c>
-      <c r="D79" s="8" t="s">
-        <v>675</v>
       </c>
       <c r="E79" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F79" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="G79" s="9" t="s">
         <v>676</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>677</v>
       </c>
       <c r="H79" s="8"/>
       <c r="I79" s="8" t="n">
@@ -6546,25 +6541,25 @@
     </row>
     <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="s">
+        <v>677</v>
+      </c>
+      <c r="B80" s="8" t="s">
         <v>678</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="C80" s="8" t="s">
         <v>679</v>
       </c>
-      <c r="C80" s="8" t="s">
+      <c r="D80" s="8" t="s">
         <v>680</v>
-      </c>
-      <c r="D80" s="8" t="s">
-        <v>681</v>
       </c>
       <c r="E80" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F80" s="8" t="s">
+        <v>681</v>
+      </c>
+      <c r="G80" s="9" t="s">
         <v>682</v>
-      </c>
-      <c r="G80" s="9" t="s">
-        <v>683</v>
       </c>
       <c r="H80" s="8"/>
       <c r="I80" s="8" t="n">
@@ -6574,25 +6569,25 @@
     </row>
     <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="s">
+        <v>683</v>
+      </c>
+      <c r="B81" s="8" t="s">
         <v>684</v>
       </c>
-      <c r="B81" s="8" t="s">
+      <c r="C81" s="8" t="s">
         <v>685</v>
       </c>
-      <c r="C81" s="8" t="s">
+      <c r="D81" s="8" t="s">
         <v>686</v>
-      </c>
-      <c r="D81" s="8" t="s">
-        <v>687</v>
       </c>
       <c r="E81" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F81" s="8" t="s">
+        <v>687</v>
+      </c>
+      <c r="G81" s="9" t="s">
         <v>688</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>689</v>
       </c>
       <c r="H81" s="8"/>
       <c r="I81" s="8" t="n">
@@ -6602,25 +6597,25 @@
     </row>
     <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B82" s="8" t="s">
         <v>441</v>
       </c>
       <c r="C82" s="8" t="s">
+        <v>690</v>
+      </c>
+      <c r="D82" s="8" t="s">
         <v>691</v>
       </c>
-      <c r="D82" s="8" t="s">
+      <c r="E82" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="F82" s="8" t="s">
         <v>692</v>
       </c>
-      <c r="E82" s="8" t="s">
-        <v>615</v>
-      </c>
-      <c r="F82" s="8" t="s">
+      <c r="G82" s="9" t="s">
         <v>693</v>
-      </c>
-      <c r="G82" s="9" t="s">
-        <v>694</v>
       </c>
       <c r="H82" s="8"/>
       <c r="I82" s="8" t="n">
@@ -6630,25 +6625,25 @@
     </row>
     <row r="83" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="s">
+        <v>694</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="C83" s="8" t="s">
         <v>695</v>
       </c>
-      <c r="B83" s="8" t="s">
-        <v>560</v>
-      </c>
-      <c r="C83" s="8" t="s">
+      <c r="D83" s="8" t="s">
         <v>696</v>
-      </c>
-      <c r="D83" s="8" t="s">
-        <v>697</v>
       </c>
       <c r="E83" s="8" t="s">
         <v>349</v>
       </c>
       <c r="F83" s="8" t="s">
+        <v>697</v>
+      </c>
+      <c r="G83" s="9" t="s">
         <v>698</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>699</v>
       </c>
       <c r="H83" s="8"/>
       <c r="I83" s="8" t="n">
@@ -6658,25 +6653,25 @@
     </row>
     <row r="84" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="s">
+        <v>699</v>
+      </c>
+      <c r="B84" s="8" t="s">
         <v>700</v>
       </c>
-      <c r="B84" s="8" t="s">
+      <c r="C84" s="8" t="s">
         <v>701</v>
       </c>
-      <c r="C84" s="8" t="s">
+      <c r="D84" s="8" t="s">
         <v>702</v>
       </c>
-      <c r="D84" s="8" t="s">
+      <c r="E84" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="F84" s="8" t="s">
         <v>703</v>
       </c>
-      <c r="E84" s="8" t="s">
-        <v>628</v>
-      </c>
-      <c r="F84" s="8" t="s">
+      <c r="G84" s="9" t="s">
         <v>704</v>
-      </c>
-      <c r="G84" s="9" t="s">
-        <v>705</v>
       </c>
       <c r="H84" s="8"/>
       <c r="I84" s="8" t="n">
@@ -6686,25 +6681,25 @@
     </row>
     <row r="85" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="s">
+        <v>705</v>
+      </c>
+      <c r="B85" s="8" t="s">
         <v>706</v>
       </c>
-      <c r="B85" s="8" t="s">
+      <c r="C85" s="8" t="s">
         <v>707</v>
       </c>
-      <c r="C85" s="8" t="s">
+      <c r="D85" s="8" t="s">
         <v>708</v>
-      </c>
-      <c r="D85" s="8" t="s">
-        <v>709</v>
       </c>
       <c r="E85" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F85" s="8" t="s">
+        <v>709</v>
+      </c>
+      <c r="G85" s="9" t="s">
         <v>710</v>
-      </c>
-      <c r="G85" s="9" t="s">
-        <v>711</v>
       </c>
       <c r="H85" s="8"/>
       <c r="I85" s="8" t="n">
@@ -6714,25 +6709,25 @@
     </row>
     <row r="86" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B86" s="8" t="s">
         <v>469</v>
       </c>
       <c r="C86" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="D86" s="8" t="s">
         <v>713</v>
-      </c>
-      <c r="D86" s="8" t="s">
-        <v>714</v>
       </c>
       <c r="E86" s="8" t="s">
         <v>472</v>
       </c>
       <c r="F86" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="G86" s="9" t="s">
         <v>715</v>
-      </c>
-      <c r="G86" s="9" t="s">
-        <v>716</v>
       </c>
       <c r="H86" s="8"/>
       <c r="I86" s="8" t="n">
@@ -6742,25 +6737,25 @@
     </row>
     <row r="87" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="s">
+        <v>716</v>
+      </c>
+      <c r="B87" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="C87" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C87" s="8" t="s">
+      <c r="D87" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="D87" s="8" t="s">
+      <c r="E87" s="8" t="s">
         <v>720</v>
       </c>
-      <c r="E87" s="8" t="s">
+      <c r="F87" s="8" t="s">
         <v>721</v>
       </c>
-      <c r="F87" s="8" t="s">
+      <c r="G87" s="9" t="s">
         <v>722</v>
-      </c>
-      <c r="G87" s="9" t="s">
-        <v>723</v>
       </c>
       <c r="H87" s="8"/>
       <c r="I87" s="8" t="n">
@@ -6770,25 +6765,25 @@
     </row>
     <row r="88" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B88" s="8" t="s">
         <v>322</v>
       </c>
       <c r="C88" s="8" t="s">
+        <v>724</v>
+      </c>
+      <c r="D88" s="8" t="s">
         <v>725</v>
-      </c>
-      <c r="D88" s="8" t="s">
-        <v>726</v>
       </c>
       <c r="E88" s="8" t="s">
         <v>408</v>
       </c>
       <c r="F88" s="8" t="s">
+        <v>726</v>
+      </c>
+      <c r="G88" s="9" t="s">
         <v>727</v>
-      </c>
-      <c r="G88" s="9" t="s">
-        <v>728</v>
       </c>
       <c r="H88" s="8"/>
       <c r="I88" s="8" t="n">
@@ -6798,25 +6793,25 @@
     </row>
     <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="s">
+        <v>728</v>
+      </c>
+      <c r="B89" s="8" t="s">
         <v>729</v>
       </c>
-      <c r="B89" s="8" t="s">
+      <c r="C89" s="8" t="s">
         <v>730</v>
       </c>
-      <c r="C89" s="8" t="s">
+      <c r="D89" s="8" t="s">
         <v>731</v>
-      </c>
-      <c r="D89" s="8" t="s">
-        <v>732</v>
       </c>
       <c r="E89" s="8" t="s">
         <v>281</v>
       </c>
       <c r="F89" s="8" t="s">
+        <v>732</v>
+      </c>
+      <c r="G89" s="9" t="s">
         <v>733</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>734</v>
       </c>
       <c r="H89" s="8"/>
       <c r="I89" s="8" t="n">
@@ -6826,25 +6821,25 @@
     </row>
     <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="s">
+        <v>734</v>
+      </c>
+      <c r="B90" s="8" t="s">
         <v>735</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="C90" s="8" t="s">
         <v>736</v>
       </c>
-      <c r="C90" s="8" t="s">
+      <c r="D90" s="8" t="s">
         <v>737</v>
-      </c>
-      <c r="D90" s="8" t="s">
-        <v>738</v>
       </c>
       <c r="E90" s="8" t="s">
         <v>432</v>
       </c>
       <c r="F90" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="G90" s="9" t="s">
         <v>739</v>
-      </c>
-      <c r="G90" s="9" t="s">
-        <v>740</v>
       </c>
       <c r="H90" s="8"/>
       <c r="I90" s="8" t="n">
@@ -6854,25 +6849,25 @@
     </row>
     <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="s">
+        <v>740</v>
+      </c>
+      <c r="B91" s="8" t="s">
         <v>741</v>
       </c>
-      <c r="B91" s="8" t="s">
+      <c r="C91" s="8" t="s">
         <v>742</v>
       </c>
-      <c r="C91" s="8" t="s">
+      <c r="D91" s="8" t="s">
         <v>743</v>
       </c>
-      <c r="D91" s="8" t="s">
+      <c r="E91" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="F91" s="8" t="s">
         <v>744</v>
       </c>
-      <c r="E91" s="8" t="s">
-        <v>615</v>
-      </c>
-      <c r="F91" s="8" t="s">
+      <c r="G91" s="9" t="s">
         <v>745</v>
-      </c>
-      <c r="G91" s="9" t="s">
-        <v>746</v>
       </c>
       <c r="H91" s="8"/>
       <c r="I91" s="8" t="n">
@@ -6882,25 +6877,25 @@
     </row>
     <row r="92" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="s">
+        <v>746</v>
+      </c>
+      <c r="B92" s="8" t="s">
         <v>747</v>
       </c>
-      <c r="B92" s="8" t="s">
+      <c r="C92" s="8" t="s">
         <v>748</v>
       </c>
-      <c r="C92" s="8" t="s">
+      <c r="D92" s="8" t="s">
         <v>749</v>
       </c>
-      <c r="D92" s="8" t="s">
+      <c r="E92" s="8" t="s">
         <v>750</v>
       </c>
-      <c r="E92" s="8" t="s">
+      <c r="F92" s="8" t="s">
         <v>751</v>
       </c>
-      <c r="F92" s="8" t="s">
+      <c r="G92" s="9" t="s">
         <v>752</v>
-      </c>
-      <c r="G92" s="9" t="s">
-        <v>753</v>
       </c>
       <c r="H92" s="8"/>
       <c r="I92" s="8" t="n">
@@ -6910,25 +6905,25 @@
     </row>
     <row r="93" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="s">
+        <v>753</v>
+      </c>
+      <c r="B93" s="8" t="s">
         <v>754</v>
       </c>
-      <c r="B93" s="8" t="s">
+      <c r="C93" s="8" t="s">
         <v>755</v>
       </c>
-      <c r="C93" s="8" t="s">
+      <c r="D93" s="8" t="s">
         <v>756</v>
-      </c>
-      <c r="D93" s="8" t="s">
-        <v>757</v>
       </c>
       <c r="E93" s="8" t="s">
         <v>237</v>
       </c>
       <c r="F93" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="G93" s="9" t="s">
         <v>758</v>
-      </c>
-      <c r="G93" s="9" t="s">
-        <v>759</v>
       </c>
       <c r="H93" s="8"/>
       <c r="I93" s="8" t="n">
@@ -6938,25 +6933,25 @@
     </row>
     <row r="94" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="s">
+        <v>759</v>
+      </c>
+      <c r="B94" s="8" t="s">
         <v>760</v>
       </c>
-      <c r="B94" s="8" t="s">
+      <c r="C94" s="8" t="s">
         <v>761</v>
       </c>
-      <c r="C94" s="8" t="s">
+      <c r="D94" s="8" t="s">
         <v>762</v>
-      </c>
-      <c r="D94" s="8" t="s">
-        <v>763</v>
       </c>
       <c r="E94" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F94" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="G94" s="9" t="s">
         <v>764</v>
-      </c>
-      <c r="G94" s="9" t="s">
-        <v>765</v>
       </c>
       <c r="H94" s="8"/>
       <c r="I94" s="8" t="n">
@@ -6966,25 +6961,25 @@
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="s">
+        <v>765</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>760</v>
+      </c>
+      <c r="C95" s="8" t="s">
         <v>766</v>
       </c>
-      <c r="B95" s="8" t="s">
-        <v>761</v>
-      </c>
-      <c r="C95" s="8" t="s">
+      <c r="D95" s="8" t="s">
         <v>767</v>
       </c>
-      <c r="D95" s="8" t="s">
+      <c r="E95" s="8" t="s">
         <v>768</v>
       </c>
-      <c r="E95" s="8" t="s">
+      <c r="F95" s="8" t="s">
         <v>769</v>
       </c>
-      <c r="F95" s="8" t="s">
+      <c r="G95" s="9" t="s">
         <v>770</v>
-      </c>
-      <c r="G95" s="9" t="s">
-        <v>771</v>
       </c>
       <c r="H95" s="8"/>
       <c r="I95" s="8" t="n">
@@ -6994,25 +6989,25 @@
     </row>
     <row r="96" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="s">
+        <v>771</v>
+      </c>
+      <c r="B96" s="8" t="s">
         <v>772</v>
       </c>
-      <c r="B96" s="8" t="s">
+      <c r="C96" s="8" t="s">
         <v>773</v>
       </c>
-      <c r="C96" s="8" t="s">
+      <c r="D96" s="8" t="s">
         <v>774</v>
-      </c>
-      <c r="D96" s="8" t="s">
-        <v>775</v>
       </c>
       <c r="E96" s="8" t="s">
         <v>281</v>
       </c>
       <c r="F96" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="G96" s="9" t="s">
         <v>776</v>
-      </c>
-      <c r="G96" s="9" t="s">
-        <v>777</v>
       </c>
       <c r="H96" s="8"/>
       <c r="I96" s="8" t="n">
@@ -7022,25 +7017,25 @@
     </row>
     <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="s">
+        <v>777</v>
+      </c>
+      <c r="B97" s="8" t="s">
         <v>778</v>
       </c>
-      <c r="B97" s="8" t="s">
+      <c r="C97" s="8" t="s">
         <v>779</v>
       </c>
-      <c r="C97" s="8" t="s">
+      <c r="D97" s="8" t="s">
         <v>780</v>
-      </c>
-      <c r="D97" s="8" t="s">
-        <v>781</v>
       </c>
       <c r="E97" s="8" t="s">
         <v>244</v>
       </c>
       <c r="F97" s="8" t="s">
+        <v>781</v>
+      </c>
+      <c r="G97" s="9" t="s">
         <v>782</v>
-      </c>
-      <c r="G97" s="9" t="s">
-        <v>783</v>
       </c>
       <c r="H97" s="8"/>
       <c r="I97" s="8" t="n">
@@ -7050,25 +7045,25 @@
     </row>
     <row r="98" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="s">
+        <v>783</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>772</v>
+      </c>
+      <c r="C98" s="8" t="s">
         <v>784</v>
       </c>
-      <c r="B98" s="8" t="s">
-        <v>773</v>
-      </c>
-      <c r="C98" s="8" t="s">
+      <c r="D98" s="8" t="s">
         <v>785</v>
-      </c>
-      <c r="D98" s="8" t="s">
-        <v>786</v>
       </c>
       <c r="E98" s="8" t="s">
         <v>432</v>
       </c>
       <c r="F98" s="8" t="s">
+        <v>786</v>
+      </c>
+      <c r="G98" s="9" t="s">
         <v>787</v>
-      </c>
-      <c r="G98" s="9" t="s">
-        <v>788</v>
       </c>
       <c r="H98" s="8"/>
       <c r="I98" s="8" t="n">
@@ -7078,25 +7073,25 @@
     </row>
     <row r="99" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="s">
+        <v>788</v>
+      </c>
+      <c r="B99" s="8" t="s">
         <v>789</v>
       </c>
-      <c r="B99" s="8" t="s">
+      <c r="C99" s="8" t="s">
         <v>790</v>
       </c>
-      <c r="C99" s="8" t="s">
+      <c r="D99" s="8" t="s">
         <v>791</v>
-      </c>
-      <c r="D99" s="8" t="s">
-        <v>792</v>
       </c>
       <c r="E99" s="8" t="s">
         <v>281</v>
       </c>
       <c r="F99" s="8" t="s">
+        <v>792</v>
+      </c>
+      <c r="G99" s="9" t="s">
         <v>793</v>
-      </c>
-      <c r="G99" s="9" t="s">
-        <v>794</v>
       </c>
       <c r="H99" s="8"/>
       <c r="I99" s="8" t="n">
@@ -7460,7 +7455,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>205</v>
@@ -7485,7 +7480,7 @@
       <c r="T3" s="13"/>
       <c r="U3" s="13"/>
       <c r="V3" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
@@ -7500,7 +7495,7 @@
       <c r="AG3" s="13"/>
       <c r="AH3" s="13"/>
       <c r="AI3" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AJ3" s="13"/>
       <c r="AK3" s="13"/>
@@ -7511,7 +7506,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>212</v>
@@ -7541,13 +7536,13 @@
       <c r="Y4" s="13"/>
       <c r="Z4" s="13"/>
       <c r="AA4" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AB4" s="13"/>
       <c r="AC4" s="13"/>
       <c r="AD4" s="13"/>
       <c r="AE4" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AF4" s="13"/>
       <c r="AG4" s="13"/>
@@ -7562,7 +7557,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>218</v>
@@ -7588,11 +7583,11 @@
       <c r="U5" s="13"/>
       <c r="V5" s="13"/>
       <c r="W5" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="X5" s="13"/>
       <c r="Y5" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Z5" s="13"/>
       <c r="AA5" s="13"/>
@@ -7613,7 +7608,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>224</v>
@@ -7639,11 +7634,11 @@
       <c r="U6" s="13"/>
       <c r="V6" s="13"/>
       <c r="W6" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="X6" s="13"/>
       <c r="Y6" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Z6" s="13"/>
       <c r="AA6" s="13"/>
@@ -7664,7 +7659,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>230</v>
@@ -7692,7 +7687,7 @@
       <c r="W7" s="13"/>
       <c r="X7" s="13"/>
       <c r="Y7" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Z7" s="13"/>
       <c r="AA7" s="13"/>
@@ -7713,7 +7708,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>236</v>
@@ -7731,7 +7726,7 @@
       <c r="M8" s="13"/>
       <c r="N8" s="13"/>
       <c r="O8" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="P8" s="13"/>
       <c r="Q8" s="13"/>
@@ -7762,7 +7757,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>243</v>
@@ -7777,7 +7772,7 @@
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
       <c r="L9" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
@@ -7811,7 +7806,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>249</v>
@@ -7826,7 +7821,7 @@
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
       <c r="L10" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="M10" s="13"/>
       <c r="N10" s="13"/>
@@ -7860,7 +7855,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>255</v>
@@ -7894,7 +7889,7 @@
       <c r="AC11" s="13"/>
       <c r="AD11" s="13"/>
       <c r="AE11" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AF11" s="13"/>
       <c r="AG11" s="13"/>
@@ -7909,7 +7904,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>260</v>
@@ -7943,7 +7938,7 @@
       <c r="AC12" s="13"/>
       <c r="AD12" s="13"/>
       <c r="AE12" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AF12" s="13"/>
       <c r="AG12" s="13"/>
@@ -7958,7 +7953,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>267</v>
@@ -7980,14 +7975,14 @@
       <c r="Q13" s="13"/>
       <c r="R13" s="13"/>
       <c r="S13" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="T13" s="13"/>
       <c r="U13" s="13"/>
       <c r="V13" s="13"/>
       <c r="W13" s="13"/>
       <c r="X13" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Y13" s="13"/>
       <c r="Z13" s="13"/>
@@ -8009,7 +8004,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>274</v>
@@ -8036,10 +8031,10 @@
       <c r="V14" s="13"/>
       <c r="W14" s="13"/>
       <c r="X14" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Y14" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Z14" s="13"/>
       <c r="AA14" s="13"/>
@@ -8060,7 +8055,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>280</v>
@@ -8072,7 +8067,7 @@
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
       <c r="I15" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J15" s="13"/>
       <c r="K15" s="13"/>
@@ -8081,7 +8076,7 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13"/>
       <c r="P15" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="13"/>
@@ -8111,7 +8106,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>287</v>
@@ -8130,7 +8125,7 @@
       <c r="N16" s="13"/>
       <c r="O16" s="13"/>
       <c r="P16" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Q16" s="13"/>
       <c r="R16" s="13"/>
@@ -8160,13 +8155,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>293</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
@@ -8183,7 +8178,7 @@
       <c r="P17" s="13"/>
       <c r="Q17" s="13"/>
       <c r="R17" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="S17" s="13"/>
       <c r="T17" s="13"/>
@@ -8211,7 +8206,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>300</v>
@@ -8240,7 +8235,7 @@
       <c r="X18" s="13"/>
       <c r="Y18" s="13"/>
       <c r="Z18" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AA18" s="13"/>
       <c r="AB18" s="13"/>
@@ -8260,7 +8255,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>306</v>
@@ -8285,7 +8280,7 @@
       <c r="T19" s="13"/>
       <c r="U19" s="13"/>
       <c r="V19" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="W19" s="13"/>
       <c r="X19" s="13"/>
@@ -8300,7 +8295,7 @@
       <c r="AG19" s="13"/>
       <c r="AH19" s="13"/>
       <c r="AI19" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AJ19" s="13"/>
       <c r="AK19" s="13"/>
@@ -8311,7 +8306,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>312</v>
@@ -8336,7 +8331,7 @@
       <c r="T20" s="13"/>
       <c r="U20" s="13"/>
       <c r="V20" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="W20" s="13"/>
       <c r="X20" s="13"/>
@@ -8360,7 +8355,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>318</v>
@@ -8375,7 +8370,7 @@
       <c r="J21" s="13"/>
       <c r="K21" s="13"/>
       <c r="L21" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="M21" s="13"/>
       <c r="N21" s="13"/>
@@ -8409,7 +8404,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>324</v>
@@ -8442,7 +8437,7 @@
       <c r="AB22" s="13"/>
       <c r="AC22" s="13"/>
       <c r="AD22" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AE22" s="13"/>
       <c r="AF22" s="13"/>
@@ -8458,7 +8453,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>331</v>
@@ -8474,7 +8469,7 @@
       <c r="K23" s="13"/>
       <c r="L23" s="13"/>
       <c r="M23" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="N23" s="13"/>
       <c r="O23" s="13"/>
@@ -8507,7 +8502,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>337</v>
@@ -8515,13 +8510,13 @@
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
       <c r="E24" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="F24" s="13"/>
       <c r="G24" s="13"/>
       <c r="H24" s="13"/>
       <c r="I24" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J24" s="13"/>
       <c r="K24" s="13"/>
@@ -8530,7 +8525,7 @@
       <c r="N24" s="13"/>
       <c r="O24" s="13"/>
       <c r="P24" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Q24" s="13"/>
       <c r="R24" s="13"/>
@@ -8560,7 +8555,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>343</v>
@@ -8580,7 +8575,7 @@
       <c r="O25" s="13"/>
       <c r="P25" s="13"/>
       <c r="Q25" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="R25" s="13"/>
       <c r="S25" s="13"/>
@@ -8609,7 +8604,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>348</v>
@@ -8634,7 +8629,7 @@
       <c r="T26" s="13"/>
       <c r="U26" s="13"/>
       <c r="V26" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="W26" s="13"/>
       <c r="X26" s="13"/>
@@ -8649,7 +8644,7 @@
       <c r="AG26" s="13"/>
       <c r="AH26" s="13"/>
       <c r="AI26" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AJ26" s="13"/>
       <c r="AK26" s="13"/>
@@ -8660,7 +8655,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>355</v>
@@ -8684,11 +8679,11 @@
       <c r="S27" s="13"/>
       <c r="T27" s="13"/>
       <c r="U27" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="V27" s="13"/>
       <c r="W27" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="X27" s="13"/>
       <c r="Y27" s="13"/>
@@ -8711,7 +8706,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>362</v>
@@ -8744,10 +8739,10 @@
       <c r="AB28" s="13"/>
       <c r="AC28" s="13"/>
       <c r="AD28" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AE28" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AF28" s="13"/>
       <c r="AG28" s="13"/>
@@ -8762,7 +8757,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>368</v>
@@ -8785,10 +8780,10 @@
       <c r="R29" s="13"/>
       <c r="S29" s="13"/>
       <c r="T29" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="U29" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="V29" s="13"/>
       <c r="W29" s="13"/>
@@ -8813,7 +8808,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>374</v>
@@ -8852,7 +8847,7 @@
       <c r="AH30" s="13"/>
       <c r="AI30" s="13"/>
       <c r="AJ30" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AK30" s="13"/>
       <c r="AL30" s="15" t="n">
@@ -8862,16 +8857,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>381</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E31" s="13"/>
       <c r="F31" s="13"/>
@@ -8913,7 +8908,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>388</v>
@@ -8922,7 +8917,7 @@
       <c r="D32" s="13"/>
       <c r="E32" s="13"/>
       <c r="F32" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="G32" s="13"/>
       <c r="H32" s="13"/>
@@ -8951,7 +8946,7 @@
       <c r="AE32" s="13"/>
       <c r="AF32" s="13"/>
       <c r="AG32" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AH32" s="13"/>
       <c r="AI32" s="13"/>
@@ -8964,7 +8959,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>394</v>
@@ -8990,11 +8985,11 @@
       <c r="U33" s="13"/>
       <c r="V33" s="13"/>
       <c r="W33" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="X33" s="13"/>
       <c r="Y33" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Z33" s="13"/>
       <c r="AA33" s="13"/>
@@ -9015,7 +9010,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>401</v>
@@ -9027,7 +9022,7 @@
       <c r="G34" s="13"/>
       <c r="H34" s="13"/>
       <c r="I34" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J34" s="13"/>
       <c r="K34" s="13"/>
@@ -9064,7 +9059,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>407</v>
@@ -9100,7 +9095,7 @@
       <c r="AE35" s="13"/>
       <c r="AF35" s="13"/>
       <c r="AG35" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AH35" s="13"/>
       <c r="AI35" s="13"/>
@@ -9113,7 +9108,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>413</v>
@@ -9132,7 +9127,7 @@
       <c r="N36" s="13"/>
       <c r="O36" s="13"/>
       <c r="P36" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Q36" s="13"/>
       <c r="R36" s="13"/>
@@ -9162,7 +9157,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>419</v>
@@ -9177,13 +9172,13 @@
       <c r="J37" s="13"/>
       <c r="K37" s="13"/>
       <c r="L37" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="13"/>
       <c r="O37" s="13"/>
       <c r="P37" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Q37" s="13"/>
       <c r="R37" s="13"/>
@@ -9213,7 +9208,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>425</v>
@@ -9227,17 +9222,17 @@
       <c r="I38" s="13"/>
       <c r="J38" s="13"/>
       <c r="K38" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="L38" s="13"/>
       <c r="M38" s="13"/>
       <c r="N38" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="O38" s="13"/>
       <c r="P38" s="13"/>
       <c r="Q38" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="R38" s="13"/>
       <c r="S38" s="13"/>
@@ -9266,7 +9261,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B39" s="12" t="s">
         <v>431</v>
@@ -9274,14 +9269,14 @@
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
       <c r="E39" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="F39" s="13"/>
       <c r="G39" s="13"/>
       <c r="H39" s="13"/>
       <c r="I39" s="13"/>
       <c r="J39" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="K39" s="13"/>
       <c r="L39" s="13"/>
@@ -9317,7 +9312,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>437</v>
@@ -9333,7 +9328,7 @@
       <c r="K40" s="13"/>
       <c r="L40" s="13"/>
       <c r="M40" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="N40" s="13"/>
       <c r="O40" s="13"/>
@@ -9366,14 +9361,14 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B41" s="12" t="s">
         <v>443</v>
       </c>
       <c r="C41" s="13"/>
       <c r="D41" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E41" s="13"/>
       <c r="F41" s="13"/>
@@ -9405,7 +9400,7 @@
       <c r="AF41" s="13"/>
       <c r="AG41" s="13"/>
       <c r="AH41" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AI41" s="13"/>
       <c r="AJ41" s="13"/>
@@ -9417,14 +9412,14 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>448</v>
       </c>
       <c r="C42" s="13"/>
       <c r="D42" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
@@ -9456,7 +9451,7 @@
       <c r="AF42" s="13"/>
       <c r="AG42" s="13"/>
       <c r="AH42" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AI42" s="13"/>
       <c r="AJ42" s="13"/>
@@ -9468,7 +9463,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B43" s="12" t="s">
         <v>453</v>
@@ -9497,7 +9492,7 @@
       <c r="X43" s="13"/>
       <c r="Y43" s="13"/>
       <c r="Z43" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AA43" s="13"/>
       <c r="AB43" s="13"/>
@@ -9517,7 +9512,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>459</v>
@@ -9544,11 +9539,11 @@
       <c r="V44" s="13"/>
       <c r="W44" s="13"/>
       <c r="X44" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Y44" s="13"/>
       <c r="Z44" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AA44" s="13"/>
       <c r="AB44" s="13"/>
@@ -9568,7 +9563,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>465</v>
@@ -9589,7 +9584,7 @@
       <c r="P45" s="13"/>
       <c r="Q45" s="13"/>
       <c r="R45" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="S45" s="13"/>
       <c r="T45" s="13"/>
@@ -9599,7 +9594,7 @@
       <c r="X45" s="13"/>
       <c r="Y45" s="13"/>
       <c r="Z45" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AA45" s="13"/>
       <c r="AB45" s="13"/>
@@ -9619,7 +9614,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>471</v>
@@ -9637,10 +9632,10 @@
       <c r="M46" s="13"/>
       <c r="N46" s="13"/>
       <c r="O46" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="P46" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Q46" s="13"/>
       <c r="R46" s="13"/>
@@ -9670,7 +9665,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B47" s="12" t="s">
         <v>478</v>
@@ -9695,11 +9690,11 @@
       <c r="T47" s="13"/>
       <c r="U47" s="13"/>
       <c r="V47" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="W47" s="13"/>
       <c r="X47" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Y47" s="13"/>
       <c r="Z47" s="13"/>
@@ -9721,7 +9716,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>484</v>
@@ -9740,7 +9735,7 @@
       <c r="N48" s="13"/>
       <c r="O48" s="13"/>
       <c r="P48" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Q48" s="13"/>
       <c r="R48" s="13"/>
@@ -9760,7 +9755,7 @@
       <c r="AF48" s="13"/>
       <c r="AG48" s="13"/>
       <c r="AH48" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AI48" s="13"/>
       <c r="AJ48" s="13"/>
@@ -9772,7 +9767,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B49" s="12" t="s">
         <v>491</v>
@@ -9795,7 +9790,7 @@
       <c r="R49" s="13"/>
       <c r="S49" s="13"/>
       <c r="T49" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="U49" s="13"/>
       <c r="V49" s="13"/>
@@ -9821,14 +9816,14 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>497</v>
       </c>
       <c r="C50" s="13"/>
       <c r="D50" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E50" s="13"/>
       <c r="F50" s="13"/>
@@ -9870,7 +9865,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="12" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B51" s="12" t="s">
         <v>503</v>
@@ -9897,7 +9892,7 @@
       <c r="V51" s="13"/>
       <c r="W51" s="13"/>
       <c r="X51" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Y51" s="13"/>
       <c r="Z51" s="13"/>
@@ -9919,7 +9914,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>509</v>
@@ -9930,7 +9925,7 @@
       <c r="F52" s="13"/>
       <c r="G52" s="13"/>
       <c r="H52" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="I52" s="13"/>
       <c r="J52" s="13"/>
@@ -9938,12 +9933,12 @@
       <c r="L52" s="13"/>
       <c r="M52" s="13"/>
       <c r="N52" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="O52" s="13"/>
       <c r="P52" s="13"/>
       <c r="Q52" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="R52" s="13"/>
       <c r="S52" s="13"/>
@@ -9972,7 +9967,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B53" s="12" t="s">
         <v>516</v>
@@ -9983,7 +9978,7 @@
       <c r="F53" s="13"/>
       <c r="G53" s="13"/>
       <c r="H53" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="I53" s="13"/>
       <c r="J53" s="13"/>
@@ -10021,7 +10016,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>521</v>
@@ -10054,7 +10049,7 @@
       <c r="AB54" s="13"/>
       <c r="AC54" s="13"/>
       <c r="AD54" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AE54" s="13"/>
       <c r="AF54" s="13"/>
@@ -10070,7 +10065,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B55" s="12" t="s">
         <v>527</v>
@@ -10101,7 +10096,7 @@
       <c r="Z55" s="13"/>
       <c r="AA55" s="13"/>
       <c r="AB55" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AC55" s="13"/>
       <c r="AD55" s="13"/>
@@ -10119,7 +10114,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>534</v>
@@ -10144,10 +10139,10 @@
       <c r="T56" s="13"/>
       <c r="U56" s="13"/>
       <c r="V56" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="W56" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="X56" s="13"/>
       <c r="Y56" s="13"/>
@@ -10161,7 +10156,7 @@
       <c r="AG56" s="13"/>
       <c r="AH56" s="13"/>
       <c r="AI56" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AJ56" s="13"/>
       <c r="AK56" s="13"/>
@@ -10172,7 +10167,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B57" s="12" t="s">
         <v>539</v>
@@ -10212,7 +10207,7 @@
       <c r="AI57" s="13"/>
       <c r="AJ57" s="13"/>
       <c r="AK57" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AL57" s="15" t="n">
         <f aca="false">COUNTIF(C57:AK57,"x")</f>
@@ -10221,7 +10216,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>544</v>
@@ -10233,7 +10228,7 @@
       <c r="G58" s="13"/>
       <c r="H58" s="13"/>
       <c r="I58" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J58" s="13"/>
       <c r="K58" s="13"/>
@@ -10270,10 +10265,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C59" s="13"/>
       <c r="D59" s="13"/>
@@ -10290,7 +10285,7 @@
       <c r="O59" s="13"/>
       <c r="P59" s="13"/>
       <c r="Q59" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="R59" s="13"/>
       <c r="S59" s="13"/>
@@ -10303,7 +10298,7 @@
       <c r="Z59" s="13"/>
       <c r="AA59" s="13"/>
       <c r="AB59" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AC59" s="13"/>
       <c r="AD59" s="13"/>
@@ -10321,10 +10316,10 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C60" s="13"/>
       <c r="D60" s="13"/>
@@ -10352,10 +10347,10 @@
       <c r="Z60" s="13"/>
       <c r="AA60" s="13"/>
       <c r="AB60" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AC60" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AD60" s="13"/>
       <c r="AE60" s="13"/>
@@ -10372,10 +10367,10 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="12" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C61" s="13"/>
       <c r="D61" s="13"/>
@@ -10407,7 +10402,7 @@
       <c r="AD61" s="13"/>
       <c r="AE61" s="13"/>
       <c r="AF61" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AG61" s="13"/>
       <c r="AH61" s="13"/>
@@ -10421,15 +10416,15 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C62" s="13"/>
       <c r="D62" s="13"/>
       <c r="E62" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="F62" s="13"/>
       <c r="G62" s="13"/>
@@ -10439,7 +10434,7 @@
       <c r="K62" s="13"/>
       <c r="L62" s="13"/>
       <c r="M62" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="N62" s="13"/>
       <c r="O62" s="13"/>
@@ -10472,10 +10467,10 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="12" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C63" s="13"/>
       <c r="D63" s="13"/>
@@ -10497,7 +10492,7 @@
       <c r="T63" s="13"/>
       <c r="U63" s="13"/>
       <c r="V63" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="W63" s="13"/>
       <c r="X63" s="13"/>
@@ -10512,7 +10507,7 @@
       <c r="AG63" s="13"/>
       <c r="AH63" s="13"/>
       <c r="AI63" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AJ63" s="13"/>
       <c r="AK63" s="13"/>
@@ -10523,10 +10518,10 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C64" s="13"/>
       <c r="D64" s="13"/>
@@ -10538,7 +10533,7 @@
       <c r="J64" s="13"/>
       <c r="K64" s="13"/>
       <c r="L64" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="M64" s="13"/>
       <c r="N64" s="13"/>
@@ -10572,10 +10567,10 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="12" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C65" s="13"/>
       <c r="D65" s="13"/>
@@ -10586,10 +10581,10 @@
       <c r="I65" s="13"/>
       <c r="J65" s="13"/>
       <c r="K65" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="L65" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="M65" s="13"/>
       <c r="N65" s="13"/>
@@ -10613,7 +10608,7 @@
       <c r="AF65" s="13"/>
       <c r="AG65" s="13"/>
       <c r="AH65" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AI65" s="13"/>
       <c r="AJ65" s="13"/>
@@ -10625,10 +10620,10 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C66" s="13"/>
       <c r="D66" s="13"/>
@@ -10659,7 +10654,7 @@
       <c r="AC66" s="13"/>
       <c r="AD66" s="13"/>
       <c r="AE66" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AF66" s="13"/>
       <c r="AG66" s="13"/>
@@ -10674,10 +10669,10 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="12" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C67" s="13"/>
       <c r="D67" s="13"/>
@@ -10711,7 +10706,7 @@
       <c r="AF67" s="13"/>
       <c r="AG67" s="13"/>
       <c r="AH67" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AI67" s="13"/>
       <c r="AJ67" s="13"/>
@@ -10723,10 +10718,10 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="12" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C68" s="13"/>
       <c r="D68" s="13"/>
@@ -10760,7 +10755,7 @@
       <c r="AF68" s="13"/>
       <c r="AG68" s="13"/>
       <c r="AH68" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AI68" s="13"/>
       <c r="AJ68" s="13"/>
@@ -10772,13 +10767,13 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D69" s="13"/>
       <c r="E69" s="13"/>
@@ -10821,10 +10816,10 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="12" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C70" s="13"/>
       <c r="D70" s="13"/>
@@ -10843,14 +10838,14 @@
       <c r="Q70" s="13"/>
       <c r="R70" s="13"/>
       <c r="S70" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="T70" s="13"/>
       <c r="U70" s="13"/>
       <c r="V70" s="13"/>
       <c r="W70" s="13"/>
       <c r="X70" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Y70" s="13"/>
       <c r="Z70" s="13"/>
@@ -10872,10 +10867,10 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="12" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C71" s="13"/>
       <c r="D71" s="13"/>
@@ -10886,7 +10881,7 @@
       <c r="I71" s="13"/>
       <c r="J71" s="13"/>
       <c r="K71" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="L71" s="13"/>
       <c r="M71" s="13"/>
@@ -10911,7 +10906,7 @@
       <c r="AF71" s="13"/>
       <c r="AG71" s="13"/>
       <c r="AH71" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AI71" s="13"/>
       <c r="AJ71" s="13"/>
@@ -10923,10 +10918,10 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C72" s="13"/>
       <c r="D72" s="13"/>
@@ -10948,7 +10943,7 @@
       <c r="T72" s="13"/>
       <c r="U72" s="13"/>
       <c r="V72" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="W72" s="13"/>
       <c r="X72" s="13"/>
@@ -10972,10 +10967,10 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="12" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C73" s="13"/>
       <c r="D73" s="13"/>
@@ -11003,7 +10998,7 @@
       <c r="Z73" s="13"/>
       <c r="AA73" s="13"/>
       <c r="AB73" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AC73" s="13"/>
       <c r="AD73" s="13"/>
@@ -11021,10 +11016,10 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C74" s="13"/>
       <c r="D74" s="13"/>
@@ -11051,10 +11046,10 @@
       <c r="Y74" s="13"/>
       <c r="Z74" s="13"/>
       <c r="AA74" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AB74" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AC74" s="13"/>
       <c r="AD74" s="13"/>
@@ -11072,10 +11067,10 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C75" s="13"/>
       <c r="D75" s="13"/>
@@ -11090,7 +11085,7 @@
       <c r="M75" s="13"/>
       <c r="N75" s="13"/>
       <c r="O75" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="P75" s="13"/>
       <c r="Q75" s="13"/>
@@ -11104,10 +11099,10 @@
       <c r="Y75" s="13"/>
       <c r="Z75" s="13"/>
       <c r="AA75" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AB75" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AC75" s="13"/>
       <c r="AD75" s="13"/>
@@ -11125,13 +11120,13 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D76" s="13"/>
       <c r="E76" s="13"/>
@@ -11147,7 +11142,7 @@
       <c r="O76" s="13"/>
       <c r="P76" s="13"/>
       <c r="Q76" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="R76" s="13"/>
       <c r="S76" s="13"/>
@@ -11176,10 +11171,10 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="12" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C77" s="13"/>
       <c r="D77" s="13"/>
@@ -11206,7 +11201,7 @@
       <c r="Y77" s="13"/>
       <c r="Z77" s="13"/>
       <c r="AA77" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AB77" s="13"/>
       <c r="AC77" s="13"/>
@@ -11225,10 +11220,10 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C78" s="13"/>
       <c r="D78" s="13"/>
@@ -11248,12 +11243,12 @@
       <c r="R78" s="13"/>
       <c r="S78" s="13"/>
       <c r="T78" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="U78" s="13"/>
       <c r="V78" s="13"/>
       <c r="W78" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="X78" s="13"/>
       <c r="Y78" s="13"/>
@@ -11276,10 +11271,10 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="12" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C79" s="13"/>
       <c r="D79" s="13"/>
@@ -11302,11 +11297,11 @@
       <c r="U79" s="13"/>
       <c r="V79" s="13"/>
       <c r="W79" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="X79" s="13"/>
       <c r="Y79" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Z79" s="13"/>
       <c r="AA79" s="13"/>
@@ -11318,7 +11313,7 @@
       <c r="AG79" s="13"/>
       <c r="AH79" s="13"/>
       <c r="AI79" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AJ79" s="13"/>
       <c r="AK79" s="13"/>
@@ -11329,10 +11324,10 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C80" s="13"/>
       <c r="D80" s="13"/>
@@ -11354,7 +11349,7 @@
       <c r="T80" s="13"/>
       <c r="U80" s="13"/>
       <c r="V80" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="W80" s="13"/>
       <c r="X80" s="13"/>
@@ -11369,7 +11364,7 @@
       <c r="AG80" s="13"/>
       <c r="AH80" s="13"/>
       <c r="AI80" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AJ80" s="13"/>
       <c r="AK80" s="13"/>
@@ -11380,10 +11375,10 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="12" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C81" s="13"/>
       <c r="D81" s="13"/>
@@ -11402,10 +11397,10 @@
       <c r="Q81" s="13"/>
       <c r="R81" s="13"/>
       <c r="S81" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="T81" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="U81" s="13"/>
       <c r="V81" s="13"/>
@@ -11431,13 +11426,13 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D82" s="13"/>
       <c r="E82" s="13"/>
@@ -11457,7 +11452,7 @@
       <c r="S82" s="13"/>
       <c r="T82" s="13"/>
       <c r="U82" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="V82" s="13"/>
       <c r="W82" s="13"/>
@@ -11482,14 +11477,14 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="12" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C83" s="13"/>
       <c r="D83" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E83" s="13"/>
       <c r="F83" s="13"/>
@@ -11521,7 +11516,7 @@
       <c r="AF83" s="13"/>
       <c r="AG83" s="13"/>
       <c r="AH83" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AI83" s="13"/>
       <c r="AJ83" s="13"/>
@@ -11533,10 +11528,10 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C84" s="13"/>
       <c r="D84" s="13"/>
@@ -11568,7 +11563,7 @@
       <c r="AD84" s="13"/>
       <c r="AE84" s="13"/>
       <c r="AF84" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AG84" s="13"/>
       <c r="AH84" s="13"/>
@@ -11582,10 +11577,10 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="12" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C85" s="13"/>
       <c r="D85" s="13"/>
@@ -11608,7 +11603,7 @@
       <c r="U85" s="13"/>
       <c r="V85" s="13"/>
       <c r="W85" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="X85" s="13"/>
       <c r="Y85" s="13"/>
@@ -11620,7 +11615,7 @@
       <c r="AE85" s="13"/>
       <c r="AF85" s="13"/>
       <c r="AG85" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AH85" s="13"/>
       <c r="AI85" s="13"/>
@@ -11633,10 +11628,10 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="12" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C86" s="13"/>
       <c r="D86" s="13"/>
@@ -11659,10 +11654,10 @@
       <c r="U86" s="13"/>
       <c r="V86" s="13"/>
       <c r="W86" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="X86" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Y86" s="13"/>
       <c r="Z86" s="13"/>
@@ -11684,10 +11679,10 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="12" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C87" s="13"/>
       <c r="D87" s="13"/>
@@ -11702,10 +11697,10 @@
       <c r="M87" s="13"/>
       <c r="N87" s="13"/>
       <c r="O87" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="P87" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Q87" s="13"/>
       <c r="R87" s="13"/>
@@ -11735,18 +11730,18 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="12" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C88" s="13"/>
       <c r="D88" s="13"/>
       <c r="E88" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="F88" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="G88" s="13"/>
       <c r="H88" s="13"/>
@@ -11756,7 +11751,7 @@
       <c r="L88" s="13"/>
       <c r="M88" s="13"/>
       <c r="N88" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="O88" s="13"/>
       <c r="P88" s="13"/>
@@ -11788,10 +11783,10 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="12" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C89" s="13"/>
       <c r="D89" s="13"/>
@@ -11821,7 +11816,7 @@
       <c r="AB89" s="13"/>
       <c r="AC89" s="13"/>
       <c r="AD89" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AE89" s="13"/>
       <c r="AF89" s="13"/>
@@ -11837,10 +11832,10 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="12" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C90" s="13"/>
       <c r="D90" s="13"/>
@@ -11850,7 +11845,7 @@
       <c r="H90" s="13"/>
       <c r="I90" s="13"/>
       <c r="J90" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="K90" s="13"/>
       <c r="L90" s="13"/>
@@ -11886,15 +11881,15 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="12" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C91" s="13"/>
       <c r="D91" s="13"/>
       <c r="E91" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="F91" s="13"/>
       <c r="G91" s="13"/>
@@ -11935,14 +11930,14 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="12" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C92" s="13"/>
       <c r="D92" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E92" s="13"/>
       <c r="F92" s="13"/>
@@ -11974,7 +11969,7 @@
       <c r="AF92" s="13"/>
       <c r="AG92" s="13"/>
       <c r="AH92" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AI92" s="13"/>
       <c r="AJ92" s="13"/>
@@ -11986,28 +11981,28 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="12" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C93" s="13"/>
       <c r="D93" s="13"/>
       <c r="E93" s="13"/>
       <c r="F93" s="13"/>
       <c r="G93" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H93" s="13"/>
       <c r="I93" s="13"/>
       <c r="J93" s="13"/>
       <c r="K93" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="L93" s="13"/>
       <c r="M93" s="13"/>
       <c r="N93" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="O93" s="13"/>
       <c r="P93" s="13"/>
@@ -12039,19 +12034,19 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="12" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C94" s="13"/>
       <c r="D94" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E94" s="13"/>
       <c r="F94" s="13"/>
       <c r="G94" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H94" s="13"/>
       <c r="I94" s="13"/>
@@ -12080,7 +12075,7 @@
       <c r="AF94" s="13"/>
       <c r="AG94" s="13"/>
       <c r="AH94" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AI94" s="13"/>
       <c r="AJ94" s="13"/>
@@ -12092,10 +12087,10 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="12" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C95" s="13"/>
       <c r="D95" s="13"/>
@@ -12118,7 +12113,7 @@
       <c r="U95" s="13"/>
       <c r="V95" s="13"/>
       <c r="W95" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="X95" s="13"/>
       <c r="Y95" s="13"/>
@@ -12141,10 +12136,10 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="12" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C96" s="13"/>
       <c r="D96" s="13"/>
@@ -12167,7 +12162,7 @@
       <c r="U96" s="13"/>
       <c r="V96" s="13"/>
       <c r="W96" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="X96" s="13"/>
       <c r="Y96" s="13"/>
@@ -12190,13 +12185,13 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="12" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C97" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D97" s="13"/>
       <c r="E97" s="13"/>
@@ -12204,7 +12199,7 @@
       <c r="G97" s="13"/>
       <c r="H97" s="13"/>
       <c r="I97" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J97" s="13"/>
       <c r="K97" s="13"/>
@@ -12241,10 +12236,10 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="12" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C98" s="13"/>
       <c r="D98" s="13"/>
@@ -12255,7 +12250,7 @@
       <c r="I98" s="13"/>
       <c r="J98" s="13"/>
       <c r="K98" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="L98" s="13"/>
       <c r="M98" s="13"/>
@@ -12290,13 +12285,13 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="12" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C99" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D99" s="13"/>
       <c r="E99" s="13"/>
@@ -12304,7 +12299,7 @@
       <c r="G99" s="13"/>
       <c r="H99" s="13"/>
       <c r="I99" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J99" s="13"/>
       <c r="K99" s="13"/>
@@ -12341,17 +12336,17 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="12" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C100" s="13"/>
       <c r="D100" s="13"/>
       <c r="E100" s="13"/>
       <c r="F100" s="13"/>
       <c r="G100" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H100" s="13"/>
       <c r="I100" s="13"/>
@@ -12360,7 +12355,7 @@
       <c r="L100" s="13"/>
       <c r="M100" s="13"/>
       <c r="N100" s="14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="O100" s="13"/>
       <c r="P100" s="13"/>
